--- a/secondary_logistics_routes.xlsx
+++ b/secondary_logistics_routes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F89"/>
+  <dimension ref="A1:G106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,15 +446,20 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>store_list</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>total_load_cft</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>route_distance_km</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>route_cost</t>
         </is>
@@ -470,13 +475,18 @@
       <c r="C2" t="n">
         <v>5</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>DPI64254, DPI66669, DPI66594, DPI66372, DPI64247</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>620.5440050899999</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>112.8614983328272</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>89314.29547251892</v>
       </c>
     </row>
@@ -485,19 +495,24 @@
         <v>0</v>
       </c>
       <c r="B3" t="n">
-        <v>1109</v>
+        <v>207</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
-      </c>
-      <c r="D3" t="n">
-        <v>615.64704425</v>
+        <v>2</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>DPI64091, DPI70040</t>
+        </is>
       </c>
       <c r="E3" t="n">
-        <v>919.1199764505016</v>
+        <v>144.79150005</v>
       </c>
       <c r="F3" t="n">
-        <v>112276.5369293103</v>
+        <v>174.6836307166889</v>
+      </c>
+      <c r="G3" t="n">
+        <v>67534.93843279795</v>
       </c>
     </row>
     <row r="4">
@@ -505,19 +520,24 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>1109</v>
+        <v>207</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D4" t="n">
-        <v>635.58155517</v>
+        <v>1</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>DPI66995</t>
+        </is>
       </c>
       <c r="E4" t="n">
-        <v>1506.21644200374</v>
+        <v>145.0125221</v>
       </c>
       <c r="F4" t="n">
-        <v>128997.0442682665</v>
+        <v>134.2947994573659</v>
+      </c>
+      <c r="G4" t="n">
+        <v>66729.18124917445</v>
       </c>
     </row>
     <row r="5">
@@ -525,19 +545,24 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>1109</v>
+        <v>407</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
-      </c>
-      <c r="D5" t="n">
-        <v>631.36292425</v>
+        <v>4</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>DPI70031, DPI66461, DPI70165, DPI64191</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>1888.72775062438</v>
+        <v>325.8430221</v>
       </c>
       <c r="F5" t="n">
-        <v>139890.9663377823</v>
+        <v>610.1415462764469</v>
+      </c>
+      <c r="G5" t="n">
+        <v>93997.43724144841</v>
       </c>
     </row>
     <row r="6">
@@ -545,19 +570,24 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>1109</v>
+        <v>407</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
-      </c>
-      <c r="D6" t="n">
-        <v>593.9202967099999</v>
+        <v>4</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>DPI64590, DPI70221, DPI70149, DPI70327</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>1766.120809792729</v>
+        <v>334.53533758</v>
       </c>
       <c r="F6" t="n">
-        <v>136399.1206628969</v>
+        <v>828.5588699925895</v>
+      </c>
+      <c r="G6" t="n">
+        <v>99455.68616111481</v>
       </c>
     </row>
     <row r="7">
@@ -568,16 +598,21 @@
         <v>1109</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D7" t="n">
-        <v>577.2739750799999</v>
+        <v>8</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>DPI64561, DPI64281, DPI65827, DPI70082, DPI67214, DPI66974, DPI70090, DPI64400</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>1043.140257074436</v>
+        <v>635.10630896</v>
       </c>
       <c r="F7" t="n">
-        <v>115808.6345214799</v>
+        <v>1841.099839748307</v>
+      </c>
+      <c r="G7" t="n">
+        <v>138534.5234360318</v>
       </c>
     </row>
     <row r="8">
@@ -585,19 +620,24 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>1109</v>
+        <v>407</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D8" t="n">
-        <v>658.66075268</v>
+        <v>4</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>DPI64694, DPI70254, DPI66511, DPI64462</t>
+        </is>
       </c>
       <c r="E8" t="n">
-        <v>1668.504275701171</v>
+        <v>346.40689368</v>
       </c>
       <c r="F8" t="n">
-        <v>133619.0017719693</v>
+        <v>974.9764917793544</v>
+      </c>
+      <c r="G8" t="n">
+        <v>103114.6625295661</v>
       </c>
     </row>
     <row r="9">
@@ -605,19 +645,24 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>1109</v>
+        <v>207</v>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
-      </c>
-      <c r="D9" t="n">
-        <v>574.44633805</v>
+        <v>2</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>DPI64606, DPI65825</t>
+        </is>
       </c>
       <c r="E9" t="n">
-        <v>1862.410046468696</v>
+        <v>146.23574425</v>
       </c>
       <c r="F9" t="n">
-        <v>139141.4381234284</v>
+        <v>500.995255690341</v>
+      </c>
+      <c r="G9" t="n">
+        <v>74044.8553510223</v>
       </c>
     </row>
     <row r="10">
@@ -625,19 +670,24 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>1109</v>
+        <v>407</v>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
-      </c>
-      <c r="D10" t="n">
-        <v>524.68860108</v>
+        <v>3</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>DPI65967, DPI66512, DPI64711</t>
+        </is>
       </c>
       <c r="E10" t="n">
-        <v>1625.472024607073</v>
+        <v>328.3208980799999</v>
       </c>
       <c r="F10" t="n">
-        <v>132393.4432608094</v>
+        <v>759.5723157985121</v>
+      </c>
+      <c r="G10" t="n">
+        <v>97731.71217180481</v>
       </c>
     </row>
     <row r="11">
@@ -645,19 +695,24 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>1109</v>
+        <v>407</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
-      </c>
-      <c r="D11" t="n">
-        <v>583.2367953200001</v>
+        <v>3</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>DPI64364, DPI66265, DPI67245</t>
+        </is>
       </c>
       <c r="E11" t="n">
-        <v>2225.795146943221</v>
+        <v>337.6667410699999</v>
       </c>
       <c r="F11" t="n">
-        <v>149490.645784943</v>
+        <v>768.9737554290704</v>
+      </c>
+      <c r="G11" t="n">
+        <v>97966.65414817247</v>
       </c>
     </row>
     <row r="12">
@@ -665,19 +720,24 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>1109</v>
+        <v>1613</v>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
-      </c>
-      <c r="D12" t="n">
-        <v>637.4483849599999</v>
+        <v>8</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>DPI64513, DPI65824, DPI67043, DPI65981, DPI65927, DPI64239, DPI66555, DPI64045</t>
+        </is>
       </c>
       <c r="E12" t="n">
-        <v>3247.478362139138</v>
+        <v>968.52758027</v>
       </c>
       <c r="F12" t="n">
-        <v>178588.1837537226</v>
+        <v>2198.53300675828</v>
+      </c>
+      <c r="G12" t="n">
+        <v>171025.8679517392</v>
       </c>
     </row>
     <row r="13">
@@ -685,19 +745,24 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>1109</v>
+        <v>1613</v>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
-      </c>
-      <c r="D13" t="n">
-        <v>565.3912172299999</v>
+        <v>9</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>DPI66503, DPI64008, DPI64619, DPI67004, DPI64175, DPI64085, DPI66060, DPI70228, DPI66100</t>
+        </is>
       </c>
       <c r="E13" t="n">
-        <v>2637.620058278286</v>
+        <v>928.5492191299999</v>
       </c>
       <c r="F13" t="n">
-        <v>161219.4192597656</v>
+        <v>2822.379392352044</v>
+      </c>
+      <c r="G13" t="n">
+        <v>191494.2678630706</v>
       </c>
     </row>
     <row r="14">
@@ -705,19 +770,24 @@
         <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>1109</v>
+        <v>407</v>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
-      </c>
-      <c r="D14" t="n">
-        <v>659.73099926</v>
+        <v>3</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>DPI70035, DPI64108, DPI66938</t>
+        </is>
       </c>
       <c r="E14" t="n">
-        <v>3369.534335814813</v>
+        <v>332.7000399999999</v>
       </c>
       <c r="F14" t="n">
-        <v>182064.3378840059</v>
+        <v>1008.624873895105</v>
+      </c>
+      <c r="G14" t="n">
+        <v>103955.5355986387</v>
       </c>
     </row>
     <row r="15">
@@ -725,19 +795,24 @@
         <v>0</v>
       </c>
       <c r="B15" t="n">
-        <v>1109</v>
+        <v>407</v>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
-      </c>
-      <c r="D15" t="n">
-        <v>597.16899331</v>
+        <v>3</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>DPI67102, DPI64024, DPI67047</t>
+        </is>
       </c>
       <c r="E15" t="n">
-        <v>4169.444632977141</v>
+        <v>317.49137532</v>
       </c>
       <c r="F15" t="n">
-        <v>204845.783147189</v>
+        <v>1077.853653632775</v>
+      </c>
+      <c r="G15" t="n">
+        <v>105685.5628042831</v>
       </c>
     </row>
     <row r="16">
@@ -745,99 +820,124 @@
         <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>1109</v>
+        <v>407</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
-      </c>
-      <c r="D16" t="n">
-        <v>453.6706360499999</v>
+        <v>4</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>DPI70234, DPI66915, DPI64506, DPI66491</t>
+        </is>
       </c>
       <c r="E16" t="n">
-        <v>5401.991556780065</v>
+        <v>316.75566</v>
       </c>
       <c r="F16" t="n">
-        <v>239948.7195370963</v>
+        <v>1664.129129929559</v>
+      </c>
+      <c r="G16" t="n">
+        <v>120336.5869569397</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>1109</v>
+        <v>1613</v>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
-      </c>
-      <c r="D17" t="n">
-        <v>556.9663399999999</v>
+        <v>9</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>DPI64361, DPI65875, DPI63898, DPI64543, DPI66759, DPI63904, DPI66091, DPI70095, DPI64374</t>
+        </is>
       </c>
       <c r="E17" t="n">
-        <v>246.2997337066784</v>
+        <v>930.8836449600001</v>
       </c>
       <c r="F17" t="n">
-        <v>93114.6164159662</v>
+        <v>4492.49493344801</v>
+      </c>
+      <c r="G17" t="n">
+        <v>246290.7587664292</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B18" t="n">
-        <v>1109</v>
+        <v>1613</v>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
-      </c>
-      <c r="D18" t="n">
-        <v>622.07051</v>
+        <v>10</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>DPI64299, DPI66380, DPI64253, DPI66953, DPI66748, DPI64137, DPI66127, DPI66329, DPI65841, DPI64563</t>
+        </is>
       </c>
       <c r="E18" t="n">
-        <v>1605.020479548436</v>
+        <v>905.8948679999999</v>
       </c>
       <c r="F18" t="n">
-        <v>131810.9832575395</v>
+        <v>5638.335582495251</v>
+      </c>
+      <c r="G18" t="n">
+        <v>283885.7904616692</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B19" t="n">
-        <v>1109</v>
+        <v>407</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
-      </c>
-      <c r="D19" t="n">
-        <v>625.68713</v>
+        <v>3</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>DPI64000, DPI63902, DPI66395</t>
+        </is>
       </c>
       <c r="E19" t="n">
-        <v>2781.125920760695</v>
+        <v>328.7647218</v>
       </c>
       <c r="F19" t="n">
-        <v>165306.4662232646</v>
+        <v>1782.570672254706</v>
+      </c>
+      <c r="G19" t="n">
+        <v>123296.4410996451</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B20" t="n">
         <v>1109</v>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
-      </c>
-      <c r="D20" t="n">
-        <v>508.19492965</v>
+        <v>7</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>DPI70166, DPI63929, DPI64001, DPI64118, DPI67138, DPI67002, DPI64644</t>
+        </is>
       </c>
       <c r="E20" t="n">
-        <v>2125.577652669282</v>
+        <v>534.7424360499999</v>
       </c>
       <c r="F20" t="n">
-        <v>146636.4515480211</v>
+        <v>6053.357926000983</v>
+      </c>
+      <c r="G20" t="n">
+        <v>258499.633732508</v>
       </c>
     </row>
     <row r="21">
@@ -845,19 +945,24 @@
         <v>1</v>
       </c>
       <c r="B21" t="n">
-        <v>1109</v>
+        <v>207</v>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
-      </c>
-      <c r="D21" t="n">
-        <v>406.47234</v>
+        <v>1</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>DPI66264</t>
+        </is>
       </c>
       <c r="E21" t="n">
-        <v>1373.26673721151</v>
+        <v>147.74808</v>
       </c>
       <c r="F21" t="n">
-        <v>125210.6366757838</v>
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>64050</v>
       </c>
     </row>
     <row r="22">
@@ -868,16 +973,21 @@
         <v>1109</v>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
-      </c>
-      <c r="D22" t="n">
-        <v>541.37676</v>
+        <v>5</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>DPI64104, DPI64273, DPI66900, DPI66263, DPI64665</t>
+        </is>
       </c>
       <c r="E22" t="n">
-        <v>1844.597415195169</v>
+        <v>602.7557599999999</v>
       </c>
       <c r="F22" t="n">
-        <v>138634.1343847584</v>
+        <v>739.2391510494806</v>
+      </c>
+      <c r="G22" t="n">
+        <v>107153.5310218892</v>
       </c>
     </row>
     <row r="23">
@@ -890,14 +1000,19 @@
       <c r="C23" t="n">
         <v>6</v>
       </c>
-      <c r="D23" t="n">
-        <v>599.5557712</v>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>DPI64502, DPI70120, DPI64758, DPI64179, DPI70197, DPI64651</t>
+        </is>
       </c>
       <c r="E23" t="n">
-        <v>2811.787423768151</v>
+        <v>635.38464</v>
       </c>
       <c r="F23" t="n">
-        <v>166179.7058289169</v>
+        <v>1902.701349962012</v>
+      </c>
+      <c r="G23" t="n">
+        <v>140288.9344469181</v>
       </c>
     </row>
     <row r="24">
@@ -905,19 +1020,24 @@
         <v>1</v>
       </c>
       <c r="B24" t="n">
-        <v>1109</v>
+        <v>207</v>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
-      </c>
-      <c r="D24" t="n">
-        <v>653.94783015</v>
+        <v>2</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>DPI70179, DFT80081</t>
+        </is>
       </c>
       <c r="E24" t="n">
-        <v>3799.382914178938</v>
+        <v>135.78948</v>
       </c>
       <c r="F24" t="n">
-        <v>194306.4253958162</v>
+        <v>794.387011442486</v>
+      </c>
+      <c r="G24" t="n">
+        <v>79898.0208782776</v>
       </c>
     </row>
     <row r="25">
@@ -925,19 +1045,24 @@
         <v>1</v>
       </c>
       <c r="B25" t="n">
-        <v>1109</v>
+        <v>207</v>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
-      </c>
-      <c r="D25" t="n">
-        <v>638.46232</v>
+        <v>2</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>DPI70273, DPI66144</t>
+        </is>
       </c>
       <c r="E25" t="n">
-        <v>2900.62342134365</v>
+        <v>138.78125</v>
       </c>
       <c r="F25" t="n">
-        <v>168709.7550398671</v>
+        <v>796.95215825844</v>
+      </c>
+      <c r="G25" t="n">
+        <v>79949.19555725588</v>
       </c>
     </row>
     <row r="26">
@@ -945,19 +1070,24 @@
         <v>1</v>
       </c>
       <c r="B26" t="n">
-        <v>1109</v>
+        <v>207</v>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
-      </c>
-      <c r="D26" t="n">
-        <v>543.23342</v>
+        <v>1</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>DPI63847</t>
+        </is>
       </c>
       <c r="E26" t="n">
-        <v>2552.914425514512</v>
+        <v>144.26477</v>
       </c>
       <c r="F26" t="n">
-        <v>158807.0028386533</v>
+        <v>399.1664633033907</v>
+      </c>
+      <c r="G26" t="n">
+        <v>72013.37094290265</v>
       </c>
     </row>
     <row r="27">
@@ -965,19 +1095,24 @@
         <v>1</v>
       </c>
       <c r="B27" t="n">
-        <v>1109</v>
+        <v>207</v>
       </c>
       <c r="C27" t="n">
-        <v>6</v>
-      </c>
-      <c r="D27" t="n">
-        <v>644.4797912700001</v>
+        <v>1</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>DPI64696</t>
+        </is>
       </c>
       <c r="E27" t="n">
-        <v>4167.04126890658</v>
+        <v>137.67475</v>
       </c>
       <c r="F27" t="n">
-        <v>204777.3353384594</v>
+        <v>399.1949303881932</v>
+      </c>
+      <c r="G27" t="n">
+        <v>72013.93886124446</v>
       </c>
     </row>
     <row r="28">
@@ -988,16 +1123,21 @@
         <v>1109</v>
       </c>
       <c r="C28" t="n">
-        <v>7</v>
-      </c>
-      <c r="D28" t="n">
-        <v>591.06386</v>
+        <v>6</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>DPI66262, DPI70302, DPI64647, DPI64032, DPI63822, DPI64409</t>
+        </is>
       </c>
       <c r="E28" t="n">
-        <v>5922.502874683351</v>
+        <v>628.25389965</v>
       </c>
       <c r="F28" t="n">
-        <v>254772.8818709819</v>
+        <v>2641.239796112111</v>
+      </c>
+      <c r="G28" t="n">
+        <v>161322.5093932729</v>
       </c>
     </row>
     <row r="29">
@@ -1005,19 +1145,24 @@
         <v>1</v>
       </c>
       <c r="B29" t="n">
-        <v>1109</v>
+        <v>207</v>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
-      </c>
-      <c r="D29" t="n">
-        <v>561.1906619600001</v>
+        <v>1</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>DPI66402</t>
+        </is>
       </c>
       <c r="E29" t="n">
-        <v>4412.000842621217</v>
+        <v>148.73862</v>
       </c>
       <c r="F29" t="n">
-        <v>211753.7839978523</v>
+        <v>458.4096633804866</v>
+      </c>
+      <c r="G29" t="n">
+        <v>73195.27278444071</v>
       </c>
     </row>
     <row r="30">
@@ -1025,19 +1170,24 @@
         <v>1</v>
       </c>
       <c r="B30" t="n">
-        <v>1109</v>
+        <v>407</v>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
-      </c>
-      <c r="D30" t="n">
-        <v>626.27238488</v>
+        <v>2</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>DPI66421, DPI70317</t>
+        </is>
       </c>
       <c r="E30" t="n">
-        <v>4568.523215332823</v>
+        <v>342.41514</v>
       </c>
       <c r="F30" t="n">
-        <v>216211.5411726788</v>
+        <v>918.8254339724073</v>
+      </c>
+      <c r="G30" t="n">
+        <v>101711.4475949705</v>
       </c>
     </row>
     <row r="31">
@@ -1045,239 +1195,299 @@
         <v>1</v>
       </c>
       <c r="B31" t="n">
-        <v>1109</v>
+        <v>407</v>
       </c>
       <c r="C31" t="n">
-        <v>6</v>
-      </c>
-      <c r="D31" t="n">
-        <v>395.19744</v>
+        <v>3</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>DPI67198, DPI66528, DPI64692</t>
+        </is>
       </c>
       <c r="E31" t="n">
-        <v>6750.070927777922</v>
+        <v>332.04138</v>
       </c>
       <c r="F31" t="n">
-        <v>278342.0200231152</v>
+        <v>1390.6651480855</v>
+      </c>
+      <c r="G31" t="n">
+        <v>113502.7220506567</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B32" t="n">
         <v>1109</v>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
-      </c>
-      <c r="D32" t="n">
-        <v>542.04156176</v>
+        <v>7</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>DPI64255, DPI63920, DFT80066, DPI64303, DPI67128, DPI64378, DPI70100</t>
+        </is>
       </c>
       <c r="E32" t="n">
-        <v>444.9330604311851</v>
+        <v>637.5615112</v>
       </c>
       <c r="F32" t="n">
-        <v>98771.69356108016</v>
+        <v>3293.221124108595</v>
+      </c>
+      <c r="G32" t="n">
+        <v>179890.9376146128</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B33" t="n">
-        <v>1109</v>
+        <v>407</v>
       </c>
       <c r="C33" t="n">
-        <v>6</v>
-      </c>
-      <c r="D33" t="n">
-        <v>611.84302913</v>
+        <v>5</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>DPI66659, DFT80087, DFT80034, DPI66092, DPI64476</t>
+        </is>
       </c>
       <c r="E33" t="n">
-        <v>1090.929716489503</v>
+        <v>340.15804015</v>
       </c>
       <c r="F33" t="n">
-        <v>117169.678325621</v>
+        <v>2376.02176481915</v>
+      </c>
+      <c r="G33" t="n">
+        <v>138126.7839028306</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B34" t="n">
-        <v>1109</v>
+        <v>207</v>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
-      </c>
-      <c r="D34" t="n">
-        <v>482.78729866</v>
+        <v>1</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>DPI64559</t>
+        </is>
       </c>
       <c r="E34" t="n">
-        <v>938.1300625069771</v>
+        <v>142.70429</v>
       </c>
       <c r="F34" t="n">
-        <v>112817.9441801987</v>
+        <v>477.0342821566059</v>
+      </c>
+      <c r="G34" t="n">
+        <v>73566.83392902429</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B35" t="n">
-        <v>1109</v>
+        <v>407</v>
       </c>
       <c r="C35" t="n">
-        <v>5</v>
-      </c>
-      <c r="D35" t="n">
-        <v>659.13299252</v>
+        <v>3</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>DPI64484, DPI66327, DPI66508</t>
+        </is>
       </c>
       <c r="E35" t="n">
-        <v>959.983315707277</v>
+        <v>325.10037</v>
       </c>
       <c r="F35" t="n">
-        <v>113440.3248313433</v>
+        <v>1441.264967290876</v>
+      </c>
+      <c r="G35" t="n">
+        <v>114767.211532599</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B36" t="n">
         <v>1109</v>
       </c>
       <c r="C36" t="n">
-        <v>9</v>
-      </c>
-      <c r="D36" t="n">
-        <v>595.25928688</v>
+        <v>5</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>DPI66229, DPI63817, DPI64511, DPI63895, DPI66335</t>
+        </is>
       </c>
       <c r="E36" t="n">
-        <v>2522.615882506675</v>
+        <v>596.84459</v>
       </c>
       <c r="F36" t="n">
-        <v>157944.1003337901</v>
+        <v>2445.138202841616</v>
+      </c>
+      <c r="G36" t="n">
+        <v>155737.5360169293</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B37" t="n">
         <v>1109</v>
       </c>
       <c r="C37" t="n">
-        <v>7</v>
-      </c>
-      <c r="D37" t="n">
-        <v>637.64418718</v>
+        <v>6</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>DPI66646, DPI70002, DPI70106, DPI66175, DPI64639, DPI64746</t>
+        </is>
       </c>
       <c r="E37" t="n">
-        <v>2789.93954307249</v>
+        <v>602.60659127</v>
       </c>
       <c r="F37" t="n">
-        <v>165557.4781867045</v>
+        <v>3443.267343772844</v>
+      </c>
+      <c r="G37" t="n">
+        <v>184164.2539506506</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B38" t="n">
-        <v>1109</v>
+        <v>1613</v>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
-      </c>
-      <c r="D38" t="n">
-        <v>592.0847569699999</v>
+        <v>10</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>DPI70041, DPI66684, DPI67031, DPI64236, DPI67024, DPI64352, DPI66734, DPI64288, DPI70073, DPI64149</t>
+        </is>
       </c>
       <c r="E38" t="n">
-        <v>2466.686961120756</v>
+        <v>892.6878400000002</v>
       </c>
       <c r="F38" t="n">
-        <v>156351.2446527191</v>
+        <v>8213.411476542757</v>
+      </c>
+      <c r="G38" t="n">
+        <v>368374.0305453679</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B39" t="n">
-        <v>1109</v>
+        <v>1613</v>
       </c>
       <c r="C39" t="n">
-        <v>4</v>
-      </c>
-      <c r="D39" t="n">
-        <v>568.3322541699999</v>
+        <v>8</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>DPI70038, DPI66692, DPI64323, DPI64166, DPI66618, DPI66102, DPI66384, DPI64392</t>
+        </is>
       </c>
       <c r="E39" t="n">
-        <v>1664.295868606319</v>
+        <v>921.08777092</v>
       </c>
       <c r="F39" t="n">
-        <v>133499.146337908</v>
+        <v>7143.659197378387</v>
+      </c>
+      <c r="G39" t="n">
+        <v>333275.4582659849</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B40" t="n">
-        <v>1109</v>
+        <v>207</v>
       </c>
       <c r="C40" t="n">
-        <v>8</v>
-      </c>
-      <c r="D40" t="n">
-        <v>591.5600192600001</v>
+        <v>1</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>DPI66408</t>
+        </is>
       </c>
       <c r="E40" t="n">
-        <v>3658.947863844777</v>
+        <v>147.33710398</v>
       </c>
       <c r="F40" t="n">
-        <v>190306.8351622992</v>
+        <v>917.3498458105961</v>
+      </c>
+      <c r="G40" t="n">
+        <v>82351.12942392139</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B41" t="n">
-        <v>1109</v>
+        <v>407</v>
       </c>
       <c r="C41" t="n">
-        <v>5</v>
-      </c>
-      <c r="D41" t="n">
-        <v>641.95727291</v>
+        <v>4</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>DPI64624, DPI66572, DPI64234, DPI64176</t>
+        </is>
       </c>
       <c r="E41" t="n">
-        <v>2839.872890696863</v>
+        <v>320.49699194</v>
       </c>
       <c r="F41" t="n">
-        <v>166979.5799270467</v>
+        <v>4144.464773084959</v>
+      </c>
+      <c r="G41" t="n">
+        <v>182320.1746793931</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B42" t="n">
-        <v>1109</v>
+        <v>407</v>
       </c>
       <c r="C42" t="n">
-        <v>7</v>
-      </c>
-      <c r="D42" t="n">
-        <v>650.1033381000001</v>
+        <v>3</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>DPI66460, DPI63993, DPI64044</t>
+        </is>
       </c>
       <c r="E42" t="n">
-        <v>4756.932804535511</v>
+        <v>193.73862</v>
       </c>
       <c r="F42" t="n">
-        <v>221577.4462731714</v>
+        <v>3525.12116945802</v>
+      </c>
+      <c r="G42" t="n">
+        <v>166842.7780247559</v>
       </c>
     </row>
     <row r="43">
@@ -1285,19 +1495,24 @@
         <v>2</v>
       </c>
       <c r="B43" t="n">
-        <v>1109</v>
+        <v>407</v>
       </c>
       <c r="C43" t="n">
-        <v>5</v>
-      </c>
-      <c r="D43" t="n">
-        <v>608.7976</v>
+        <v>3</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>DPI70142, DPI70109, DPI64052</t>
+        </is>
       </c>
       <c r="E43" t="n">
-        <v>3660.976173975346</v>
+        <v>320.90075138</v>
       </c>
       <c r="F43" t="n">
-        <v>190364.6014348179</v>
+        <v>176.6967455688558</v>
+      </c>
+      <c r="G43" t="n">
+        <v>83165.65167176571</v>
       </c>
     </row>
     <row r="44">
@@ -1305,19 +1520,24 @@
         <v>2</v>
       </c>
       <c r="B44" t="n">
-        <v>1109</v>
+        <v>407</v>
       </c>
       <c r="C44" t="n">
-        <v>6</v>
-      </c>
-      <c r="D44" t="n">
-        <v>630.460695</v>
+        <v>3</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>DPI66179, DPI66597, DPI63958</t>
+        </is>
       </c>
       <c r="E44" t="n">
-        <v>4704.598151748469</v>
+        <v>341.97570951</v>
       </c>
       <c r="F44" t="n">
-        <v>220086.9553617964</v>
+        <v>448.4323666464777</v>
+      </c>
+      <c r="G44" t="n">
+        <v>89956.32484249548</v>
       </c>
     </row>
     <row r="45">
@@ -1325,19 +1545,24 @@
         <v>2</v>
       </c>
       <c r="B45" t="n">
-        <v>1109</v>
+        <v>207</v>
       </c>
       <c r="C45" t="n">
-        <v>8</v>
-      </c>
-      <c r="D45" t="n">
-        <v>626.7582999999998</v>
+        <v>2</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>DPI64638, DPI64218</t>
+        </is>
       </c>
       <c r="E45" t="n">
-        <v>6429.015470152602</v>
+        <v>141.52363</v>
       </c>
       <c r="F45" t="n">
-        <v>269198.3605899461</v>
+        <v>361.3283894734152</v>
+      </c>
+      <c r="G45" t="n">
+        <v>71258.50136999463</v>
       </c>
     </row>
     <row r="46">
@@ -1345,19 +1570,24 @@
         <v>2</v>
       </c>
       <c r="B46" t="n">
-        <v>1109</v>
+        <v>407</v>
       </c>
       <c r="C46" t="n">
-        <v>5</v>
-      </c>
-      <c r="D46" t="n">
-        <v>633.77935</v>
+        <v>3</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>DPI66387, DPI66307, DPI66039</t>
+        </is>
       </c>
       <c r="E46" t="n">
-        <v>4148.256991006207</v>
+        <v>349.4845</v>
       </c>
       <c r="F46" t="n">
-        <v>204242.3591038568</v>
+        <v>549.4052752319394</v>
+      </c>
+      <c r="G46" t="n">
+        <v>92479.63782804616</v>
       </c>
     </row>
     <row r="47">
@@ -1365,19 +1595,24 @@
         <v>2</v>
       </c>
       <c r="B47" t="n">
-        <v>1109</v>
+        <v>1613</v>
       </c>
       <c r="C47" t="n">
-        <v>5</v>
-      </c>
-      <c r="D47" t="n">
-        <v>605.0483</v>
+        <v>8</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>DPI67121, DPI66289, DPI64039, DPI64301, DPI66339, DPI66203, DPI64450, DPI66069</t>
+        </is>
       </c>
       <c r="E47" t="n">
-        <v>4870.382323990115</v>
+        <v>902.05745714</v>
       </c>
       <c r="F47" t="n">
-        <v>224808.4885872385</v>
+        <v>1506.817140437383</v>
+      </c>
+      <c r="G47" t="n">
+        <v>148330.6703777505</v>
       </c>
     </row>
     <row r="48">
@@ -1388,16 +1623,21 @@
         <v>1109</v>
       </c>
       <c r="C48" t="n">
-        <v>6</v>
-      </c>
-      <c r="D48" t="n">
-        <v>649.77431</v>
+        <v>9</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>DPI64686, DPI66590, DPI70316, DFT80044, DPI64216, DFT80088, DPI70255, DPI70009, DPI66923</t>
+        </is>
       </c>
       <c r="E48" t="n">
-        <v>6757.117384537068</v>
+        <v>621.71592092</v>
       </c>
       <c r="F48" t="n">
-        <v>278542.7031116157</v>
+        <v>2149.913702733013</v>
+      </c>
+      <c r="G48" t="n">
+        <v>147329.5422538362</v>
       </c>
     </row>
     <row r="49">
@@ -1408,181 +1648,226 @@
         <v>1109</v>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
-      </c>
-      <c r="D49" t="n">
-        <v>312.29982</v>
+        <v>6</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>DPI64480, DPI66078, DPI64433, DPI66658, DPI67187, DPI66221</t>
+        </is>
       </c>
       <c r="E49" t="n">
-        <v>3623.585321416223</v>
+        <v>598.1027300000001</v>
       </c>
       <c r="F49" t="n">
-        <v>189299.709953934</v>
+        <v>2337.5389221152</v>
+      </c>
+      <c r="G49" t="n">
+        <v>152673.1085018409</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B50" t="n">
-        <v>1109</v>
+        <v>1613</v>
       </c>
       <c r="C50" t="n">
-        <v>6</v>
-      </c>
-      <c r="D50" t="n">
-        <v>544.45234078</v>
+        <v>10</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>DPI70105, DPI66373, DPI64196, DPI66653, DPI66645, DPI66154, DPI63827, DPI66153, DPI70081, DPI67072</t>
+        </is>
       </c>
       <c r="E50" t="n">
-        <v>620.6707878959645</v>
+        <v>971.88974101</v>
       </c>
       <c r="F50" t="n">
-        <v>103776.7040392771</v>
+        <v>4096.684966185147</v>
+      </c>
+      <c r="G50" t="n">
+        <v>233304.2337405347</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B51" t="n">
-        <v>1109</v>
+        <v>407</v>
       </c>
       <c r="C51" t="n">
-        <v>5</v>
-      </c>
-      <c r="D51" t="n">
-        <v>615.84392637</v>
+        <v>2</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>DPI66313, DPI66449</t>
+        </is>
       </c>
       <c r="E51" t="n">
-        <v>1072.664380963965</v>
+        <v>315.86378731</v>
       </c>
       <c r="F51" t="n">
-        <v>116649.4815698537</v>
+        <v>833.0782276266925</v>
+      </c>
+      <c r="G51" t="n">
+        <v>99568.62490839104</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B52" t="n">
-        <v>1109</v>
+        <v>407</v>
       </c>
       <c r="C52" t="n">
-        <v>6</v>
-      </c>
-      <c r="D52" t="n">
-        <v>614.19161563</v>
+        <v>3</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>DPI66576, DPI63919, DPI64592</t>
+        </is>
       </c>
       <c r="E52" t="n">
-        <v>1360.675478797181</v>
+        <v>330.8032</v>
       </c>
       <c r="F52" t="n">
-        <v>124852.0376361437</v>
+        <v>1268.125198302735</v>
+      </c>
+      <c r="G52" t="n">
+        <v>110440.4487055854</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B53" t="n">
-        <v>1109</v>
+        <v>1613</v>
       </c>
       <c r="C53" t="n">
-        <v>7</v>
-      </c>
-      <c r="D53" t="n">
-        <v>646.7075726099998</v>
+        <v>10</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>DPI66636, DFT80077, DFT80078, DPI64136, DPI64431, DPI64413, DPI64244, DPI64094, DPI66128, DPI66715</t>
+        </is>
       </c>
       <c r="E53" t="n">
-        <v>1643.450991809727</v>
+        <v>941.4133046699999</v>
       </c>
       <c r="F53" t="n">
-        <v>132905.484246741</v>
+        <v>5020.143212902989</v>
+      </c>
+      <c r="G53" t="n">
+        <v>263602.8988153471</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B54" t="n">
-        <v>1109</v>
+        <v>407</v>
       </c>
       <c r="C54" t="n">
-        <v>6</v>
-      </c>
-      <c r="D54" t="n">
-        <v>635.65504634</v>
+        <v>4</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>DPI64436, DPI64119, DPI70096, DPI64666</t>
+        </is>
       </c>
       <c r="E54" t="n">
-        <v>1447.811845777364</v>
+        <v>331.5481275000001</v>
       </c>
       <c r="F54" t="n">
-        <v>127333.6813677393</v>
+        <v>2641.374991257408</v>
+      </c>
+      <c r="G54" t="n">
+        <v>144757.9610315226</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B55" t="n">
-        <v>1109</v>
+        <v>407</v>
       </c>
       <c r="C55" t="n">
-        <v>6</v>
-      </c>
-      <c r="D55" t="n">
-        <v>591.30277859</v>
+        <v>3</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>DPI70047, DPI66679, DPI66209</t>
+        </is>
       </c>
       <c r="E55" t="n">
-        <v>1474.774964358996</v>
+        <v>345.1143381000001</v>
       </c>
       <c r="F55" t="n">
-        <v>128101.5909849442</v>
+        <v>2053.462139596656</v>
+      </c>
+      <c r="G55" t="n">
+        <v>130066.0188685204</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B56" t="n">
-        <v>1109</v>
+        <v>207</v>
       </c>
       <c r="C56" t="n">
-        <v>6</v>
-      </c>
-      <c r="D56" t="n">
-        <v>627.94332129</v>
+        <v>2</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>DPI70190, DPI67224</t>
+        </is>
       </c>
       <c r="E56" t="n">
-        <v>1507.026864145879</v>
+        <v>146.0747</v>
       </c>
       <c r="F56" t="n">
-        <v>129020.1250908746</v>
+        <v>1388.894523206169</v>
+      </c>
+      <c r="G56" t="n">
+        <v>91758.44573796308</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B57" t="n">
         <v>1109</v>
       </c>
       <c r="C57" t="n">
-        <v>6</v>
-      </c>
-      <c r="D57" t="n">
-        <v>651.97662963</v>
+        <v>5</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>DPI64634, DPI67148, DPI64742, DPI63976, DPI64456</t>
+        </is>
       </c>
       <c r="E57" t="n">
-        <v>1533.198288298764</v>
+        <v>634.3604575000001</v>
       </c>
       <c r="F57" t="n">
-        <v>129765.4872507488</v>
+        <v>3732.276882797153</v>
+      </c>
+      <c r="G57" t="n">
+        <v>192395.2456220629</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B58" t="n">
         <v>1109</v>
@@ -1590,59 +1875,74 @@
       <c r="C58" t="n">
         <v>6</v>
       </c>
-      <c r="D58" t="n">
-        <v>626.1952616399999</v>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>DPI66574, DPI66946, DPI64169, DPI64628, DPI64056, DPI67074</t>
+        </is>
       </c>
       <c r="E58" t="n">
-        <v>1550.226766295313</v>
+        <v>634.7518375000001</v>
       </c>
       <c r="F58" t="n">
-        <v>130250.4583040905</v>
+        <v>4729.782125555788</v>
+      </c>
+      <c r="G58" t="n">
+        <v>220804.1949358289</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B59" t="n">
         <v>1109</v>
       </c>
       <c r="C59" t="n">
-        <v>7</v>
-      </c>
-      <c r="D59" t="n">
-        <v>633.8066488400001</v>
+        <v>8</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>DPI66172, DPI64057, DPI66051, DPI63802, DPI64037, DPI70253, DPI70213, DPI66067</t>
+        </is>
       </c>
       <c r="E59" t="n">
-        <v>1834.740419074528</v>
+        <v>650.4852999999999</v>
       </c>
       <c r="F59" t="n">
-        <v>138353.4071352425</v>
+        <v>6459.321119963359</v>
+      </c>
+      <c r="G59" t="n">
+        <v>270061.4654965565</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B60" t="n">
         <v>1109</v>
       </c>
       <c r="C60" t="n">
-        <v>6</v>
-      </c>
-      <c r="D60" t="n">
-        <v>561.9605617</v>
+        <v>5</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>DPI66742, DPI67178, DPI64297, DPI64724, DPI63915</t>
+        </is>
       </c>
       <c r="E60" t="n">
-        <v>1597.26484478381</v>
+        <v>626.19535</v>
       </c>
       <c r="F60" t="n">
-        <v>131590.1027794429</v>
+        <v>4162.18445493579</v>
+      </c>
+      <c r="G60" t="n">
+        <v>204639.0132765713</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B61" t="n">
         <v>1109</v>
@@ -1650,54 +1950,69 @@
       <c r="C61" t="n">
         <v>6</v>
       </c>
-      <c r="D61" t="n">
-        <v>573.73844528</v>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>DPI67180, DPI70296, DPI66096, DPI64018, DPI66634, DPI70214</t>
+        </is>
       </c>
       <c r="E61" t="n">
-        <v>1613.934592898211</v>
+        <v>631.91267</v>
       </c>
       <c r="F61" t="n">
-        <v>132064.857205741</v>
+        <v>6251.338632338227</v>
+      </c>
+      <c r="G61" t="n">
+        <v>264138.1242489927</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B62" t="n">
         <v>1109</v>
       </c>
       <c r="C62" t="n">
-        <v>6</v>
-      </c>
-      <c r="D62" t="n">
-        <v>644.29095512</v>
+        <v>5</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>DPI64495, DPI66129, DFT80080, DPI70229, DPI66736</t>
+        </is>
       </c>
       <c r="E62" t="n">
-        <v>1627.349429055388</v>
+        <v>627.55891</v>
       </c>
       <c r="F62" t="n">
-        <v>132446.9117394974</v>
+        <v>5715.227117645433</v>
+      </c>
+      <c r="G62" t="n">
+        <v>248869.668310542</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B63" t="n">
-        <v>1109</v>
+        <v>407</v>
       </c>
       <c r="C63" t="n">
-        <v>5</v>
-      </c>
-      <c r="D63" t="n">
-        <v>613.5520235</v>
+        <v>2</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>DPI70107, DPI64548</t>
+        </is>
       </c>
       <c r="E63" t="n">
-        <v>1370.90626015478</v>
+        <v>175.93195</v>
       </c>
       <c r="F63" t="n">
-        <v>125143.4102892081</v>
+        <v>2445.173651824534</v>
+      </c>
+      <c r="G63" t="n">
+        <v>139854.8895590951</v>
       </c>
     </row>
     <row r="64">
@@ -1705,19 +2020,24 @@
         <v>3</v>
       </c>
       <c r="B64" t="n">
-        <v>1109</v>
+        <v>407</v>
       </c>
       <c r="C64" t="n">
-        <v>5</v>
-      </c>
-      <c r="D64" t="n">
-        <v>600.58108141</v>
+        <v>3</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>DPI66929, DPI66437, DPI64600</t>
+        </is>
       </c>
       <c r="E64" t="n">
-        <v>1389.366175505938</v>
+        <v>336.06904157</v>
       </c>
       <c r="F64" t="n">
-        <v>125669.1486784091</v>
+        <v>45.88063523883613</v>
+      </c>
+      <c r="G64" t="n">
+        <v>79896.55707461851</v>
       </c>
     </row>
     <row r="65">
@@ -1725,19 +2045,24 @@
         <v>3</v>
       </c>
       <c r="B65" t="n">
-        <v>1109</v>
+        <v>207</v>
       </c>
       <c r="C65" t="n">
-        <v>6</v>
-      </c>
-      <c r="D65" t="n">
-        <v>621.47575249</v>
+        <v>2</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>DPI64377, DPI66626</t>
+        </is>
       </c>
       <c r="E65" t="n">
-        <v>1718.640429117111</v>
+        <v>142.07492374</v>
       </c>
       <c r="F65" t="n">
-        <v>135046.8794212553</v>
+        <v>369.7925494388147</v>
+      </c>
+      <c r="G65" t="n">
+        <v>71427.36136130436</v>
       </c>
     </row>
     <row r="66">
@@ -1745,19 +2070,24 @@
         <v>3</v>
       </c>
       <c r="B66" t="n">
-        <v>1109</v>
+        <v>1613</v>
       </c>
       <c r="C66" t="n">
-        <v>8</v>
-      </c>
-      <c r="D66" t="n">
-        <v>579.54584497</v>
+        <v>9</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>DPI70176, DPI66578, DPI66573, DPI63823, DPI67042, DPI66998, DPI70057, DPI66386, DPI67110</t>
+        </is>
       </c>
       <c r="E66" t="n">
-        <v>3226.450659869074</v>
+        <v>939.6523527100001</v>
       </c>
       <c r="F66" t="n">
-        <v>177989.3147930712</v>
+        <v>1949.101653238935</v>
+      </c>
+      <c r="G66" t="n">
+        <v>162842.0252427695</v>
       </c>
     </row>
     <row r="67">
@@ -1765,19 +2095,24 @@
         <v>3</v>
       </c>
       <c r="B67" t="n">
-        <v>1109</v>
+        <v>1613</v>
       </c>
       <c r="C67" t="n">
-        <v>7</v>
-      </c>
-      <c r="D67" t="n">
-        <v>641.80445808</v>
+        <v>9</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>DPI70140, DPI66685, DPI66378, DPI66053, DPI67064, DPI67179, DPI66241, DPI66094, DPI70216</t>
+        </is>
       </c>
       <c r="E67" t="n">
-        <v>4315.816826171716</v>
+        <v>921.88629411</v>
       </c>
       <c r="F67" t="n">
-        <v>209014.4632093704</v>
+        <v>2093.76531224934</v>
+      </c>
+      <c r="G67" t="n">
+        <v>167588.4398949009</v>
       </c>
     </row>
     <row r="68">
@@ -1788,16 +2123,21 @@
         <v>1109</v>
       </c>
       <c r="C68" t="n">
-        <v>12</v>
-      </c>
-      <c r="D68" t="n">
-        <v>562.34070482</v>
+        <v>6</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>DPI70091, DPI66076, DPI66619, DPI64577, DPI66191, DPI66522</t>
+        </is>
       </c>
       <c r="E68" t="n">
-        <v>9994.184119313983</v>
+        <v>624.9482230900001</v>
       </c>
       <c r="F68" t="n">
-        <v>370734.3637180622</v>
+        <v>1443.523097806382</v>
+      </c>
+      <c r="G68" t="n">
+        <v>127211.5378255258</v>
       </c>
     </row>
     <row r="69">
@@ -1805,19 +2145,24 @@
         <v>3</v>
       </c>
       <c r="B69" t="n">
-        <v>1109</v>
+        <v>1613</v>
       </c>
       <c r="C69" t="n">
-        <v>8</v>
-      </c>
-      <c r="D69" t="n">
-        <v>612.18888426</v>
+        <v>9</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>DPI66194, DFT80095, DPI70320, DPI64331, DPI64520, DPI66660, DPI66400, DPI67217, DPI65919</t>
+        </is>
       </c>
       <c r="E69" t="n">
-        <v>6990.112657892177</v>
+        <v>953.4635650600001</v>
       </c>
       <c r="F69" t="n">
-        <v>285178.4084967692</v>
+        <v>2214.149932842416</v>
+      </c>
+      <c r="G69" t="n">
+        <v>171538.2592965597</v>
       </c>
     </row>
     <row r="70">
@@ -1825,19 +2170,24 @@
         <v>3</v>
       </c>
       <c r="B70" t="n">
-        <v>1109</v>
+        <v>1613</v>
       </c>
       <c r="C70" t="n">
-        <v>13</v>
-      </c>
-      <c r="D70" t="n">
-        <v>653.35869202</v>
+        <v>9</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>DPI66377, DPI66688, DPI64631, DPI66621, DPI64650, DPI66521, DPI66359, DPI70104, DPI66755</t>
+        </is>
       </c>
       <c r="E70" t="n">
-        <v>11666.99568309908</v>
+        <v>894.22743988</v>
       </c>
       <c r="F70" t="n">
-        <v>418376.0370546618</v>
+        <v>2287.509704000288</v>
+      </c>
+      <c r="G70" t="n">
+        <v>173945.1933882495</v>
       </c>
     </row>
     <row r="71">
@@ -1848,16 +2198,21 @@
         <v>1109</v>
       </c>
       <c r="C71" t="n">
-        <v>10</v>
-      </c>
-      <c r="D71" t="n">
-        <v>650.6067225500001</v>
+        <v>6</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>DPI66042, DPI66126, DPI64019, DPI65789, DPI63950, DPI65840</t>
+        </is>
       </c>
       <c r="E71" t="n">
-        <v>9855.013699219391</v>
+        <v>651.1897926199999</v>
       </c>
       <c r="F71" t="n">
-        <v>366770.7901537683</v>
+        <v>1546.206326110544</v>
+      </c>
+      <c r="G71" t="n">
+        <v>130135.9561676283</v>
       </c>
     </row>
     <row r="72">
@@ -1865,359 +2220,874 @@
         <v>3</v>
       </c>
       <c r="B72" t="n">
-        <v>1109</v>
+        <v>407</v>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
-      </c>
-      <c r="D72" t="n">
-        <v>73.27007999999999</v>
+        <v>3</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>DPI63951, DPI66422, DPI66014</t>
+        </is>
       </c>
       <c r="E72" t="n">
-        <v>1029.534169042662</v>
+        <v>330.00319794</v>
       </c>
       <c r="F72" t="n">
-        <v>115421.133134335</v>
+        <v>782.3167326506256</v>
+      </c>
+      <c r="G72" t="n">
+        <v>98300.09514893913</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B73" t="n">
-        <v>1109</v>
+        <v>207</v>
       </c>
       <c r="C73" t="n">
-        <v>7</v>
-      </c>
-      <c r="D73" t="n">
-        <v>626.9946460000001</v>
+        <v>2</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>DPI64026, DPI66389</t>
+        </is>
       </c>
       <c r="E73" t="n">
-        <v>953.9992158911998</v>
+        <v>145.55047117</v>
       </c>
       <c r="F73" t="n">
-        <v>113269.8976685814</v>
+        <v>523.4193225885434</v>
+      </c>
+      <c r="G73" t="n">
+        <v>74492.21548564144</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
+        <v>3</v>
+      </c>
+      <c r="B74" t="n">
+        <v>407</v>
+      </c>
+      <c r="C74" t="n">
         <v>4</v>
       </c>
-      <c r="B74" t="n">
-        <v>1109</v>
-      </c>
-      <c r="C74" t="n">
-        <v>7</v>
-      </c>
-      <c r="D74" t="n">
-        <v>578.762444</v>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>DPI66136, DPI66410, DPI65969, DPI64250</t>
+        </is>
       </c>
       <c r="E74" t="n">
-        <v>1318.716439259287</v>
+        <v>336.6333720600001</v>
       </c>
       <c r="F74" t="n">
-        <v>123657.0441901045</v>
+        <v>1054.689053600161</v>
+      </c>
+      <c r="G74" t="n">
+        <v>105106.679449468</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B75" t="n">
-        <v>1109</v>
+        <v>407</v>
       </c>
       <c r="C75" t="n">
         <v>3</v>
       </c>
-      <c r="D75" t="n">
-        <v>567.4541654999999</v>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>DPI66501, DPI64470, DPI65993</t>
+        </is>
       </c>
       <c r="E75" t="n">
-        <v>579.9460322577389</v>
+        <v>323.65744947</v>
       </c>
       <c r="F75" t="n">
-        <v>102616.8629987004</v>
+        <v>798.5381956920228</v>
+      </c>
+      <c r="G75" t="n">
+        <v>98705.46951034365</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B76" t="n">
-        <v>1109</v>
+        <v>407</v>
       </c>
       <c r="C76" t="n">
-        <v>6</v>
-      </c>
-      <c r="D76" t="n">
-        <v>656.5918285</v>
+        <v>3</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>DPI70148, DPI65915, DPI65779</t>
+        </is>
       </c>
       <c r="E76" t="n">
-        <v>1265.928559261617</v>
+        <v>321.93852002</v>
       </c>
       <c r="F76" t="n">
-        <v>122153.6453677709</v>
+        <v>801.0144191108886</v>
+      </c>
+      <c r="G76" t="n">
+        <v>98767.35033358111</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B77" t="n">
-        <v>1109</v>
+        <v>207</v>
       </c>
       <c r="C77" t="n">
-        <v>6</v>
-      </c>
-      <c r="D77" t="n">
-        <v>514.6383</v>
+        <v>1</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>DPI66280</t>
+        </is>
       </c>
       <c r="E77" t="n">
-        <v>3642.093172157054</v>
+        <v>139.22461155</v>
       </c>
       <c r="F77" t="n">
-        <v>189826.8135430329</v>
+        <v>268.7863980540556</v>
+      </c>
+      <c r="G77" t="n">
+        <v>69412.28864117841</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B78" t="n">
-        <v>1109</v>
+        <v>207</v>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
-      </c>
-      <c r="D78" t="n">
-        <v>995.3472000000002</v>
+        <v>2</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>DPI67118, DPI70069</t>
+        </is>
       </c>
       <c r="E78" t="n">
-        <v>780.3195097475926</v>
+        <v>140.82943761</v>
       </c>
       <c r="F78" t="n">
-        <v>108323.4996376114</v>
+        <v>538.6124259579057</v>
+      </c>
+      <c r="G78" t="n">
+        <v>74795.31789786022</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B79" t="n">
-        <v>1109</v>
+        <v>1613</v>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
-      </c>
-      <c r="D79" t="n">
-        <v>106.680992</v>
+        <v>9</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>DPI64602, DPI67183, DPI67126, DPI66538, DPI67021, DPI65877, DPI67014, DPI70261, DPI65998</t>
+        </is>
       </c>
       <c r="E79" t="n">
-        <v>938.8964782102512</v>
+        <v>918.58840689</v>
       </c>
       <c r="F79" t="n">
-        <v>112839.7716994279</v>
+        <v>2439.226724571303</v>
+      </c>
+      <c r="G79" t="n">
+        <v>178923.0288331844</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B80" t="n">
         <v>1109</v>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
-      </c>
-      <c r="D80" t="n">
-        <v>898.0380000000002</v>
+        <v>6</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>DPI66970, DPI64240, DPI64140, DPI66622, DPI66926, DPI64207</t>
+        </is>
       </c>
       <c r="E80" t="n">
-        <v>964.0147164099201</v>
+        <v>635.77834015</v>
       </c>
       <c r="F80" t="n">
-        <v>113555.1391233545</v>
+        <v>1649.271304550981</v>
+      </c>
+      <c r="G80" t="n">
+        <v>133071.246753612</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B81" t="n">
-        <v>1109</v>
+        <v>207</v>
       </c>
       <c r="C81" t="n">
-        <v>2</v>
-      </c>
-      <c r="D81" t="n">
-        <v>585.0013999999999</v>
+        <v>1</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>DPI64227</t>
+        </is>
       </c>
       <c r="E81" t="n">
-        <v>1982.759633426955</v>
+        <v>137.7462625</v>
       </c>
       <c r="F81" t="n">
-        <v>142568.9943599997</v>
+        <v>278.6798782223319</v>
+      </c>
+      <c r="G81" t="n">
+        <v>69609.66357053551</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B82" t="n">
         <v>1109</v>
       </c>
       <c r="C82" t="n">
-        <v>3</v>
-      </c>
-      <c r="D82" t="n">
-        <v>608.2781</v>
+        <v>5</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>DPI66333, DPI66031, DPI66733, DPI67181, DPI64408</t>
+        </is>
       </c>
       <c r="E82" t="n">
-        <v>3096.360824950401</v>
+        <v>635.58432131</v>
       </c>
       <c r="F82" t="n">
-        <v>174284.3562945874</v>
+        <v>1407.785459025591</v>
+      </c>
+      <c r="G82" t="n">
+        <v>126193.7298730488</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B83" t="n">
         <v>1109</v>
       </c>
       <c r="C83" t="n">
-        <v>4</v>
-      </c>
-      <c r="D83" t="n">
-        <v>531.191197</v>
+        <v>7</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>DPI64752, DPI70306, DPI64469, DPI63978, DPI67093, DPI70256, DPI64043</t>
+        </is>
       </c>
       <c r="E83" t="n">
-        <v>4577.142713582805</v>
+        <v>631.6363794299999</v>
       </c>
       <c r="F83" t="n">
-        <v>216457.0244828383</v>
+        <v>2137.719327548343</v>
+      </c>
+      <c r="G83" t="n">
+        <v>146982.2464485768</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B84" t="n">
-        <v>1109</v>
+        <v>407</v>
       </c>
       <c r="C84" t="n">
         <v>5</v>
       </c>
-      <c r="D84" t="n">
-        <v>489.2667653</v>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>DPI64720, DPI64741, DPI64279, DPI64073, DPI66548</t>
+        </is>
       </c>
       <c r="E84" t="n">
-        <v>36.55878538166268</v>
+        <v>317.3867891</v>
       </c>
       <c r="F84" t="n">
-        <v>87141.19420766976</v>
+        <v>2520.053067953841</v>
+      </c>
+      <c r="G84" t="n">
+        <v>141726.1261681665</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B85" t="n">
         <v>1109</v>
       </c>
       <c r="C85" t="n">
-        <v>4</v>
-      </c>
-      <c r="D85" t="n">
-        <v>648.3898508</v>
+        <v>7</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>DPI64203, DPI66119, DPI67050, DPI66224, DPI70058, DPI66945, DPI64428</t>
+        </is>
       </c>
       <c r="E85" t="n">
-        <v>78.40931508301942</v>
+        <v>640.75966165</v>
       </c>
       <c r="F85" t="n">
-        <v>88333.09729356439</v>
+        <v>4539.216716455613</v>
+      </c>
+      <c r="G85" t="n">
+        <v>215376.8920846559</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B86" t="n">
-        <v>1109</v>
+        <v>207</v>
       </c>
       <c r="C86" t="n">
-        <v>6</v>
-      </c>
-      <c r="D86" t="n">
-        <v>569.4190411999999</v>
+        <v>4</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>DPI64083, DPI64310, DPI64317, DPI70039</t>
+        </is>
       </c>
       <c r="E86" t="n">
-        <v>210.795346137534</v>
+        <v>140.84405604</v>
       </c>
       <c r="F86" t="n">
-        <v>92103.45145799697</v>
+        <v>3277.775543054072</v>
+      </c>
+      <c r="G86" t="n">
+        <v>129441.6220839287</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B87" t="n">
-        <v>1109</v>
+        <v>407</v>
       </c>
       <c r="C87" t="n">
-        <v>5</v>
-      </c>
-      <c r="D87" t="n">
-        <v>613.33671866</v>
+        <v>7</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>DPI63813, DPI66239, DPI66940, DPI66591, DPI66944, DFT80058, DPI66640</t>
+        </is>
       </c>
       <c r="E87" t="n">
-        <v>796.74944379109</v>
+        <v>327.69205942</v>
       </c>
       <c r="F87" t="n">
-        <v>108791.4241591702</v>
+        <v>5932.120344325858</v>
+      </c>
+      <c r="G87" t="n">
+        <v>226993.6874047032</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B88" t="n">
         <v>1109</v>
       </c>
       <c r="C88" t="n">
-        <v>6</v>
-      </c>
-      <c r="D88" t="n">
-        <v>602.2002538199999</v>
+        <v>8</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>DPI64252, DPI67062, DPI70032, DPI66532, DPI64145, DPI70022, DPI66125, DPI66497</t>
+        </is>
       </c>
       <c r="E88" t="n">
-        <v>2604.326206063504</v>
+        <v>612.18888426</v>
       </c>
       <c r="F88" t="n">
-        <v>160271.2103486886</v>
+        <v>6990.112657892177</v>
+      </c>
+      <c r="G88" t="n">
+        <v>285178.4084967692</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
+        <v>3</v>
+      </c>
+      <c r="B89" t="n">
+        <v>407</v>
+      </c>
+      <c r="C89" t="n">
+        <v>7</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>DPI66730, DPI64525, DPI64102, DPI66999, DPI66029, DPI64336, DPI66104</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>342.83971353</v>
+      </c>
+      <c r="F89" t="n">
+        <v>6181.368542405836</v>
+      </c>
+      <c r="G89" t="n">
+        <v>233222.3998747218</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>3</v>
+      </c>
+      <c r="B90" t="n">
+        <v>1109</v>
+      </c>
+      <c r="C90" t="n">
+        <v>11</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>DPI64291, DPI64237, DPI64641, DPI63999, DPI64079, DPI64703, DPI66652, DPI64418, DPI66122, DPI66326, DPI63945</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>626.18171139</v>
+      </c>
+      <c r="F90" t="n">
+        <v>10391.33379473243</v>
+      </c>
+      <c r="G90" t="n">
+        <v>382045.1864739796</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>3</v>
+      </c>
+      <c r="B91" t="n">
+        <v>207</v>
+      </c>
+      <c r="C91" t="n">
+        <v>2</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>DPI66729, DPI64350</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>149.24456164</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1976.713766983252</v>
+      </c>
+      <c r="G91" t="n">
+        <v>103485.4396513159</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>3</v>
+      </c>
+      <c r="B92" t="n">
+        <v>407</v>
+      </c>
+      <c r="C92" t="n">
+        <v>4</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>DPI63936, DPI64706, DPI64246, DPI64106</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>258.96950801</v>
+      </c>
+      <c r="F92" t="n">
+        <v>4002.127447239615</v>
+      </c>
+      <c r="G92" t="n">
+        <v>178763.164906518</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>4</v>
+      </c>
+      <c r="B93" t="n">
+        <v>1109</v>
+      </c>
+      <c r="C93" t="n">
+        <v>7</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>DPI67040, DFT80016, DPI63872, DPI66487, DPI64235, DPI63862, DPI66035</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>626.9946460000001</v>
+      </c>
+      <c r="F93" t="n">
+        <v>953.9992158911998</v>
+      </c>
+      <c r="G93" t="n">
+        <v>113269.8976685814</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>4</v>
+      </c>
+      <c r="B94" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C94" t="n">
+        <v>9</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>DPI70051, DPI64424, DPI64594, DFT80025, DPI67069, DPI66008, DPI64181, DPI66507, DPI64190</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>902.4486694999999</v>
+      </c>
+      <c r="F94" t="n">
+        <v>1704.113917754574</v>
+      </c>
+      <c r="G94" t="n">
+        <v>154803.9776415276</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>4</v>
+      </c>
+      <c r="B95" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C95" t="n">
+        <v>7</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>DPI66463, DPI66332, DPI70014, DPI64040, DPI70126, DPI64717, DPI66290</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>900.3597684999999</v>
+      </c>
+      <c r="F95" t="n">
+        <v>1460.477113024069</v>
+      </c>
+      <c r="G95" t="n">
+        <v>146810.2540783197</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>4</v>
+      </c>
+      <c r="B96" t="n">
+        <v>407</v>
+      </c>
+      <c r="C96" t="n">
+        <v>3</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>DPI70129, DPI63871, DPI64610</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>321.0171</v>
+      </c>
+      <c r="F96" t="n">
+        <v>1331.431670715557</v>
+      </c>
+      <c r="G96" t="n">
+        <v>112022.4774511818</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>4</v>
+      </c>
+      <c r="B97" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C97" t="n">
+        <v>4</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>DPI67252, DFT80069, DPI67235, DPI64205</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>1188.9684</v>
+      </c>
+      <c r="F97" t="n">
+        <v>3090.98101118909</v>
+      </c>
+      <c r="G97" t="n">
+        <v>200307.086977114</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>4</v>
+      </c>
+      <c r="B98" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C98" t="n">
+        <v>2</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>DPI70321, DPI63834</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>1004.718992</v>
+      </c>
+      <c r="F98" t="n">
+        <v>1902.911194620171</v>
+      </c>
+      <c r="G98" t="n">
+        <v>161326.5162954878</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>4</v>
+      </c>
+      <c r="B99" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C99" t="n">
+        <v>4</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>DPI63843, DPI63905, DPI64204, DPI70182</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>1097.6534</v>
+      </c>
+      <c r="F99" t="n">
+        <v>4034.7875945488</v>
+      </c>
+      <c r="G99" t="n">
+        <v>231273.3809771462</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>4</v>
+      </c>
+      <c r="B100" t="n">
+        <v>1109</v>
+      </c>
+      <c r="C100" t="n">
         <v>5</v>
       </c>
-      <c r="B89" t="n">
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>DPI64084, DPI66904, DPI64030, DPI64349, DPI64286</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>626.8172970000001</v>
+      </c>
+      <c r="F100" t="n">
+        <v>5621.475577411361</v>
+      </c>
+      <c r="G100" t="n">
+        <v>246199.6244446756</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>5</v>
+      </c>
+      <c r="B101" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C101" t="n">
+        <v>8</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>DPI70309, DPI67135, DPI70018, DPI70242, DPI64549, DPI66441, DPI65995, DPI66445</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>1009.0595105</v>
+      </c>
+      <c r="F101" t="n">
+        <v>91.73551571635204</v>
+      </c>
+      <c r="G101" t="n">
+        <v>101901.8422706535</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>5</v>
+      </c>
+      <c r="B102" t="n">
         <v>1109</v>
       </c>
-      <c r="C89" t="n">
-        <v>3</v>
-      </c>
-      <c r="D89" t="n">
-        <v>302.5549763</v>
-      </c>
-      <c r="E89" t="n">
-        <v>2833.354037567163</v>
-      </c>
-      <c r="F89" t="n">
-        <v>166793.9229899128</v>
+      <c r="C102" t="n">
+        <v>6</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>DPI64683, DPI64122, DPI70144, DPI64494, DPI70323, DPI67086</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>651.2168534</v>
+      </c>
+      <c r="F102" t="n">
+        <v>158.193720352646</v>
+      </c>
+      <c r="G102" t="n">
+        <v>90605.35715564336</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>5</v>
+      </c>
+      <c r="B103" t="n">
+        <v>407</v>
+      </c>
+      <c r="C103" t="n">
+        <v>3</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>DPI64434, DPI66500, DPI64005</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>343.41081056</v>
+      </c>
+      <c r="F103" t="n">
+        <v>230.9984849200232</v>
+      </c>
+      <c r="G103" t="n">
+        <v>84522.65213815137</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>5</v>
+      </c>
+      <c r="B104" t="n">
+        <v>207</v>
+      </c>
+      <c r="C104" t="n">
+        <v>1</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>DPI64448</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>135.638204</v>
+      </c>
+      <c r="F104" t="n">
+        <v>85.33204615383583</v>
+      </c>
+      <c r="G104" t="n">
+        <v>65752.37432076903</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>5</v>
+      </c>
+      <c r="B105" t="n">
+        <v>1109</v>
+      </c>
+      <c r="C105" t="n">
+        <v>7</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>DPI64702, DPI64390, DPI64654, DPI64629, DPI70303, DPI70186, DPI64737</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>613.14582532</v>
+      </c>
+      <c r="F105" t="n">
+        <v>2521.471546397088</v>
+      </c>
+      <c r="G105" t="n">
+        <v>157911.5096413891</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>5</v>
+      </c>
+      <c r="B106" t="n">
+        <v>1109</v>
+      </c>
+      <c r="C106" t="n">
+        <v>4</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>DPI66620, DPI64226, DPI66927, DPI64655</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>472.6964023</v>
+      </c>
+      <c r="F106" t="n">
+        <v>3472.461820484029</v>
+      </c>
+      <c r="G106" t="n">
+        <v>184995.7126473851</v>
       </c>
     </row>
   </sheetData>

--- a/secondary_logistics_routes.xlsx
+++ b/secondary_logistics_routes.xlsx
@@ -477,17 +477,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DPI64254, DPI66669, DPI66594, DPI66372, DPI64247</t>
+          <t>DPI64254 -&gt; DPI66669 -&gt; DPI66594 -&gt; DPI66372 -&gt; DPI64247</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>620.5440050899999</v>
       </c>
       <c r="F2" t="n">
-        <v>112.8614983328272</v>
+        <v>43.46942819675499</v>
       </c>
       <c r="G2" t="n">
-        <v>89314.29547251892</v>
+        <v>87338.00931504359</v>
       </c>
     </row>
     <row r="3">
@@ -502,17 +502,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DPI64091, DPI70040</t>
+          <t>DPI64091 -&gt; DPI70040</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>144.79150005</v>
       </c>
       <c r="F3" t="n">
-        <v>174.6836307166889</v>
+        <v>137.1013903889973</v>
       </c>
       <c r="G3" t="n">
-        <v>67534.93843279795</v>
+        <v>66785.1727382605</v>
       </c>
     </row>
     <row r="4">
@@ -552,17 +552,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DPI70031, DPI66461, DPI70165, DPI64191</t>
+          <t>DPI70031 -&gt; DPI66461 -&gt; DPI70165 -&gt; DPI64191</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>325.8430221</v>
       </c>
       <c r="F5" t="n">
-        <v>610.1415462764469</v>
+        <v>368.5993169800281</v>
       </c>
       <c r="G5" t="n">
-        <v>93997.43724144841</v>
+        <v>87961.2969313309</v>
       </c>
     </row>
     <row r="6">
@@ -577,17 +577,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DPI64590, DPI70221, DPI70149, DPI70327</t>
+          <t>DPI64590 -&gt; DPI70327 -&gt; DPI70221 -&gt; DPI70149</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>334.53533758</v>
       </c>
       <c r="F6" t="n">
-        <v>828.5588699925895</v>
+        <v>533.1915497261534</v>
       </c>
       <c r="G6" t="n">
-        <v>99455.68616111481</v>
+        <v>92074.45682765657</v>
       </c>
     </row>
     <row r="7">
@@ -602,17 +602,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>DPI64561, DPI64281, DPI65827, DPI70082, DPI67214, DPI66974, DPI70090, DPI64400</t>
+          <t>DPI64561 -&gt; DPI64281 -&gt; DPI65827 -&gt; DPI66974 -&gt; DPI67214 -&gt; DPI70082 -&gt; DPI64400 -&gt; DPI70090</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>635.10630896</v>
       </c>
       <c r="F7" t="n">
-        <v>1841.099839748307</v>
+        <v>526.3935180540061</v>
       </c>
       <c r="G7" t="n">
-        <v>138534.5234360318</v>
+        <v>101091.6873941781</v>
       </c>
     </row>
     <row r="8">
@@ -627,17 +627,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DPI64694, DPI70254, DPI66511, DPI64462</t>
+          <t>DPI64694 -&gt; DPI70254 -&gt; DPI66511 -&gt; DPI64462</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>346.40689368</v>
       </c>
       <c r="F8" t="n">
-        <v>974.9764917793544</v>
+        <v>296.8217307442487</v>
       </c>
       <c r="G8" t="n">
-        <v>103114.6625295661</v>
+        <v>86167.57505129877</v>
       </c>
     </row>
     <row r="9">
@@ -652,17 +652,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>DPI64606, DPI65825</t>
+          <t>DPI64606 -&gt; DPI65825</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>146.23574425</v>
       </c>
       <c r="F9" t="n">
-        <v>500.995255690341</v>
+        <v>276.7577793159488</v>
       </c>
       <c r="G9" t="n">
-        <v>74044.8553510223</v>
+        <v>69571.31769735318</v>
       </c>
     </row>
     <row r="10">
@@ -677,17 +677,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DPI65967, DPI66512, DPI64711</t>
+          <t>DPI65967 -&gt; DPI64711 -&gt; DPI66512</t>
         </is>
       </c>
       <c r="E10" t="n">
         <v>328.3208980799999</v>
       </c>
       <c r="F10" t="n">
-        <v>759.5723157985121</v>
+        <v>285.0466941086402</v>
       </c>
       <c r="G10" t="n">
-        <v>97731.71217180481</v>
+        <v>85873.31688577491</v>
       </c>
     </row>
     <row r="11">
@@ -702,17 +702,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DPI64364, DPI66265, DPI67245</t>
+          <t>DPI64364 -&gt; DPI67245 -&gt; DPI66265</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>337.6667410699999</v>
       </c>
       <c r="F11" t="n">
-        <v>768.9737554290704</v>
+        <v>275.9108540825973</v>
       </c>
       <c r="G11" t="n">
-        <v>97966.65414817247</v>
+        <v>85645.01224352411</v>
       </c>
     </row>
     <row r="12">
@@ -727,17 +727,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>DPI64513, DPI65824, DPI67043, DPI65981, DPI65927, DPI64239, DPI66555, DPI64045</t>
+          <t>DPI64513 -&gt; DPI65824 -&gt; DPI65981 -&gt; DPI65927 -&gt; DPI67043 -&gt; DPI66555 -&gt; DPI64239 -&gt; DPI64045</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>968.52758027</v>
       </c>
       <c r="F12" t="n">
-        <v>2198.53300675828</v>
+        <v>725.757176473101</v>
       </c>
       <c r="G12" t="n">
-        <v>171025.8679517392</v>
+        <v>122704.0929600824</v>
       </c>
     </row>
     <row r="13">
@@ -752,17 +752,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>DPI66503, DPI64008, DPI64619, DPI67004, DPI64175, DPI64085, DPI66060, DPI70228, DPI66100</t>
+          <t>DPI66503 -&gt; DPI64008 -&gt; DPI67004 -&gt; DPI64175 -&gt; DPI66100 -&gt; DPI64619 -&gt; DPI66060 -&gt; DPI64085 -&gt; DPI70228</t>
         </is>
       </c>
       <c r="E13" t="n">
         <v>928.5492191299999</v>
       </c>
       <c r="F13" t="n">
-        <v>2822.379392352044</v>
+        <v>902.6241608899024</v>
       </c>
       <c r="G13" t="n">
-        <v>191494.2678630706</v>
+        <v>128507.0987187977</v>
       </c>
     </row>
     <row r="14">
@@ -777,17 +777,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DPI70035, DPI64108, DPI66938</t>
+          <t>DPI70035 -&gt; DPI64108 -&gt; DPI66938</t>
         </is>
       </c>
       <c r="E14" t="n">
         <v>332.7000399999999</v>
       </c>
       <c r="F14" t="n">
-        <v>1008.624873895105</v>
+        <v>515.8892308925966</v>
       </c>
       <c r="G14" t="n">
-        <v>103955.5355986387</v>
+        <v>91642.07188000598</v>
       </c>
     </row>
     <row r="15">
@@ -802,17 +802,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>DPI67102, DPI64024, DPI67047</t>
+          <t>DPI67102 -&gt; DPI64024 -&gt; DPI67047</t>
         </is>
       </c>
       <c r="E15" t="n">
         <v>317.49137532</v>
       </c>
       <c r="F15" t="n">
-        <v>1077.853653632775</v>
+        <v>538.2622643052007</v>
       </c>
       <c r="G15" t="n">
-        <v>105685.5628042831</v>
+        <v>92201.17398498696</v>
       </c>
     </row>
     <row r="16">
@@ -827,17 +827,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DPI70234, DPI66915, DPI64506, DPI66491</t>
+          <t>DPI70234 -&gt; DPI66491 -&gt; DPI66915 -&gt; DPI64506</t>
         </is>
       </c>
       <c r="E16" t="n">
         <v>316.75566</v>
       </c>
       <c r="F16" t="n">
-        <v>1664.129129929559</v>
+        <v>807.2826872166887</v>
       </c>
       <c r="G16" t="n">
-        <v>120336.5869569397</v>
+        <v>98923.99435354504</v>
       </c>
     </row>
     <row r="17">
@@ -852,17 +852,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DPI64361, DPI65875, DPI63898, DPI64543, DPI66759, DPI63904, DPI66091, DPI70095, DPI64374</t>
+          <t>DPI64361 -&gt; DPI65875 -&gt; DPI63898 -&gt; DPI64543 -&gt; DPI66759 -&gt; DPI63904 -&gt; DPI66091 -&gt; DPI70095 -&gt; DPI64374</t>
         </is>
       </c>
       <c r="E17" t="n">
         <v>930.8836449600001</v>
       </c>
       <c r="F17" t="n">
-        <v>4492.49493344801</v>
+        <v>1233.537444888914</v>
       </c>
       <c r="G17" t="n">
-        <v>246290.7587664292</v>
+        <v>139364.3635668053</v>
       </c>
     </row>
     <row r="18">
@@ -877,17 +877,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DPI64299, DPI66380, DPI64253, DPI66953, DPI66748, DPI64137, DPI66127, DPI66329, DPI65841, DPI64563</t>
+          <t>DPI64299 -&gt; DPI64253 -&gt; DPI66748 -&gt; DPI66127 -&gt; DPI66329 -&gt; DPI65841 -&gt; DPI64563 -&gt; DPI64137 -&gt; DPI66953 -&gt; DPI66380</t>
         </is>
       </c>
       <c r="E18" t="n">
         <v>905.8948679999999</v>
       </c>
       <c r="F18" t="n">
-        <v>5638.335582495251</v>
+        <v>1173.437149199483</v>
       </c>
       <c r="G18" t="n">
-        <v>283885.7904616692</v>
+        <v>137392.472865235</v>
       </c>
     </row>
     <row r="19">
@@ -902,17 +902,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DPI64000, DPI63902, DPI66395</t>
+          <t>DPI64000 -&gt; DPI63902 -&gt; DPI66395</t>
         </is>
       </c>
       <c r="E19" t="n">
         <v>328.7647218</v>
       </c>
       <c r="F19" t="n">
-        <v>1782.570672254706</v>
+        <v>1551.117640800664</v>
       </c>
       <c r="G19" t="n">
-        <v>123296.4410996451</v>
+        <v>117512.4298436086</v>
       </c>
     </row>
     <row r="20">
@@ -927,17 +927,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>DPI70166, DPI63929, DPI64001, DPI64118, DPI67138, DPI67002, DPI64644</t>
+          <t>DPI70166 -&gt; DPI63929 -&gt; DPI64118 -&gt; DPI64644 -&gt; DPI67002 -&gt; DPI67138 -&gt; DPI64001</t>
         </is>
       </c>
       <c r="E20" t="n">
         <v>534.7424360499999</v>
       </c>
       <c r="F20" t="n">
-        <v>6053.357926000983</v>
+        <v>1825.237845342925</v>
       </c>
       <c r="G20" t="n">
-        <v>258499.633732508</v>
+        <v>138082.7738353665</v>
       </c>
     </row>
     <row r="21">
@@ -977,17 +977,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>DPI64104, DPI64273, DPI66900, DPI66263, DPI64665</t>
+          <t>DPI64104 -&gt; DPI64273 -&gt; DPI66900 -&gt; DPI64665 -&gt; DPI66263</t>
         </is>
       </c>
       <c r="E22" t="n">
         <v>602.7557599999999</v>
       </c>
       <c r="F22" t="n">
-        <v>739.2391510494806</v>
+        <v>388.1028766516076</v>
       </c>
       <c r="G22" t="n">
-        <v>107153.5310218892</v>
+        <v>97153.16992703779</v>
       </c>
     </row>
     <row r="23">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DPI64502, DPI70120, DPI64758, DPI64179, DPI70197, DPI64651</t>
+          <t>DPI64502 -&gt; DPI70120 -&gt; DPI64758 -&gt; DPI64179 -&gt; DPI70197 -&gt; DPI64651</t>
         </is>
       </c>
       <c r="E23" t="n">
         <v>635.38464</v>
       </c>
       <c r="F23" t="n">
-        <v>1902.701349962012</v>
+        <v>850.7110758840822</v>
       </c>
       <c r="G23" t="n">
-        <v>140288.9344469181</v>
+        <v>110328.2514411787</v>
       </c>
     </row>
     <row r="24">
@@ -1027,17 +1027,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DPI70179, DFT80081</t>
+          <t>DPI70179 -&gt; DFT80081</t>
         </is>
       </c>
       <c r="E24" t="n">
         <v>135.78948</v>
       </c>
       <c r="F24" t="n">
-        <v>794.387011442486</v>
+        <v>502.8336648803545</v>
       </c>
       <c r="G24" t="n">
-        <v>79898.0208782776</v>
+        <v>74081.53161436308</v>
       </c>
     </row>
     <row r="25">
@@ -1052,17 +1052,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>DPI70273, DPI66144</t>
+          <t>DPI70273 -&gt; DPI66144</t>
         </is>
       </c>
       <c r="E25" t="n">
         <v>138.78125</v>
       </c>
       <c r="F25" t="n">
-        <v>796.95215825844</v>
+        <v>399.04152217355</v>
       </c>
       <c r="G25" t="n">
-        <v>79949.19555725588</v>
+        <v>72010.87836736233</v>
       </c>
     </row>
     <row r="26">
@@ -1127,17 +1127,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>DPI66262, DPI70302, DPI64647, DPI64032, DPI63822, DPI64409</t>
+          <t>DPI66262 -&gt; DPI70302 -&gt; DPI64647 -&gt; DPI64032 -&gt; DPI64409 -&gt; DPI63822</t>
         </is>
       </c>
       <c r="E28" t="n">
         <v>628.25389965</v>
       </c>
       <c r="F28" t="n">
-        <v>2641.239796112111</v>
+        <v>922.4731099182513</v>
       </c>
       <c r="G28" t="n">
-        <v>161322.5093932729</v>
+        <v>112372.0341704718</v>
       </c>
     </row>
     <row r="29">
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DPI66421, DPI70317</t>
+          <t>DPI66421 -&gt; DPI70317</t>
         </is>
       </c>
       <c r="E30" t="n">
         <v>342.41514</v>
       </c>
       <c r="F30" t="n">
-        <v>918.8254339724073</v>
+        <v>487.6654235666871</v>
       </c>
       <c r="G30" t="n">
-        <v>101711.4475949705</v>
+        <v>90936.75893493151</v>
       </c>
     </row>
     <row r="31">
@@ -1202,17 +1202,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>DPI67198, DPI66528, DPI64692</t>
+          <t>DPI67198 -&gt; DPI64692 -&gt; DPI66528</t>
         </is>
       </c>
       <c r="E31" t="n">
         <v>332.04138</v>
       </c>
       <c r="F31" t="n">
-        <v>1390.6651480855</v>
+        <v>469.0117179012091</v>
       </c>
       <c r="G31" t="n">
-        <v>113502.7220506567</v>
+        <v>90470.60283035121</v>
       </c>
     </row>
     <row r="32">
@@ -1227,17 +1227,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>DPI64255, DPI63920, DFT80066, DPI64303, DPI67128, DPI64378, DPI70100</t>
+          <t>DPI64255 -&gt; DPI64303 -&gt; DPI70100 -&gt; DPI67128 -&gt; DPI64378 -&gt; DPI63920 -&gt; DFT80066</t>
         </is>
       </c>
       <c r="E32" t="n">
         <v>637.5615112</v>
       </c>
       <c r="F32" t="n">
-        <v>3293.221124108595</v>
+        <v>926.4025676681233</v>
       </c>
       <c r="G32" t="n">
-        <v>179890.9376146128</v>
+        <v>112483.9451271882</v>
       </c>
     </row>
     <row r="33">
@@ -1252,17 +1252,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DPI66659, DFT80087, DFT80034, DPI66092, DPI64476</t>
+          <t>DPI66659 -&gt; DPI64476 -&gt; DFT80034 -&gt; DPI66092 -&gt; DFT80087</t>
         </is>
       </c>
       <c r="E33" t="n">
         <v>340.15804015</v>
       </c>
       <c r="F33" t="n">
-        <v>2376.02176481915</v>
+        <v>930.3305622703397</v>
       </c>
       <c r="G33" t="n">
-        <v>138126.7839028306</v>
+        <v>101998.9607511358</v>
       </c>
     </row>
     <row r="34">
@@ -1302,17 +1302,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>DPI64484, DPI66327, DPI66508</t>
+          <t>DPI64484 -&gt; DPI66327 -&gt; DPI66508</t>
         </is>
       </c>
       <c r="E35" t="n">
         <v>325.10037</v>
       </c>
       <c r="F35" t="n">
-        <v>1441.264967290876</v>
+        <v>484.2416578484302</v>
       </c>
       <c r="G35" t="n">
-        <v>114767.211532599</v>
+        <v>90851.19902963228</v>
       </c>
     </row>
     <row r="36">
@@ -1327,17 +1327,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>DPI66229, DPI63817, DPI64511, DPI63895, DPI66335</t>
+          <t>DPI66229 -&gt; DPI63817 -&gt; DPI63895 -&gt; DPI64511 -&gt; DPI66335</t>
         </is>
       </c>
       <c r="E36" t="n">
         <v>596.84459</v>
       </c>
       <c r="F36" t="n">
-        <v>2445.138202841616</v>
+        <v>501.8633351957513</v>
       </c>
       <c r="G36" t="n">
-        <v>155737.5360169293</v>
+        <v>100393.067786375</v>
       </c>
     </row>
     <row r="37">
@@ -1352,17 +1352,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>DPI66646, DPI70002, DPI70106, DPI66175, DPI64639, DPI64746</t>
+          <t>DPI66646 -&gt; DPI66175 -&gt; DPI64639 -&gt; DPI70106 -&gt; DPI70002 -&gt; DPI64746</t>
         </is>
       </c>
       <c r="E37" t="n">
         <v>602.60659127</v>
       </c>
       <c r="F37" t="n">
-        <v>3443.267343772844</v>
+        <v>1596.491015022981</v>
       </c>
       <c r="G37" t="n">
-        <v>184164.2539506506</v>
+        <v>131568.0641078545</v>
       </c>
     </row>
     <row r="38">
@@ -1377,17 +1377,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>DPI70041, DPI66684, DPI67031, DPI64236, DPI67024, DPI64352, DPI66734, DPI64288, DPI70073, DPI64149</t>
+          <t>DPI70041 -&gt; DPI66684 -&gt; DPI67031 -&gt; DPI67024 -&gt; DPI64352 -&gt; DPI64288 -&gt; DPI70073 -&gt; DPI66734 -&gt; DPI64236 -&gt; DPI64149</t>
         </is>
       </c>
       <c r="E38" t="n">
         <v>892.6878400000002</v>
       </c>
       <c r="F38" t="n">
-        <v>8213.411476542757</v>
+        <v>915.2616410909682</v>
       </c>
       <c r="G38" t="n">
-        <v>368374.0305453679</v>
+        <v>128921.7344441947</v>
       </c>
     </row>
     <row r="39">
@@ -1402,17 +1402,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>DPI70038, DPI66692, DPI64323, DPI64166, DPI66618, DPI66102, DPI66384, DPI64392</t>
+          <t>DPI70038 -&gt; DPI64166 -&gt; DPI66102 -&gt; DPI66384 -&gt; DPI64392 -&gt; DPI66618 -&gt; DPI64323 -&gt; DPI66692</t>
         </is>
       </c>
       <c r="E39" t="n">
         <v>921.08777092</v>
       </c>
       <c r="F39" t="n">
-        <v>7143.659197378387</v>
+        <v>1777.219274370255</v>
       </c>
       <c r="G39" t="n">
-        <v>333275.4582659849</v>
+        <v>157202.5643920881</v>
       </c>
     </row>
     <row r="40">
@@ -1452,17 +1452,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>DPI64624, DPI66572, DPI64234, DPI64176</t>
+          <t>DPI64624 -&gt; DPI64176 -&gt; DPI64234 -&gt; DPI66572</t>
         </is>
       </c>
       <c r="E41" t="n">
         <v>320.49699194</v>
       </c>
       <c r="F41" t="n">
-        <v>4144.464773084959</v>
+        <v>1750.941400284894</v>
       </c>
       <c r="G41" t="n">
-        <v>182320.1746793931</v>
+        <v>122506.0255931195</v>
       </c>
     </row>
     <row r="42">
@@ -1477,17 +1477,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>DPI66460, DPI63993, DPI64044</t>
+          <t>DPI66460 -&gt; DPI63993 -&gt; DPI64044</t>
         </is>
       </c>
       <c r="E42" t="n">
         <v>193.73862</v>
       </c>
       <c r="F42" t="n">
-        <v>3525.12116945802</v>
+        <v>1264.224626669494</v>
       </c>
       <c r="G42" t="n">
-        <v>166842.7780247559</v>
+        <v>110342.9734204707</v>
       </c>
     </row>
     <row r="43">
@@ -1502,17 +1502,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>DPI70142, DPI70109, DPI64052</t>
+          <t>DPI70142 -&gt; DPI70109 -&gt; DPI64052</t>
         </is>
       </c>
       <c r="E43" t="n">
         <v>320.90075138</v>
       </c>
       <c r="F43" t="n">
-        <v>176.6967455688558</v>
+        <v>165.7603039122733</v>
       </c>
       <c r="G43" t="n">
-        <v>83165.65167176571</v>
+        <v>82892.3499947677</v>
       </c>
     </row>
     <row r="44">
@@ -1527,17 +1527,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>DPI66179, DPI66597, DPI63958</t>
+          <t>DPI66179 -&gt; DPI66597 -&gt; DPI63958</t>
         </is>
       </c>
       <c r="E44" t="n">
         <v>341.97570951</v>
       </c>
       <c r="F44" t="n">
-        <v>448.4323666464777</v>
+        <v>199.9099514532233</v>
       </c>
       <c r="G44" t="n">
-        <v>89956.32484249548</v>
+        <v>83745.74968681605</v>
       </c>
     </row>
     <row r="45">
@@ -1552,17 +1552,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>DPI64638, DPI64218</t>
+          <t>DPI64638 -&gt; DPI64218</t>
         </is>
       </c>
       <c r="E45" t="n">
         <v>141.52363</v>
       </c>
       <c r="F45" t="n">
-        <v>361.3283894734152</v>
+        <v>184.9738277624375</v>
       </c>
       <c r="G45" t="n">
-        <v>71258.50136999463</v>
+        <v>67740.22786386062</v>
       </c>
     </row>
     <row r="46">
@@ -1577,17 +1577,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>DPI66387, DPI66307, DPI66039</t>
+          <t>DPI66387 -&gt; DPI66307 -&gt; DPI66039</t>
         </is>
       </c>
       <c r="E46" t="n">
         <v>349.4845</v>
       </c>
       <c r="F46" t="n">
-        <v>549.4052752319394</v>
+        <v>190.8797116503079</v>
       </c>
       <c r="G46" t="n">
-        <v>92479.63782804616</v>
+        <v>83520.0839941412</v>
       </c>
     </row>
     <row r="47">
@@ -1602,17 +1602,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>DPI67121, DPI66289, DPI64039, DPI64301, DPI66339, DPI66203, DPI64450, DPI66069</t>
+          <t>DPI67121 -&gt; DPI64450 -&gt; DPI66203 -&gt; DPI66289 -&gt; DPI64039 -&gt; DPI66069 -&gt; DPI64301 -&gt; DPI66339</t>
         </is>
       </c>
       <c r="E47" t="n">
         <v>902.05745714</v>
       </c>
       <c r="F47" t="n">
-        <v>1506.817140437383</v>
+        <v>202.8545068429208</v>
       </c>
       <c r="G47" t="n">
-        <v>148330.6703777505</v>
+        <v>105547.6563695162</v>
       </c>
     </row>
     <row r="48">
@@ -1627,17 +1627,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>DPI64686, DPI66590, DPI70316, DFT80044, DPI64216, DFT80088, DPI70255, DPI70009, DPI66923</t>
+          <t>DPI64686 -&gt; DPI66590 -&gt; DFT80044 -&gt; DPI64216 -&gt; DFT80088 -&gt; DPI70316 -&gt; DPI70255 -&gt; DPI70009 -&gt; DPI66923</t>
         </is>
       </c>
       <c r="E48" t="n">
         <v>621.71592092</v>
       </c>
       <c r="F48" t="n">
-        <v>2149.913702733013</v>
+        <v>797.0558633621556</v>
       </c>
       <c r="G48" t="n">
-        <v>147329.5422538362</v>
+        <v>108800.1509885542</v>
       </c>
     </row>
     <row r="49">
@@ -1652,17 +1652,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>DPI64480, DPI66078, DPI64433, DPI66658, DPI67187, DPI66221</t>
+          <t>DPI64480 -&gt; DPI64433 -&gt; DPI66078 -&gt; DPI66658 -&gt; DPI67187 -&gt; DPI66221</t>
         </is>
       </c>
       <c r="E49" t="n">
         <v>598.1027300000001</v>
       </c>
       <c r="F49" t="n">
-        <v>2337.5389221152</v>
+        <v>668.0261888267878</v>
       </c>
       <c r="G49" t="n">
-        <v>152673.1085018409</v>
+        <v>105125.3858577869</v>
       </c>
     </row>
     <row r="50">
@@ -1677,17 +1677,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>DPI70105, DPI66373, DPI64196, DPI66653, DPI66645, DPI66154, DPI63827, DPI66153, DPI70081, DPI67072</t>
+          <t>DPI70105 -&gt; DPI66653 -&gt; DPI64196 -&gt; DPI66373 -&gt; DPI66153 -&gt; DPI67072 -&gt; DPI70081 -&gt; DPI66154 -&gt; DPI63827 -&gt; DPI66645</t>
         </is>
       </c>
       <c r="E50" t="n">
         <v>971.88974101</v>
       </c>
       <c r="F50" t="n">
-        <v>4096.684966185147</v>
+        <v>876.8393249252302</v>
       </c>
       <c r="G50" t="n">
-        <v>233304.2337405347</v>
+        <v>127661.0982507968</v>
       </c>
     </row>
     <row r="51">
@@ -1702,17 +1702,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>DPI66313, DPI66449</t>
+          <t>DPI66313 -&gt; DPI66449</t>
         </is>
       </c>
       <c r="E51" t="n">
         <v>315.86378731</v>
       </c>
       <c r="F51" t="n">
-        <v>833.0782276266925</v>
+        <v>425.0427875226114</v>
       </c>
       <c r="G51" t="n">
-        <v>99568.62490839104</v>
+        <v>89371.81926019005</v>
       </c>
     </row>
     <row r="52">
@@ -1727,17 +1727,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>DPI66576, DPI63919, DPI64592</t>
+          <t>DPI66576 -&gt; DPI64592 -&gt; DPI63919</t>
         </is>
       </c>
       <c r="E52" t="n">
         <v>330.8032</v>
       </c>
       <c r="F52" t="n">
-        <v>1268.125198302735</v>
+        <v>430.0531118874321</v>
       </c>
       <c r="G52" t="n">
-        <v>110440.4487055854</v>
+        <v>89497.02726606693</v>
       </c>
     </row>
     <row r="53">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>DPI66636, DFT80077, DFT80078, DPI64136, DPI64431, DPI64413, DPI64244, DPI64094, DPI66128, DPI66715</t>
+          <t>DPI66636 -&gt; DFT80077 -&gt; DFT80078 -&gt; DPI64136 -&gt; DPI64431 -&gt; DPI64413 -&gt; DPI64244 -&gt; DPI66128 -&gt; DPI64094 -&gt; DPI66715</t>
         </is>
       </c>
       <c r="E53" t="n">
         <v>941.4133046699999</v>
       </c>
       <c r="F53" t="n">
-        <v>5020.143212902989</v>
+        <v>1557.328733483469</v>
       </c>
       <c r="G53" t="n">
-        <v>263602.8988153471</v>
+        <v>149987.9557455926</v>
       </c>
     </row>
     <row r="54">
@@ -1777,17 +1777,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>DPI64436, DPI64119, DPI70096, DPI64666</t>
+          <t>DPI64436 -&gt; DPI64666 -&gt; DPI64119 -&gt; DPI70096</t>
         </is>
       </c>
       <c r="E54" t="n">
         <v>331.5481275000001</v>
       </c>
       <c r="F54" t="n">
-        <v>2641.374991257408</v>
+        <v>1770.720356264008</v>
       </c>
       <c r="G54" t="n">
-        <v>144757.9610315226</v>
+        <v>123000.3017030375</v>
       </c>
     </row>
     <row r="55">
@@ -1802,17 +1802,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>DPI70047, DPI66679, DPI66209</t>
+          <t>DPI70047 -&gt; DPI66679 -&gt; DPI66209</t>
         </is>
       </c>
       <c r="E55" t="n">
         <v>345.1143381000001</v>
       </c>
       <c r="F55" t="n">
-        <v>2053.462139596656</v>
+        <v>1194.400756043251</v>
       </c>
       <c r="G55" t="n">
-        <v>130066.0188685204</v>
+        <v>108598.0748935208</v>
       </c>
     </row>
     <row r="56">
@@ -1827,17 +1827,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>DPI70190, DPI67224</t>
+          <t>DPI70190 -&gt; DPI67224</t>
         </is>
       </c>
       <c r="E56" t="n">
         <v>146.0747</v>
       </c>
       <c r="F56" t="n">
-        <v>1388.894523206169</v>
+        <v>700.2236885152075</v>
       </c>
       <c r="G56" t="n">
-        <v>91758.44573796308</v>
+        <v>78019.46258587838</v>
       </c>
     </row>
     <row r="57">
@@ -1852,17 +1852,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>DPI64634, DPI67148, DPI64742, DPI63976, DPI64456</t>
+          <t>DPI64634 -&gt; DPI63976 -&gt; DPI64742 -&gt; DPI67148 -&gt; DPI64456</t>
         </is>
       </c>
       <c r="E57" t="n">
         <v>634.3604575000001</v>
       </c>
       <c r="F57" t="n">
-        <v>3732.276882797153</v>
+        <v>1149.362337677768</v>
       </c>
       <c r="G57" t="n">
-        <v>192395.2456220629</v>
+        <v>118833.8393770628</v>
       </c>
     </row>
     <row r="58">
@@ -1877,17 +1877,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>DPI66574, DPI66946, DPI64169, DPI64628, DPI64056, DPI67074</t>
+          <t>DPI66574 -&gt; DPI66946 -&gt; DPI64056 -&gt; DPI67074 -&gt; DPI64628 -&gt; DPI64169</t>
         </is>
       </c>
       <c r="E58" t="n">
         <v>634.7518375000001</v>
       </c>
       <c r="F58" t="n">
-        <v>4729.782125555788</v>
+        <v>2104.594631462105</v>
       </c>
       <c r="G58" t="n">
-        <v>220804.1949358289</v>
+        <v>146038.8551040407</v>
       </c>
     </row>
     <row r="59">
@@ -1902,17 +1902,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>DPI66172, DPI64057, DPI66051, DPI63802, DPI64037, DPI70253, DPI70213, DPI66067</t>
+          <t>DPI66172 -&gt; DPI64057 -&gt; DPI63802 -&gt; DPI66051 -&gt; DPI64037 -&gt; DPI70213 -&gt; DPI66067 -&gt; DPI70253</t>
         </is>
       </c>
       <c r="E59" t="n">
         <v>650.4852999999999</v>
       </c>
       <c r="F59" t="n">
-        <v>6459.321119963359</v>
+        <v>2118.672848779382</v>
       </c>
       <c r="G59" t="n">
-        <v>270061.4654965565</v>
+        <v>146439.8027332368</v>
       </c>
     </row>
     <row r="60">
@@ -1927,17 +1927,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>DPI66742, DPI67178, DPI64297, DPI64724, DPI63915</t>
+          <t>DPI66742 -&gt; DPI67178 -&gt; DPI64297 -&gt; DPI64724 -&gt; DPI63915</t>
         </is>
       </c>
       <c r="E60" t="n">
         <v>626.19535</v>
       </c>
       <c r="F60" t="n">
-        <v>4162.18445493579</v>
+        <v>841.2896834820029</v>
       </c>
       <c r="G60" t="n">
-        <v>204639.0132765713</v>
+        <v>110059.9301855674</v>
       </c>
     </row>
     <row r="61">
@@ -1952,17 +1952,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>DPI67180, DPI70296, DPI66096, DPI64018, DPI66634, DPI70214</t>
+          <t>DPI67180 -&gt; DPI70296 -&gt; DPI66096 -&gt; DPI64018 -&gt; DPI70214 -&gt; DPI66634</t>
         </is>
       </c>
       <c r="E61" t="n">
         <v>631.91267</v>
       </c>
       <c r="F61" t="n">
-        <v>6251.338632338227</v>
+        <v>1920.131362158535</v>
       </c>
       <c r="G61" t="n">
-        <v>264138.1242489927</v>
+        <v>140785.3411942751</v>
       </c>
     </row>
     <row r="62">
@@ -1977,17 +1977,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>DPI64495, DPI66129, DFT80080, DPI70229, DPI66736</t>
+          <t>DPI64495 -&gt; DPI66129 -&gt; DFT80080 -&gt; DPI70229 -&gt; DPI66736</t>
         </is>
       </c>
       <c r="E62" t="n">
         <v>627.55891</v>
       </c>
       <c r="F62" t="n">
-        <v>5715.227117645433</v>
+        <v>1258.15430281568</v>
       </c>
       <c r="G62" t="n">
-        <v>248869.668310542</v>
+        <v>121932.2345441906</v>
       </c>
     </row>
     <row r="63">
@@ -2002,17 +2002,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>DPI70107, DPI64548</t>
+          <t>DPI70107 -&gt; DPI64548</t>
         </is>
       </c>
       <c r="E63" t="n">
         <v>175.93195</v>
       </c>
       <c r="F63" t="n">
-        <v>2445.173651824534</v>
+        <v>1332.589494907853</v>
       </c>
       <c r="G63" t="n">
-        <v>139854.8895590951</v>
+        <v>112051.4114777472</v>
       </c>
     </row>
     <row r="64">
@@ -2027,17 +2027,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>DPI66929, DPI66437, DPI64600</t>
+          <t>DPI66929 -&gt; DPI66437 -&gt; DPI64600</t>
         </is>
       </c>
       <c r="E64" t="n">
         <v>336.06904157</v>
       </c>
       <c r="F64" t="n">
-        <v>45.88063523883613</v>
+        <v>44.42178865891638</v>
       </c>
       <c r="G64" t="n">
-        <v>79896.55707461851</v>
+        <v>79860.10049858633</v>
       </c>
     </row>
     <row r="65">
@@ -2052,17 +2052,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>DPI64377, DPI66626</t>
+          <t>DPI64377 -&gt; DPI66626</t>
         </is>
       </c>
       <c r="E65" t="n">
         <v>142.07492374</v>
       </c>
       <c r="F65" t="n">
-        <v>369.7925494388147</v>
+        <v>197.9088171345552</v>
       </c>
       <c r="G65" t="n">
-        <v>71427.36136130436</v>
+        <v>67998.28090183437</v>
       </c>
     </row>
     <row r="66">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>DPI70176, DPI66578, DPI66573, DPI63823, DPI67042, DPI66998, DPI70057, DPI66386, DPI67110</t>
+          <t>DPI70176 -&gt; DPI66578 -&gt; DPI67042 -&gt; DPI70057 -&gt; DPI63823 -&gt; DPI66386 -&gt; DPI67110 -&gt; DPI66998 -&gt; DPI66573</t>
         </is>
       </c>
       <c r="E66" t="n">
         <v>939.6523527100001</v>
       </c>
       <c r="F66" t="n">
-        <v>1949.101653238935</v>
+        <v>246.0671157761433</v>
       </c>
       <c r="G66" t="n">
-        <v>162842.0252427695</v>
+        <v>106965.4620686153</v>
       </c>
     </row>
     <row r="67">
@@ -2102,17 +2102,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>DPI70140, DPI66685, DPI66378, DPI66053, DPI67064, DPI67179, DPI66241, DPI66094, DPI70216</t>
+          <t>DPI70140 -&gt; DPI67064 -&gt; DPI66241 -&gt; DPI67179 -&gt; DPI66685 -&gt; DPI66053 -&gt; DPI66094 -&gt; DPI66378 -&gt; DPI70216</t>
         </is>
       </c>
       <c r="E67" t="n">
         <v>921.88629411</v>
       </c>
       <c r="F67" t="n">
-        <v>2093.76531224934</v>
+        <v>490.1938041679894</v>
       </c>
       <c r="G67" t="n">
-        <v>167588.4398949009</v>
+        <v>114975.2587147517</v>
       </c>
     </row>
     <row r="68">
@@ -2127,17 +2127,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>DPI70091, DPI66076, DPI66619, DPI64577, DPI66191, DPI66522</t>
+          <t>DPI70091 -&gt; DPI66191 -&gt; DPI64577 -&gt; DPI66522 -&gt; DPI66619 -&gt; DPI66076</t>
         </is>
       </c>
       <c r="E68" t="n">
         <v>624.9482230900001</v>
       </c>
       <c r="F68" t="n">
-        <v>1443.523097806382</v>
+        <v>257.4381857812567</v>
       </c>
       <c r="G68" t="n">
-        <v>127211.5378255258</v>
+        <v>93431.83953105019</v>
       </c>
     </row>
     <row r="69">
@@ -2152,17 +2152,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>DPI66194, DFT80095, DPI70320, DPI64331, DPI64520, DPI66660, DPI66400, DPI67217, DPI65919</t>
+          <t>DPI66194 -&gt; DPI66660 -&gt; DPI65919 -&gt; DPI64331 -&gt; DPI67217 -&gt; DPI66400 -&gt; DPI64520 -&gt; DPI70320 -&gt; DFT80095</t>
         </is>
       </c>
       <c r="E69" t="n">
         <v>953.4635650600001</v>
       </c>
       <c r="F69" t="n">
-        <v>2214.149932842416</v>
+        <v>273.7890505047844</v>
       </c>
       <c r="G69" t="n">
-        <v>171538.2592965597</v>
+        <v>107875.018747062</v>
       </c>
     </row>
     <row r="70">
@@ -2177,17 +2177,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>DPI66377, DPI66688, DPI64631, DPI66621, DPI64650, DPI66521, DPI66359, DPI70104, DPI66755</t>
+          <t>DPI66377 -&gt; DPI64650 -&gt; DPI66359 -&gt; DPI70104 -&gt; DPI66688 -&gt; DPI66755 -&gt; DPI66621 -&gt; DPI64631 -&gt; DPI66521</t>
         </is>
       </c>
       <c r="E70" t="n">
         <v>894.22743988</v>
       </c>
       <c r="F70" t="n">
-        <v>2287.509704000288</v>
+        <v>293.0113364446653</v>
       </c>
       <c r="G70" t="n">
-        <v>173945.1933882495</v>
+        <v>108505.7019487495</v>
       </c>
     </row>
     <row r="71">
@@ -2202,17 +2202,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>DPI66042, DPI66126, DPI64019, DPI65789, DPI63950, DPI65840</t>
+          <t>DPI66042 -&gt; DPI63950 -&gt; DPI65840 -&gt; DPI66126 -&gt; DPI65789 -&gt; DPI64019</t>
         </is>
       </c>
       <c r="E71" t="n">
         <v>651.1897926199999</v>
       </c>
       <c r="F71" t="n">
-        <v>1546.206326110544</v>
+        <v>270.7011416285878</v>
       </c>
       <c r="G71" t="n">
-        <v>130135.9561676283</v>
+        <v>93809.56851358218</v>
       </c>
     </row>
     <row r="72">
@@ -2227,17 +2227,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>DPI63951, DPI66422, DPI66014</t>
+          <t>DPI63951 -&gt; DPI66422 -&gt; DPI66014</t>
         </is>
       </c>
       <c r="E72" t="n">
         <v>330.00319794</v>
       </c>
       <c r="F72" t="n">
-        <v>782.3167326506256</v>
+        <v>267.4195017856523</v>
       </c>
       <c r="G72" t="n">
-        <v>98300.09514893913</v>
+        <v>85432.81334962345</v>
       </c>
     </row>
     <row r="73">
@@ -2252,17 +2252,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>DPI64026, DPI66389</t>
+          <t>DPI64026 -&gt; DPI66389</t>
         </is>
       </c>
       <c r="E73" t="n">
         <v>145.55047117</v>
       </c>
       <c r="F73" t="n">
-        <v>523.4193225885434</v>
+        <v>263.3495786151545</v>
       </c>
       <c r="G73" t="n">
-        <v>74492.21548564144</v>
+        <v>69303.82409337233</v>
       </c>
     </row>
     <row r="74">
@@ -2277,17 +2277,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>DPI66136, DPI66410, DPI65969, DPI64250</t>
+          <t>DPI66136 -&gt; DPI65969 -&gt; DPI66410 -&gt; DPI64250</t>
         </is>
       </c>
       <c r="E74" t="n">
         <v>336.6333720600001</v>
       </c>
       <c r="F74" t="n">
-        <v>1054.689053600161</v>
+        <v>272.3753738607775</v>
       </c>
       <c r="G74" t="n">
-        <v>105106.679449468</v>
+        <v>85556.66059278083</v>
       </c>
     </row>
     <row r="75">
@@ -2302,17 +2302,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>DPI66501, DPI64470, DPI65993</t>
+          <t>DPI66501 -&gt; DPI64470 -&gt; DPI65993</t>
         </is>
       </c>
       <c r="E75" t="n">
         <v>323.65744947</v>
       </c>
       <c r="F75" t="n">
-        <v>798.5381956920228</v>
+        <v>275.7012910726287</v>
       </c>
       <c r="G75" t="n">
-        <v>98705.46951034365</v>
+        <v>85639.77526390499</v>
       </c>
     </row>
     <row r="76">
@@ -2327,17 +2327,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>DPI70148, DPI65915, DPI65779</t>
+          <t>DPI70148 -&gt; DPI65915 -&gt; DPI65779</t>
         </is>
       </c>
       <c r="E76" t="n">
         <v>321.93852002</v>
       </c>
       <c r="F76" t="n">
-        <v>801.0144191108886</v>
+        <v>285.8778413154109</v>
       </c>
       <c r="G76" t="n">
-        <v>98767.35033358111</v>
+        <v>85894.08725447212</v>
       </c>
     </row>
     <row r="77">
@@ -2377,17 +2377,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>DPI67118, DPI70069</t>
+          <t>DPI67118 -&gt; DPI70069</t>
         </is>
       </c>
       <c r="E78" t="n">
         <v>140.82943761</v>
       </c>
       <c r="F78" t="n">
-        <v>538.6124259579057</v>
+        <v>288.7751695832079</v>
       </c>
       <c r="G78" t="n">
-        <v>74795.31789786022</v>
+        <v>69811.064633185</v>
       </c>
     </row>
     <row r="79">
@@ -2402,17 +2402,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>DPI64602, DPI67183, DPI67126, DPI66538, DPI67021, DPI65877, DPI67014, DPI70261, DPI65998</t>
+          <t>DPI64602 -&gt; DPI67183 -&gt; DPI66538 -&gt; DPI65998 -&gt; DPI67014 -&gt; DPI65877 -&gt; DPI67126 -&gt; DPI70261 -&gt; DPI67021</t>
         </is>
       </c>
       <c r="E79" t="n">
         <v>918.58840689</v>
       </c>
       <c r="F79" t="n">
-        <v>2439.226724571303</v>
+        <v>296.907209287421</v>
       </c>
       <c r="G79" t="n">
-        <v>178923.0288331844</v>
+        <v>108633.5255367203</v>
       </c>
     </row>
     <row r="80">
@@ -2427,17 +2427,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>DPI66970, DPI64240, DPI64140, DPI66622, DPI66926, DPI64207</t>
+          <t>DPI66970 -&gt; DPI64240 -&gt; DPI66926 -&gt; DPI64140 -&gt; DPI66622 -&gt; DPI64207</t>
         </is>
       </c>
       <c r="E80" t="n">
         <v>635.77834015</v>
       </c>
       <c r="F80" t="n">
-        <v>1649.271304550981</v>
+        <v>297.7172279449737</v>
       </c>
       <c r="G80" t="n">
-        <v>133071.246753612</v>
+        <v>94578.98665187285</v>
       </c>
     </row>
     <row r="81">
@@ -2477,17 +2477,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>DPI66333, DPI66031, DPI66733, DPI67181, DPI64408</t>
+          <t>DPI66333 -&gt; DPI64408 -&gt; DPI66031 -&gt; DPI67181 -&gt; DPI66733</t>
         </is>
       </c>
       <c r="E82" t="n">
         <v>635.58432131</v>
       </c>
       <c r="F82" t="n">
-        <v>1407.785459025591</v>
+        <v>291.1457885229876</v>
       </c>
       <c r="G82" t="n">
-        <v>126193.7298730488</v>
+        <v>94391.83205713468</v>
       </c>
     </row>
     <row r="83">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>DPI64752, DPI70306, DPI64469, DPI63978, DPI67093, DPI70256, DPI64043</t>
+          <t>DPI64752 -&gt; DPI63978 -&gt; DPI70306 -&gt; DPI64469 -&gt; DPI67093 -&gt; DPI70256 -&gt; DPI64043</t>
         </is>
       </c>
       <c r="E83" t="n">
         <v>631.6363794299999</v>
       </c>
       <c r="F83" t="n">
-        <v>2137.719327548343</v>
+        <v>663.6163567022193</v>
       </c>
       <c r="G83" t="n">
-        <v>146982.2464485768</v>
+        <v>104999.7938388792</v>
       </c>
     </row>
     <row r="84">
@@ -2527,17 +2527,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>DPI64720, DPI64741, DPI64279, DPI64073, DPI66548</t>
+          <t>DPI64720 -&gt; DPI64741 -&gt; DPI64279 -&gt; DPI64073 -&gt; DPI66548</t>
         </is>
       </c>
       <c r="E84" t="n">
         <v>317.3867891</v>
       </c>
       <c r="F84" t="n">
-        <v>2520.053067953841</v>
+        <v>1115.637800892066</v>
       </c>
       <c r="G84" t="n">
-        <v>141726.1261681665</v>
+        <v>106629.7886442927</v>
       </c>
     </row>
     <row r="85">
@@ -2552,17 +2552,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>DPI64203, DPI66119, DPI67050, DPI66224, DPI70058, DPI66945, DPI64428</t>
+          <t>DPI64203 -&gt; DPI66119 -&gt; DPI67050 -&gt; DPI70058 -&gt; DPI66224 -&gt; DPI66945 -&gt; DPI64428</t>
         </is>
       </c>
       <c r="E85" t="n">
         <v>640.75966165</v>
       </c>
       <c r="F85" t="n">
-        <v>4539.216716455613</v>
+        <v>1163.141949882287</v>
       </c>
       <c r="G85" t="n">
-        <v>215376.8920846559</v>
+        <v>119226.2827326475</v>
       </c>
     </row>
     <row r="86">
@@ -2577,17 +2577,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>DPI64083, DPI64310, DPI64317, DPI70039</t>
+          <t>DPI64083 -&gt; DPI70039 -&gt; DPI64317 -&gt; DPI64310</t>
         </is>
       </c>
       <c r="E86" t="n">
         <v>140.84405604</v>
       </c>
       <c r="F86" t="n">
-        <v>3277.775543054072</v>
+        <v>1581.927617644406</v>
       </c>
       <c r="G86" t="n">
-        <v>129441.6220839287</v>
+        <v>95609.4559720059</v>
       </c>
     </row>
     <row r="87">
@@ -2602,17 +2602,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>DPI63813, DPI66239, DPI66940, DPI66591, DPI66944, DFT80058, DPI66640</t>
+          <t>DPI63813 -&gt; DPI66640 -&gt; DPI66239 -&gt; DPI66591 -&gt; DPI66944 -&gt; DFT80058 -&gt; DPI66940</t>
         </is>
       </c>
       <c r="E87" t="n">
         <v>327.69205942</v>
       </c>
       <c r="F87" t="n">
-        <v>5932.120344325858</v>
+        <v>1343.916324211989</v>
       </c>
       <c r="G87" t="n">
-        <v>226993.6874047032</v>
+        <v>112334.4689420576</v>
       </c>
     </row>
     <row r="88">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>DPI64252, DPI67062, DPI70032, DPI66532, DPI64145, DPI70022, DPI66125, DPI66497</t>
+          <t>DPI64252 -&gt; DPI67062 -&gt; DPI66532 -&gt; DPI66125 -&gt; DPI66497 -&gt; DPI64145 -&gt; DPI70022 -&gt; DPI70032</t>
         </is>
       </c>
       <c r="E88" t="n">
         <v>612.18888426</v>
       </c>
       <c r="F88" t="n">
-        <v>6990.112657892177</v>
+        <v>976.7605089881511</v>
       </c>
       <c r="G88" t="n">
-        <v>285178.4084967692</v>
+        <v>113918.1392959825</v>
       </c>
     </row>
     <row r="89">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>DPI66730, DPI64525, DPI64102, DPI66999, DPI66029, DPI64336, DPI66104</t>
+          <t>DPI66730 -&gt; DPI66104 -&gt; DPI64336 -&gt; DPI64102 -&gt; DPI66029 -&gt; DPI64525 -&gt; DPI66999</t>
         </is>
       </c>
       <c r="E89" t="n">
         <v>342.83971353</v>
       </c>
       <c r="F89" t="n">
-        <v>6181.368542405836</v>
+        <v>1091.769728310716</v>
       </c>
       <c r="G89" t="n">
-        <v>233222.3998747218</v>
+        <v>106033.3255104848</v>
       </c>
     </row>
     <row r="90">
@@ -2677,17 +2677,17 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>DPI64291, DPI64237, DPI64641, DPI63999, DPI64079, DPI64703, DPI66652, DPI64418, DPI66122, DPI66326, DPI63945</t>
+          <t>DPI64291 -&gt; DPI64237 -&gt; DPI64079 -&gt; DPI64641 -&gt; DPI63999 -&gt; DPI66652 -&gt; DPI64703 -&gt; DPI66326 -&gt; DPI64418 -&gt; DPI66122 -&gt; DPI63945</t>
         </is>
       </c>
       <c r="E90" t="n">
         <v>626.18171139</v>
       </c>
       <c r="F90" t="n">
-        <v>10391.33379473243</v>
+        <v>1355.345101984429</v>
       </c>
       <c r="G90" t="n">
-        <v>382045.1864739796</v>
+        <v>124700.2285045165</v>
       </c>
     </row>
     <row r="91">
@@ -2702,17 +2702,17 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>DPI66729, DPI64350</t>
+          <t>DPI66729 -&gt; DPI64350</t>
         </is>
       </c>
       <c r="E91" t="n">
         <v>149.24456164</v>
       </c>
       <c r="F91" t="n">
-        <v>1976.713766983252</v>
+        <v>990.1562603971061</v>
       </c>
       <c r="G91" t="n">
-        <v>103485.4396513159</v>
+        <v>83803.61739492227</v>
       </c>
     </row>
     <row r="92">
@@ -2727,17 +2727,17 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>DPI63936, DPI64706, DPI64246, DPI64106</t>
+          <t>DPI63936 -&gt; DPI64246 -&gt; DPI64706 -&gt; DPI64106</t>
         </is>
       </c>
       <c r="E92" t="n">
         <v>258.96950801</v>
       </c>
       <c r="F92" t="n">
-        <v>4002.127447239615</v>
+        <v>2040.577261524614</v>
       </c>
       <c r="G92" t="n">
-        <v>178763.164906518</v>
+        <v>129744.0257655001</v>
       </c>
     </row>
     <row r="93">
@@ -2752,17 +2752,17 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>DPI67040, DFT80016, DPI63872, DPI66487, DPI64235, DPI63862, DPI66035</t>
+          <t>DPI67040 -&gt; DFT80016 -&gt; DPI63872 -&gt; DPI66487 -&gt; DPI64235 -&gt; DPI63862 -&gt; DPI66035</t>
         </is>
       </c>
       <c r="E93" t="n">
         <v>626.9946460000001</v>
       </c>
       <c r="F93" t="n">
-        <v>953.9992158911998</v>
+        <v>261.9494428119992</v>
       </c>
       <c r="G93" t="n">
-        <v>113269.8976685814</v>
+        <v>93560.32013128574</v>
       </c>
     </row>
     <row r="94">
@@ -2777,17 +2777,17 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>DPI70051, DPI64424, DPI64594, DFT80025, DPI67069, DPI66008, DPI64181, DPI66507, DPI64190</t>
+          <t>DPI70051 -&gt; DPI64594 -&gt; DFT80025 -&gt; DPI64424 -&gt; DPI67069 -&gt; DPI66008 -&gt; DPI64190 -&gt; DPI66507 -&gt; DPI64181</t>
         </is>
       </c>
       <c r="E94" t="n">
         <v>902.4486694999999</v>
       </c>
       <c r="F94" t="n">
-        <v>1704.113917754574</v>
+        <v>267.3574828392963</v>
       </c>
       <c r="G94" t="n">
-        <v>154803.9776415276</v>
+        <v>107663.9990119573</v>
       </c>
     </row>
     <row r="95">
@@ -2802,17 +2802,17 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>DPI66463, DPI66332, DPI70014, DPI64040, DPI70126, DPI64717, DPI66290</t>
+          <t>DPI66463 -&gt; DPI66332 -&gt; DPI64040 -&gt; DPI70014 -&gt; DPI66290 -&gt; DPI64717 -&gt; DPI70126</t>
         </is>
       </c>
       <c r="E95" t="n">
         <v>900.3597684999999</v>
       </c>
       <c r="F95" t="n">
-        <v>1460.477113024069</v>
+        <v>267.0573933100857</v>
       </c>
       <c r="G95" t="n">
-        <v>146810.2540783197</v>
+        <v>107654.1530745039</v>
       </c>
     </row>
     <row r="96">
@@ -2827,17 +2827,17 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>DPI70129, DPI63871, DPI64610</t>
+          <t>DPI70129 -&gt; DPI63871 -&gt; DPI64610</t>
         </is>
       </c>
       <c r="E96" t="n">
         <v>321.0171</v>
       </c>
       <c r="F96" t="n">
-        <v>1331.431670715557</v>
+        <v>496.5059663172007</v>
       </c>
       <c r="G96" t="n">
-        <v>112022.4774511818</v>
+        <v>91157.68409826685</v>
       </c>
     </row>
     <row r="97">
@@ -2852,17 +2852,17 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>DPI67252, DFT80069, DPI67235, DPI64205</t>
+          <t>DPI67252 -&gt; DFT80069 -&gt; DPI67235 -&gt; DPI64205</t>
         </is>
       </c>
       <c r="E97" t="n">
         <v>1188.9684</v>
       </c>
       <c r="F97" t="n">
-        <v>3090.98101118909</v>
+        <v>782.2969086544604</v>
       </c>
       <c r="G97" t="n">
-        <v>200307.086977114</v>
+        <v>124559.1615729528</v>
       </c>
     </row>
     <row r="98">
@@ -2877,17 +2877,17 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>DPI70321, DPI63834</t>
+          <t>DPI70321 -&gt; DPI63834</t>
         </is>
       </c>
       <c r="E98" t="n">
         <v>1004.718992</v>
       </c>
       <c r="F98" t="n">
-        <v>1902.911194620171</v>
+        <v>1362.663404144986</v>
       </c>
       <c r="G98" t="n">
-        <v>161326.5162954878</v>
+        <v>143600.986289997</v>
       </c>
     </row>
     <row r="99">
@@ -2902,17 +2902,17 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>DPI63843, DPI63905, DPI64204, DPI70182</t>
+          <t>DPI63843 -&gt; DPI70182 -&gt; DPI64204 -&gt; DPI63905</t>
         </is>
       </c>
       <c r="E99" t="n">
         <v>1097.6534</v>
       </c>
       <c r="F99" t="n">
-        <v>4034.7875945488</v>
+        <v>1171.455934532805</v>
       </c>
       <c r="G99" t="n">
-        <v>231273.3809771462</v>
+        <v>137327.4692120213</v>
       </c>
     </row>
     <row r="100">
@@ -2927,17 +2927,17 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>DPI64084, DPI66904, DPI64030, DPI64349, DPI64286</t>
+          <t>DPI64084 -&gt; DPI66904 -&gt; DPI64030 -&gt; DPI64349 -&gt; DPI64286</t>
         </is>
       </c>
       <c r="E100" t="n">
         <v>626.8172970000001</v>
       </c>
       <c r="F100" t="n">
-        <v>5621.475577411361</v>
+        <v>1236.792837359789</v>
       </c>
       <c r="G100" t="n">
-        <v>246199.6244446756</v>
+        <v>121323.8600080068</v>
       </c>
     </row>
     <row r="101">
@@ -2952,17 +2952,17 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>DPI70309, DPI67135, DPI70018, DPI70242, DPI64549, DPI66441, DPI65995, DPI66445</t>
+          <t>DPI70309 -&gt; DPI67135 -&gt; DPI70242 -&gt; DPI64549 -&gt; DPI66441 -&gt; DPI65995 -&gt; DPI66445 -&gt; DPI70018</t>
         </is>
       </c>
       <c r="E101" t="n">
         <v>1009.0595105</v>
       </c>
       <c r="F101" t="n">
-        <v>91.73551571635204</v>
+        <v>23.58376126529379</v>
       </c>
       <c r="G101" t="n">
-        <v>101901.8422706535</v>
+        <v>99665.78320711429</v>
       </c>
     </row>
     <row r="102">
@@ -2977,17 +2977,17 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>DPI64683, DPI64122, DPI70144, DPI64494, DPI70323, DPI67086</t>
+          <t>DPI64683 -&gt; DPI64122 -&gt; DPI64494 -&gt; DPI67086 -&gt; DPI70144 -&gt; DPI70323</t>
         </is>
       </c>
       <c r="E102" t="n">
         <v>651.2168534</v>
       </c>
       <c r="F102" t="n">
-        <v>158.193720352646</v>
+        <v>63.54210509166184</v>
       </c>
       <c r="G102" t="n">
-        <v>90605.35715564336</v>
+        <v>87909.67915301053</v>
       </c>
     </row>
     <row r="103">
@@ -3002,17 +3002,17 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>DPI64434, DPI66500, DPI64005</t>
+          <t>DPI64434 -&gt; DPI66500 -&gt; DPI64005</t>
         </is>
       </c>
       <c r="E103" t="n">
         <v>343.41081056</v>
       </c>
       <c r="F103" t="n">
-        <v>230.9984849200232</v>
+        <v>99.14331195660742</v>
       </c>
       <c r="G103" t="n">
-        <v>84522.65213815137</v>
+        <v>81227.59136579563</v>
       </c>
     </row>
     <row r="104">
@@ -3052,17 +3052,17 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>DPI64702, DPI64390, DPI64654, DPI64629, DPI70303, DPI70186, DPI64737</t>
+          <t>DPI64702 -&gt; DPI64390 -&gt; DPI64654 -&gt; DPI64629 -&gt; DPI70303 -&gt; DPI70186 -&gt; DPI64737</t>
         </is>
       </c>
       <c r="E105" t="n">
         <v>613.14582532</v>
       </c>
       <c r="F105" t="n">
-        <v>2521.471546397088</v>
+        <v>1020.965337131069</v>
       </c>
       <c r="G105" t="n">
-        <v>157911.5096413891</v>
+        <v>115177.0928014929</v>
       </c>
     </row>
     <row r="106">
@@ -3077,17 +3077,17 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>DPI66620, DPI64226, DPI66927, DPI64655</t>
+          <t>DPI66620 -&gt; DPI64226 -&gt; DPI66927 -&gt; DPI64655</t>
         </is>
       </c>
       <c r="E106" t="n">
         <v>472.6964023</v>
       </c>
       <c r="F106" t="n">
-        <v>3472.461820484029</v>
+        <v>1111.32597474315</v>
       </c>
       <c r="G106" t="n">
-        <v>184995.7126473851</v>
+        <v>117750.5637606849</v>
       </c>
     </row>
   </sheetData>

--- a/secondary_logistics_routes.xlsx
+++ b/secondary_logistics_routes.xlsx
@@ -461,7 +461,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>route_cost</t>
+          <t>monthly_route_cost</t>
         </is>
       </c>
     </row>
@@ -487,7 +487,7 @@
         <v>43.46942819675499</v>
       </c>
       <c r="G2" t="n">
-        <v>87338.00931504359</v>
+        <v>98480.09315043582</v>
       </c>
     </row>
     <row r="3">
@@ -512,7 +512,7 @@
         <v>137.1013903889973</v>
       </c>
       <c r="G3" t="n">
-        <v>66785.1727382605</v>
+        <v>91401.72738260496</v>
       </c>
     </row>
     <row r="4">
@@ -537,7 +537,7 @@
         <v>134.2947994573659</v>
       </c>
       <c r="G4" t="n">
-        <v>66729.18124917445</v>
+        <v>90841.81249174449</v>
       </c>
     </row>
     <row r="5">
@@ -562,7 +562,7 @@
         <v>368.5993169800281</v>
       </c>
       <c r="G5" t="n">
-        <v>87961.2969313309</v>
+        <v>170862.969313309</v>
       </c>
     </row>
     <row r="6">
@@ -587,7 +587,7 @@
         <v>533.1915497261534</v>
       </c>
       <c r="G6" t="n">
-        <v>92074.45682765657</v>
+        <v>211994.5682765657</v>
       </c>
     </row>
     <row r="7">
@@ -612,7 +612,7 @@
         <v>526.3935180540061</v>
       </c>
       <c r="G7" t="n">
-        <v>101091.6873941781</v>
+        <v>236016.8739417809</v>
       </c>
     </row>
     <row r="8">
@@ -637,7 +637,7 @@
         <v>296.8217307442487</v>
       </c>
       <c r="G8" t="n">
-        <v>86167.57505129877</v>
+        <v>152925.7505129878</v>
       </c>
     </row>
     <row r="9">
@@ -662,7 +662,7 @@
         <v>276.7577793159488</v>
       </c>
       <c r="G9" t="n">
-        <v>69571.31769735318</v>
+        <v>119263.1769735318</v>
       </c>
     </row>
     <row r="10">
@@ -687,7 +687,7 @@
         <v>285.0466941086402</v>
       </c>
       <c r="G10" t="n">
-        <v>85873.31688577491</v>
+        <v>149983.1688577492</v>
       </c>
     </row>
     <row r="11">
@@ -712,7 +712,7 @@
         <v>275.9108540825973</v>
       </c>
       <c r="G11" t="n">
-        <v>85645.01224352411</v>
+        <v>147700.1224352411</v>
       </c>
     </row>
     <row r="12">
@@ -737,7 +737,7 @@
         <v>725.757176473101</v>
       </c>
       <c r="G12" t="n">
-        <v>122704.0929600824</v>
+        <v>337012.9296008245</v>
       </c>
     </row>
     <row r="13">
@@ -762,7 +762,7 @@
         <v>902.6241608899024</v>
       </c>
       <c r="G13" t="n">
-        <v>128507.0987187977</v>
+        <v>395042.987187977</v>
       </c>
     </row>
     <row r="14">
@@ -787,7 +787,7 @@
         <v>515.8892308925966</v>
       </c>
       <c r="G14" t="n">
-        <v>91642.07188000598</v>
+        <v>207670.7188000599</v>
       </c>
     </row>
     <row r="15">
@@ -812,7 +812,7 @@
         <v>538.2622643052007</v>
       </c>
       <c r="G15" t="n">
-        <v>92201.17398498696</v>
+        <v>213261.7398498697</v>
       </c>
     </row>
     <row r="16">
@@ -837,7 +837,7 @@
         <v>807.2826872166887</v>
       </c>
       <c r="G16" t="n">
-        <v>98923.99435354504</v>
+        <v>280489.9435354505</v>
       </c>
     </row>
     <row r="17">
@@ -862,7 +862,7 @@
         <v>1233.537444888914</v>
       </c>
       <c r="G17" t="n">
-        <v>139364.3635668053</v>
+        <v>503615.6356680528</v>
       </c>
     </row>
     <row r="18">
@@ -887,7 +887,7 @@
         <v>1173.437149199483</v>
       </c>
       <c r="G18" t="n">
-        <v>137392.472865235</v>
+        <v>483896.7286523503</v>
       </c>
     </row>
     <row r="19">
@@ -912,7 +912,7 @@
         <v>1551.117640800664</v>
       </c>
       <c r="G19" t="n">
-        <v>117512.4298436086</v>
+        <v>466374.2984360859</v>
       </c>
     </row>
     <row r="20">
@@ -937,7 +937,7 @@
         <v>1825.237845342925</v>
       </c>
       <c r="G20" t="n">
-        <v>138082.7738353665</v>
+        <v>605927.738353665</v>
       </c>
     </row>
     <row r="21">
@@ -987,7 +987,7 @@
         <v>388.1028766516076</v>
       </c>
       <c r="G22" t="n">
-        <v>97153.16992703779</v>
+        <v>196631.6992703778</v>
       </c>
     </row>
     <row r="23">
@@ -1012,7 +1012,7 @@
         <v>850.7110758840822</v>
       </c>
       <c r="G23" t="n">
-        <v>110328.2514411787</v>
+        <v>328382.5144117866</v>
       </c>
     </row>
     <row r="24">
@@ -1037,7 +1037,7 @@
         <v>502.8336648803545</v>
       </c>
       <c r="G24" t="n">
-        <v>74081.53161436308</v>
+        <v>164365.3161436307</v>
       </c>
     </row>
     <row r="25">
@@ -1062,7 +1062,7 @@
         <v>399.04152217355</v>
       </c>
       <c r="G25" t="n">
-        <v>72010.87836736233</v>
+        <v>143658.7836736232</v>
       </c>
     </row>
     <row r="26">
@@ -1087,7 +1087,7 @@
         <v>399.1664633033907</v>
       </c>
       <c r="G26" t="n">
-        <v>72013.37094290265</v>
+        <v>143683.7094290264</v>
       </c>
     </row>
     <row r="27">
@@ -1112,7 +1112,7 @@
         <v>399.1949303881932</v>
       </c>
       <c r="G27" t="n">
-        <v>72013.93886124446</v>
+        <v>143689.3886124445</v>
       </c>
     </row>
     <row r="28">
@@ -1137,7 +1137,7 @@
         <v>922.4731099182513</v>
       </c>
       <c r="G28" t="n">
-        <v>112372.0341704718</v>
+        <v>348820.341704718</v>
       </c>
     </row>
     <row r="29">
@@ -1162,7 +1162,7 @@
         <v>458.4096633804866</v>
       </c>
       <c r="G29" t="n">
-        <v>73195.27278444071</v>
+        <v>155502.7278444071</v>
       </c>
     </row>
     <row r="30">
@@ -1187,7 +1187,7 @@
         <v>487.6654235666871</v>
       </c>
       <c r="G30" t="n">
-        <v>90936.75893493151</v>
+        <v>200617.5893493151</v>
       </c>
     </row>
     <row r="31">
@@ -1212,7 +1212,7 @@
         <v>469.0117179012091</v>
       </c>
       <c r="G31" t="n">
-        <v>90470.60283035121</v>
+        <v>195956.0283035121</v>
       </c>
     </row>
     <row r="32">
@@ -1237,7 +1237,7 @@
         <v>926.4025676681233</v>
       </c>
       <c r="G32" t="n">
-        <v>112483.9451271882</v>
+        <v>349939.4512718815</v>
       </c>
     </row>
     <row r="33">
@@ -1262,7 +1262,7 @@
         <v>930.3305622703397</v>
       </c>
       <c r="G33" t="n">
-        <v>101998.9607511358</v>
+        <v>311239.6075113579</v>
       </c>
     </row>
     <row r="34">
@@ -1287,7 +1287,7 @@
         <v>477.0342821566059</v>
       </c>
       <c r="G34" t="n">
-        <v>73566.83392902429</v>
+        <v>159218.3392902429</v>
       </c>
     </row>
     <row r="35">
@@ -1312,7 +1312,7 @@
         <v>484.2416578484302</v>
       </c>
       <c r="G35" t="n">
-        <v>90851.19902963228</v>
+        <v>199761.9902963227</v>
       </c>
     </row>
     <row r="36">
@@ -1337,7 +1337,7 @@
         <v>501.8633351957513</v>
       </c>
       <c r="G36" t="n">
-        <v>100393.067786375</v>
+        <v>229030.67786375</v>
       </c>
     </row>
     <row r="37">
@@ -1362,7 +1362,7 @@
         <v>1596.491015022981</v>
       </c>
       <c r="G37" t="n">
-        <v>131568.0641078545</v>
+        <v>540780.641078545</v>
       </c>
     </row>
     <row r="38">
@@ -1387,7 +1387,7 @@
         <v>915.2616410909682</v>
       </c>
       <c r="G38" t="n">
-        <v>128921.7344441947</v>
+        <v>399189.3444419467</v>
       </c>
     </row>
     <row r="39">
@@ -1412,7 +1412,7 @@
         <v>1777.219274370255</v>
       </c>
       <c r="G39" t="n">
-        <v>157202.5643920881</v>
+        <v>681997.6439208809</v>
       </c>
     </row>
     <row r="40">
@@ -1437,7 +1437,7 @@
         <v>917.3498458105961</v>
       </c>
       <c r="G40" t="n">
-        <v>82351.12942392139</v>
+        <v>247061.2942392139</v>
       </c>
     </row>
     <row r="41">
@@ -1462,7 +1462,7 @@
         <v>1750.941400284894</v>
       </c>
       <c r="G41" t="n">
-        <v>122506.0255931195</v>
+        <v>516310.255931195</v>
       </c>
     </row>
     <row r="42">
@@ -1487,7 +1487,7 @@
         <v>1264.224626669494</v>
       </c>
       <c r="G42" t="n">
-        <v>110342.9734204707</v>
+        <v>394679.7342047066</v>
       </c>
     </row>
     <row r="43">
@@ -1512,7 +1512,7 @@
         <v>165.7603039122733</v>
       </c>
       <c r="G43" t="n">
-        <v>82892.3499947677</v>
+        <v>120173.4999476771</v>
       </c>
     </row>
     <row r="44">
@@ -1537,7 +1537,7 @@
         <v>199.9099514532233</v>
       </c>
       <c r="G44" t="n">
-        <v>83745.74968681605</v>
+        <v>128707.4968681605</v>
       </c>
     </row>
     <row r="45">
@@ -1562,7 +1562,7 @@
         <v>184.9738277624375</v>
       </c>
       <c r="G45" t="n">
-        <v>67740.22786386062</v>
+        <v>100952.2786386063</v>
       </c>
     </row>
     <row r="46">
@@ -1587,7 +1587,7 @@
         <v>190.8797116503079</v>
       </c>
       <c r="G46" t="n">
-        <v>83520.0839941412</v>
+        <v>126450.8399414119</v>
       </c>
     </row>
     <row r="47">
@@ -1612,7 +1612,7 @@
         <v>202.8545068429208</v>
       </c>
       <c r="G47" t="n">
-        <v>105547.6563695162</v>
+        <v>165448.5636951623</v>
       </c>
     </row>
     <row r="48">
@@ -1637,7 +1637,7 @@
         <v>797.0558633621556</v>
       </c>
       <c r="G48" t="n">
-        <v>108800.1509885542</v>
+        <v>313101.5098855419</v>
       </c>
     </row>
     <row r="49">
@@ -1662,7 +1662,7 @@
         <v>668.0261888267878</v>
       </c>
       <c r="G49" t="n">
-        <v>105125.3858577869</v>
+        <v>276353.8585778692</v>
       </c>
     </row>
     <row r="50">
@@ -1687,7 +1687,7 @@
         <v>876.8393249252302</v>
       </c>
       <c r="G50" t="n">
-        <v>127661.0982507968</v>
+        <v>386582.9825079681</v>
       </c>
     </row>
     <row r="51">
@@ -1712,7 +1712,7 @@
         <v>425.0427875226114</v>
       </c>
       <c r="G51" t="n">
-        <v>89371.81926019005</v>
+        <v>184968.1926019006</v>
       </c>
     </row>
     <row r="52">
@@ -1737,7 +1737,7 @@
         <v>430.0531118874321</v>
       </c>
       <c r="G52" t="n">
-        <v>89497.02726606693</v>
+        <v>186220.2726606693</v>
       </c>
     </row>
     <row r="53">
@@ -1762,7 +1762,7 @@
         <v>1557.328733483469</v>
       </c>
       <c r="G53" t="n">
-        <v>149987.9557455926</v>
+        <v>609851.5574559262</v>
       </c>
     </row>
     <row r="54">
@@ -1787,7 +1787,7 @@
         <v>1770.720356264008</v>
       </c>
       <c r="G54" t="n">
-        <v>123000.3017030375</v>
+        <v>521253.0170303755</v>
       </c>
     </row>
     <row r="55">
@@ -1812,7 +1812,7 @@
         <v>1194.400756043251</v>
       </c>
       <c r="G55" t="n">
-        <v>108598.0748935208</v>
+        <v>377230.7489352084</v>
       </c>
     </row>
     <row r="56">
@@ -1837,7 +1837,7 @@
         <v>700.2236885152075</v>
       </c>
       <c r="G56" t="n">
-        <v>78019.46258587838</v>
+        <v>203744.6258587839</v>
       </c>
     </row>
     <row r="57">
@@ -1862,7 +1862,7 @@
         <v>1149.362337677768</v>
       </c>
       <c r="G57" t="n">
-        <v>118833.8393770628</v>
+        <v>413438.3937706284</v>
       </c>
     </row>
     <row r="58">
@@ -1887,7 +1887,7 @@
         <v>2104.594631462105</v>
       </c>
       <c r="G58" t="n">
-        <v>146038.8551040407</v>
+        <v>685488.5510404074</v>
       </c>
     </row>
     <row r="59">
@@ -1912,7 +1912,7 @@
         <v>2118.672848779382</v>
       </c>
       <c r="G59" t="n">
-        <v>146439.8027332368</v>
+        <v>689498.027332368</v>
       </c>
     </row>
     <row r="60">
@@ -1937,7 +1937,7 @@
         <v>841.2896834820029</v>
       </c>
       <c r="G60" t="n">
-        <v>110059.9301855674</v>
+        <v>325699.3018556745</v>
       </c>
     </row>
     <row r="61">
@@ -1962,7 +1962,7 @@
         <v>1920.131362158535</v>
       </c>
       <c r="G61" t="n">
-        <v>140785.3411942751</v>
+        <v>632953.4119427507</v>
       </c>
     </row>
     <row r="62">
@@ -1987,7 +1987,7 @@
         <v>1258.15430281568</v>
       </c>
       <c r="G62" t="n">
-        <v>121932.2345441906</v>
+        <v>444422.3454419057</v>
       </c>
     </row>
     <row r="63">
@@ -2012,7 +2012,7 @@
         <v>1332.589494907853</v>
       </c>
       <c r="G63" t="n">
-        <v>112051.4114777472</v>
+        <v>411764.1147774725</v>
       </c>
     </row>
     <row r="64">
@@ -2037,7 +2037,7 @@
         <v>44.42178865891638</v>
       </c>
       <c r="G64" t="n">
-        <v>79860.10049858633</v>
+        <v>89851.0049858632</v>
       </c>
     </row>
     <row r="65">
@@ -2062,7 +2062,7 @@
         <v>197.9088171345552</v>
       </c>
       <c r="G65" t="n">
-        <v>67998.28090183437</v>
+        <v>103532.8090183438</v>
       </c>
     </row>
     <row r="66">
@@ -2087,7 +2087,7 @@
         <v>246.0671157761433</v>
       </c>
       <c r="G66" t="n">
-        <v>106965.4620686153</v>
+        <v>179626.6206861526</v>
       </c>
     </row>
     <row r="67">
@@ -2112,7 +2112,7 @@
         <v>490.1938041679894</v>
       </c>
       <c r="G67" t="n">
-        <v>114975.2587147517</v>
+        <v>259724.5871475173</v>
       </c>
     </row>
     <row r="68">
@@ -2137,7 +2137,7 @@
         <v>257.4381857812567</v>
       </c>
       <c r="G68" t="n">
-        <v>93431.83953105019</v>
+        <v>159418.3953105019</v>
       </c>
     </row>
     <row r="69">
@@ -2162,7 +2162,7 @@
         <v>273.7890505047844</v>
       </c>
       <c r="G69" t="n">
-        <v>107875.018747062</v>
+        <v>188722.1874706198</v>
       </c>
     </row>
     <row r="70">
@@ -2187,7 +2187,7 @@
         <v>293.0113364446653</v>
       </c>
       <c r="G70" t="n">
-        <v>108505.7019487495</v>
+        <v>195029.0194874947</v>
       </c>
     </row>
     <row r="71">
@@ -2212,7 +2212,7 @@
         <v>270.7011416285878</v>
       </c>
       <c r="G71" t="n">
-        <v>93809.56851358218</v>
+        <v>163195.6851358218</v>
       </c>
     </row>
     <row r="72">
@@ -2237,7 +2237,7 @@
         <v>267.4195017856523</v>
       </c>
       <c r="G72" t="n">
-        <v>85432.81334962345</v>
+        <v>145578.1334962345</v>
       </c>
     </row>
     <row r="73">
@@ -2262,7 +2262,7 @@
         <v>263.3495786151545</v>
       </c>
       <c r="G73" t="n">
-        <v>69303.82409337233</v>
+        <v>116588.2409337233</v>
       </c>
     </row>
     <row r="74">
@@ -2287,7 +2287,7 @@
         <v>272.3753738607775</v>
       </c>
       <c r="G74" t="n">
-        <v>85556.66059278083</v>
+        <v>146816.6059278083</v>
       </c>
     </row>
     <row r="75">
@@ -2312,7 +2312,7 @@
         <v>275.7012910726287</v>
       </c>
       <c r="G75" t="n">
-        <v>85639.77526390499</v>
+        <v>147647.7526390499</v>
       </c>
     </row>
     <row r="76">
@@ -2337,7 +2337,7 @@
         <v>285.8778413154109</v>
       </c>
       <c r="G76" t="n">
-        <v>85894.08725447212</v>
+        <v>150190.8725447212</v>
       </c>
     </row>
     <row r="77">
@@ -2362,7 +2362,7 @@
         <v>268.7863980540556</v>
       </c>
       <c r="G77" t="n">
-        <v>69412.28864117841</v>
+        <v>117672.8864117841</v>
       </c>
     </row>
     <row r="78">
@@ -2387,7 +2387,7 @@
         <v>288.7751695832079</v>
       </c>
       <c r="G78" t="n">
-        <v>69811.064633185</v>
+        <v>121660.64633185</v>
       </c>
     </row>
     <row r="79">
@@ -2412,7 +2412,7 @@
         <v>296.907209287421</v>
       </c>
       <c r="G79" t="n">
-        <v>108633.5255367203</v>
+        <v>196307.2553672028</v>
       </c>
     </row>
     <row r="80">
@@ -2437,7 +2437,7 @@
         <v>297.7172279449737</v>
       </c>
       <c r="G80" t="n">
-        <v>94578.98665187285</v>
+        <v>170889.8665187285</v>
       </c>
     </row>
     <row r="81">
@@ -2462,7 +2462,7 @@
         <v>278.6798782223319</v>
       </c>
       <c r="G81" t="n">
-        <v>69609.66357053551</v>
+        <v>119646.6357053552</v>
       </c>
     </row>
     <row r="82">
@@ -2487,7 +2487,7 @@
         <v>291.1457885229876</v>
       </c>
       <c r="G82" t="n">
-        <v>94391.83205713468</v>
+        <v>169018.3205713468</v>
       </c>
     </row>
     <row r="83">
@@ -2512,7 +2512,7 @@
         <v>663.6163567022193</v>
       </c>
       <c r="G83" t="n">
-        <v>104999.7938388792</v>
+        <v>275097.9383887921</v>
       </c>
     </row>
     <row r="84">
@@ -2537,7 +2537,7 @@
         <v>1115.637800892066</v>
       </c>
       <c r="G84" t="n">
-        <v>106629.7886442927</v>
+        <v>357547.8864429273</v>
       </c>
     </row>
     <row r="85">
@@ -2562,7 +2562,7 @@
         <v>1163.141949882287</v>
       </c>
       <c r="G85" t="n">
-        <v>119226.2827326475</v>
+        <v>417362.8273264752</v>
       </c>
     </row>
     <row r="86">
@@ -2587,7 +2587,7 @@
         <v>1581.927617644406</v>
       </c>
       <c r="G86" t="n">
-        <v>95609.4559720059</v>
+        <v>379644.559720059</v>
       </c>
     </row>
     <row r="87">
@@ -2612,7 +2612,7 @@
         <v>1343.916324211989</v>
       </c>
       <c r="G87" t="n">
-        <v>112334.4689420576</v>
+        <v>414594.6894205761</v>
       </c>
     </row>
     <row r="88">
@@ -2637,7 +2637,7 @@
         <v>976.7605089881511</v>
       </c>
       <c r="G88" t="n">
-        <v>113918.1392959825</v>
+        <v>364281.3929598254</v>
       </c>
     </row>
     <row r="89">
@@ -2662,7 +2662,7 @@
         <v>1091.769728310716</v>
       </c>
       <c r="G89" t="n">
-        <v>106033.3255104848</v>
+        <v>351583.2551048479</v>
       </c>
     </row>
     <row r="90">
@@ -2687,7 +2687,7 @@
         <v>1355.345101984429</v>
       </c>
       <c r="G90" t="n">
-        <v>124700.2285045165</v>
+        <v>472102.2850451654</v>
       </c>
     </row>
     <row r="91">
@@ -2712,7 +2712,7 @@
         <v>990.1562603971061</v>
       </c>
       <c r="G91" t="n">
-        <v>83803.61739492227</v>
+        <v>261586.1739492227</v>
       </c>
     </row>
     <row r="92">
@@ -2737,7 +2737,7 @@
         <v>2040.577261524614</v>
       </c>
       <c r="G92" t="n">
-        <v>129744.0257655001</v>
+        <v>588690.257655001</v>
       </c>
     </row>
     <row r="93">
@@ -2762,7 +2762,7 @@
         <v>261.9494428119992</v>
       </c>
       <c r="G93" t="n">
-        <v>93560.32013128574</v>
+        <v>160703.2013128574</v>
       </c>
     </row>
     <row r="94">
@@ -2787,7 +2787,7 @@
         <v>267.3574828392963</v>
       </c>
       <c r="G94" t="n">
-        <v>107663.9990119573</v>
+        <v>186611.9901195731</v>
       </c>
     </row>
     <row r="95">
@@ -2812,7 +2812,7 @@
         <v>267.0573933100857</v>
       </c>
       <c r="G95" t="n">
-        <v>107654.1530745039</v>
+        <v>186513.5307450391</v>
       </c>
     </row>
     <row r="96">
@@ -2837,7 +2837,7 @@
         <v>496.5059663172007</v>
       </c>
       <c r="G96" t="n">
-        <v>91157.68409826685</v>
+        <v>202826.8409826685</v>
       </c>
     </row>
     <row r="97">
@@ -2862,7 +2862,7 @@
         <v>782.2969086544604</v>
       </c>
       <c r="G97" t="n">
-        <v>124559.1615729528</v>
+        <v>355563.6157295285</v>
       </c>
     </row>
     <row r="98">
@@ -2887,7 +2887,7 @@
         <v>1362.663404144986</v>
       </c>
       <c r="G98" t="n">
-        <v>143600.986289997</v>
+        <v>545981.86289997</v>
       </c>
     </row>
     <row r="99">
@@ -2912,7 +2912,7 @@
         <v>1171.455934532805</v>
       </c>
       <c r="G99" t="n">
-        <v>137327.4692120213</v>
+        <v>483246.6921202134</v>
       </c>
     </row>
     <row r="100">
@@ -2937,7 +2937,7 @@
         <v>1236.792837359789</v>
       </c>
       <c r="G100" t="n">
-        <v>121323.8600080068</v>
+        <v>438338.600080068</v>
       </c>
     </row>
     <row r="101">
@@ -2962,7 +2962,7 @@
         <v>23.58376126529379</v>
       </c>
       <c r="G101" t="n">
-        <v>99665.78320711429</v>
+        <v>106629.8320711429</v>
       </c>
     </row>
     <row r="102">
@@ -2987,7 +2987,7 @@
         <v>63.54210509166184</v>
       </c>
       <c r="G102" t="n">
-        <v>87909.67915301053</v>
+        <v>104196.7915301053</v>
       </c>
     </row>
     <row r="103">
@@ -3012,7 +3012,7 @@
         <v>99.14331195660742</v>
       </c>
       <c r="G103" t="n">
-        <v>81227.59136579563</v>
+        <v>103525.9136579562</v>
       </c>
     </row>
     <row r="104">
@@ -3037,7 +3037,7 @@
         <v>85.33204615383583</v>
       </c>
       <c r="G104" t="n">
-        <v>65752.37432076903</v>
+        <v>81073.74320769025</v>
       </c>
     </row>
     <row r="105">
@@ -3062,7 +3062,7 @@
         <v>1020.965337131069</v>
       </c>
       <c r="G105" t="n">
-        <v>115177.0928014929</v>
+        <v>376870.9280149285</v>
       </c>
     </row>
     <row r="106">
@@ -3087,7 +3087,7 @@
         <v>1111.32597474315</v>
       </c>
       <c r="G106" t="n">
-        <v>117750.5637606849</v>
+        <v>402605.6376068491</v>
       </c>
     </row>
   </sheetData>

--- a/secondary_logistics_routes.xlsx
+++ b/secondary_logistics_routes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,15 +451,25 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>total_load_cft</t>
+          <t>route_load_cft</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>truck_capacity_cft</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>truck_utilization_percent</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>route_distance_km</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>monthly_route_cost</t>
         </is>
@@ -473,146 +483,1763 @@
         <v>1613</v>
       </c>
       <c r="C2" t="n">
-        <v>92</v>
+        <v>8</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DPI64254 -&gt; DPI66669 -&gt; DPI66594 -&gt; DPI66372 -&gt; DPI64247 -&gt; DPI64091 -&gt; DPI70040 -&gt; DPI64191 -&gt; DPI70090 -&gt; DPI64239 -&gt; DPI64045 -&gt; DPI66503 -&gt; DPI64024 -&gt; DPI67047 -&gt; DPI64361 -&gt; DPI65875 -&gt; DPI63898 -&gt; DPI64543 -&gt; DPI64253 -&gt; DPI66748 -&gt; DPI66127 -&gt; DPI66329 -&gt; DPI65841 -&gt; DPI64563 -&gt; DPI64137 -&gt; DPI63902 -&gt; DPI64299 -&gt; DPI64001 -&gt; DPI64590 -&gt; DPI64400 -&gt; DPI64281 -&gt; DPI64561 -&gt; DPI65827 -&gt; DPI66974 -&gt; DPI70327 -&gt; DPI67214 -&gt; DPI70254 -&gt; DPI66511 -&gt; DPI66512 -&gt; DPI66265 -&gt; DPI65825 -&gt; DPI65967 -&gt; DPI64364 -&gt; DPI65824 -&gt; DPI64513 -&gt; DPI65981 -&gt; DPI65927 -&gt; DPI67043 -&gt; DPI67245 -&gt; DPI64711 -&gt; DPI70082 -&gt; DPI70221 -&gt; DPI64694 -&gt; DPI64462 -&gt; DPI64606 -&gt; DPI66995 -&gt; DPI70031 -&gt; DPI66461 -&gt; DPI70165 -&gt; DPI66555 -&gt; DPI66100 -&gt; DPI64175 -&gt; DPI67004 -&gt; DPI64619 -&gt; DPI66060 -&gt; DPI64085 -&gt; DPI70234 -&gt; DPI66491 -&gt; DPI66380 -&gt; DPI66953 -&gt; DPI66759 -&gt; DPI66395 -&gt; DPI64374 -&gt; DPI66091 -&gt; DPI70095 -&gt; DPI63904 -&gt; DPI70166 -&gt; DPI63929 -&gt; DPI64118 -&gt; DPI64644 -&gt; DPI67002 -&gt; DPI67138 -&gt; DPI66938 -&gt; DPI64108 -&gt; DPI70149 -&gt; DPI70035 -&gt; DPI64008 -&gt; DPI67102 -&gt; DPI66915 -&gt; DPI64506 -&gt; DPI64000 -&gt; DPI70228</t>
+          <t>DPI66995 -&gt; DPI70031 -&gt; DPI66461 -&gt; DPI66555 -&gt; DPI70234 -&gt; DPI66380 -&gt; DPI66395 -&gt; DPI63929</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8928.772518490001</v>
+        <v>901.76759583</v>
       </c>
       <c r="F2" t="n">
-        <v>3691.980204444936</v>
+        <v>980</v>
       </c>
       <c r="G2" t="n">
-        <v>1310230.705078384</v>
+        <v>92.01710161530612</v>
+      </c>
+      <c r="H2" t="n">
+        <v>915</v>
+      </c>
+      <c r="I2" t="n">
+        <v>399103.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B3" t="n">
         <v>1613</v>
       </c>
       <c r="C3" t="n">
-        <v>83</v>
+        <v>10</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DPI66264 -&gt; DPI64104 -&gt; DPI64273 -&gt; DPI66900 -&gt; DPI64179 -&gt; DPI70197 -&gt; DPI63847 -&gt; DPI66144 -&gt; DPI70273 -&gt; DPI70179 -&gt; DPI64651 -&gt; DPI66262 -&gt; DPI70302 -&gt; DFT80087 -&gt; DPI64559 -&gt; DPI66092 -&gt; DPI64484 -&gt; DPI66327 -&gt; DPI66229 -&gt; DPI63817 -&gt; DPI63895 -&gt; DPI64511 -&gt; DPI66508 -&gt; DFT80034 -&gt; DFT80066 -&gt; DPI66335 -&gt; DPI70002 -&gt; DPI70106 -&gt; DFT80081 -&gt; DPI64639 -&gt; DPI66684 -&gt; DPI67031 -&gt; DPI67024 -&gt; DPI64352 -&gt; DPI64288 -&gt; DPI70073 -&gt; DPI70038 -&gt; DPI64149 -&gt; DPI66734 -&gt; DPI64236 -&gt; DPI70041 -&gt; DPI66646 -&gt; DPI66175 -&gt; DPI70317 -&gt; DPI67198 -&gt; DPI64692 -&gt; DPI66528 -&gt; DPI63920 -&gt; DPI66659 -&gt; DPI70100 -&gt; DPI64303 -&gt; DPI67128 -&gt; DPI64255 -&gt; DPI63822 -&gt; DPI66421 -&gt; DPI64409 -&gt; DPI64378 -&gt; DPI64476 -&gt; DPI64032 -&gt; DPI66402 -&gt; DPI64647 -&gt; DPI64758 -&gt; DPI66263 -&gt; DPI64665 -&gt; DPI64502 -&gt; DPI70120 -&gt; DPI64696 -&gt; DPI64746 -&gt; DPI66618 -&gt; DPI64392 -&gt; DPI66408 -&gt; DPI66384 -&gt; DPI66102 -&gt; DPI64166 -&gt; DPI64624 -&gt; DPI64323 -&gt; DPI66692 -&gt; DPI64176 -&gt; DPI66460 -&gt; DPI64234 -&gt; DPI66572 -&gt; DPI63993 -&gt; DPI64044</t>
+          <t>DPI70165 -&gt; DPI67004 -&gt; DPI64175 -&gt; DPI66100 -&gt; DPI66491 -&gt; DPI66953 -&gt; DPI66759 -&gt; DPI64085 -&gt; DPI66060 -&gt; DPI64619</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>8514.17148911</v>
+        <v>955.8999013800001</v>
       </c>
       <c r="F3" t="n">
-        <v>4270.055128651869</v>
+        <v>980</v>
       </c>
       <c r="G3" t="n">
-        <v>1499897.087710678</v>
+        <v>97.54080626326531</v>
+      </c>
+      <c r="H3" t="n">
+        <v>626</v>
+      </c>
+      <c r="I3" t="n">
+        <v>304282.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B4" t="n">
         <v>1613</v>
       </c>
       <c r="C4" t="n">
-        <v>105</v>
+        <v>11</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DPI70142 -&gt; DPI70109 -&gt; DPI64052 -&gt; DPI66179 -&gt; DPI66597 -&gt; DPI67121 -&gt; DPI64450 -&gt; DPI66039 -&gt; DPI66307 -&gt; DPI64638 -&gt; DPI63958 -&gt; DPI66203 -&gt; DPI66289 -&gt; DPI64039 -&gt; DPI66069 -&gt; DPI64301 -&gt; DPI66339 -&gt; DPI66387 -&gt; DPI64218 -&gt; DPI64686 -&gt; DPI66590 -&gt; DFT80044 -&gt; DPI64216 -&gt; DFT80088 -&gt; DPI70316 -&gt; DPI70255 -&gt; DPI66645 -&gt; DPI64413 -&gt; DPI64244 -&gt; DPI66128 -&gt; DPI64094 -&gt; DPI66715 -&gt; DPI64169 -&gt; DPI66051 -&gt; DPI63802 -&gt; DPI64057 -&gt; DPI66172 -&gt; DPI64037 -&gt; DPI70096 -&gt; DPI70009 -&gt; DPI66221 -&gt; DPI64196 -&gt; DPI66373 -&gt; DPI66153 -&gt; DPI67072 -&gt; DPI70081 -&gt; DPI66154 -&gt; DPI66576 -&gt; DPI66313 -&gt; DPI63827 -&gt; DPI64592 -&gt; DPI63919 -&gt; DPI66449 -&gt; DPI66653 -&gt; DPI64431 -&gt; DPI70047 -&gt; DPI66679 -&gt; DPI64136 -&gt; DPI64436 -&gt; DPI64456 -&gt; DPI66574 -&gt; DPI66946 -&gt; DPI66742 -&gt; DPI67178 -&gt; DPI64297 -&gt; DPI66067 -&gt; DPI70213 -&gt; DPI64724 -&gt; DPI63915 -&gt; DPI67148 -&gt; DPI64742 -&gt; DPI63976 -&gt; DPI64634 -&gt; DPI67224 -&gt; DPI66209 -&gt; DPI70190 -&gt; DPI64666 -&gt; DPI66636 -&gt; DFT80077 -&gt; DPI66923 -&gt; DFT80078 -&gt; DPI64119 -&gt; DPI64628 -&gt; DPI67074 -&gt; DPI64056 -&gt; DPI70253 -&gt; DPI67180 -&gt; DPI70296 -&gt; DPI70105 -&gt; DPI67187 -&gt; DPI66658 -&gt; DPI64433 -&gt; DPI66078 -&gt; DPI64480 -&gt; DPI66096 -&gt; DPI64018 -&gt; DPI70229 -&gt; DPI66736 -&gt; DPI66129 -&gt; DPI64495 -&gt; DFT80080 -&gt; DPI64548 -&gt; DPI70214 -&gt; DPI66634 -&gt; DPI70107</t>
+          <t>DPI64091 -&gt; DPI64239 -&gt; DPI64045 -&gt; DPI66503 -&gt; DPI64000 -&gt; DPI64506 -&gt; DPI66915 -&gt; DPI67102 -&gt; DPI70035 -&gt; DPI64008 -&gt; DPI70040</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>10639.66437254</v>
+        <v>945.71706717</v>
       </c>
       <c r="F4" t="n">
-        <v>4874.378219866247</v>
+        <v>980</v>
       </c>
       <c r="G4" t="n">
-        <v>1698175.493938116</v>
+        <v>96.50174154795917</v>
+      </c>
+      <c r="H4" t="n">
+        <v>656</v>
+      </c>
+      <c r="I4" t="n">
+        <v>314125.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B5" t="n">
         <v>1613</v>
       </c>
       <c r="C5" t="n">
-        <v>154</v>
+        <v>12</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DPI66929 -&gt; DPI66437 -&gt; DPI64600 -&gt; DPI70216 -&gt; DPI67093 -&gt; DPI70256 -&gt; DPI64043 -&gt; DPI64720 -&gt; DPI64741 -&gt; DPI66119 -&gt; DPI64203 -&gt; DPI67050 -&gt; DPI64279 -&gt; DPI66224 -&gt; DPI70058 -&gt; DPI64310 -&gt; DPI64317 -&gt; DPI64252 -&gt; DPI67062 -&gt; DPI66532 -&gt; DPI66125 -&gt; DPI64102 -&gt; DPI66029 -&gt; DPI64336 -&gt; DPI66497 -&gt; DPI64525 -&gt; DPI64145 -&gt; DPI64237 -&gt; DPI66640 -&gt; DPI63813 -&gt; DPI70022 -&gt; DPI70039 -&gt; DPI66239 -&gt; DPI66591 -&gt; DPI66944 -&gt; DPI66945 -&gt; DFT80058 -&gt; DPI66730 -&gt; DPI66104 -&gt; DPI64291 -&gt; DPI70032 -&gt; DPI66999 -&gt; DPI64641 -&gt; DPI63999 -&gt; DPI64079 -&gt; DPI66652 -&gt; DPI64703 -&gt; DPI63936 -&gt; DPI64246 -&gt; DPI66326 -&gt; DPI64418 -&gt; DPI66122 -&gt; DPI66729 -&gt; DPI64350 -&gt; DPI63945 -&gt; DPI66940 -&gt; DPI64428 -&gt; DPI64377 -&gt; DPI66626 -&gt; DPI70176 -&gt; DPI66578 -&gt; DPI67042 -&gt; DPI70057 -&gt; DPI66378 -&gt; DPI66094 -&gt; DPI66053 -&gt; DPI66685 -&gt; DPI70140 -&gt; DPI67064 -&gt; DPI66241 -&gt; DPI70091 -&gt; DPI66191 -&gt; DPI64331 -&gt; DPI65919 -&gt; DPI66377 -&gt; DPI64650 -&gt; DPI66126 -&gt; DPI65840 -&gt; DPI66410 -&gt; DPI66422 -&gt; DPI66014 -&gt; DPI64250 -&gt; DPI67118 -&gt; DPI67126 -&gt; DPI66970 -&gt; DPI64240 -&gt; DPI64227 -&gt; DPI66333 -&gt; DPI64408 -&gt; DPI66031 -&gt; DPI67181 -&gt; DPI66733 -&gt; DPI64752 -&gt; DPI63978 -&gt; DPI70306 -&gt; DPI66926 -&gt; DPI65877 -&gt; DPI66280 -&gt; DPI65998 -&gt; DPI64140 -&gt; DPI66538 -&gt; DPI67183 -&gt; DPI64602 -&gt; DPI67014 -&gt; DPI65779 -&gt; DPI66136 -&gt; DPI65969 -&gt; DPI63951 -&gt; DPI65789 -&gt; DPI66521 -&gt; DPI64631 -&gt; DPI64019 -&gt; DPI66660 -&gt; DPI66194 -&gt; DPI66076 -&gt; DPI66619 -&gt; DPI67217 -&gt; DPI66400 -&gt; DPI64520 -&gt; DPI66522 -&gt; DPI64577 -&gt; DPI66688 -&gt; DPI66042 -&gt; DPI70104 -&gt; DPI66359 -&gt; DPI63950 -&gt; DPI66389 -&gt; DPI64026 -&gt; DPI66755 -&gt; DPI66621 -&gt; DPI70320 -&gt; DFT80095 -&gt; DPI70069 -&gt; DPI67021 -&gt; DPI70148 -&gt; DPI64207 -&gt; DPI66622 -&gt; DPI70261 -&gt; DPI65993 -&gt; DPI64470 -&gt; DPI65915 -&gt; DPI66501 -&gt; DPI67179 -&gt; DPI66386 -&gt; DPI67110 -&gt; DPI66998 -&gt; DPI66573 -&gt; DPI63823 -&gt; DPI64469 -&gt; DPI64073 -&gt; DPI66548 -&gt; DPI64083 -&gt; DPI64106 -&gt; DPI64706</t>
+          <t>DPI64253 -&gt; DPI66748 -&gt; DPI66127 -&gt; DPI64563 -&gt; DPI66329 -&gt; DPI65841 -&gt; DPI64137 -&gt; DPI63902 -&gt; DPI64001 -&gt; DPI64299 -&gt; DPI64543 -&gt; DPI63898</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>13576.78934791999</v>
+        <v>974.8624757700002</v>
       </c>
       <c r="F5" t="n">
-        <v>3265.487377989844</v>
+        <v>980</v>
       </c>
       <c r="G5" t="n">
-        <v>1170298.408718468</v>
+        <v>99.47576283367349</v>
+      </c>
+      <c r="H5" t="n">
+        <v>833</v>
+      </c>
+      <c r="I5" t="n">
+        <v>372199.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B6" t="n">
         <v>1613</v>
       </c>
       <c r="C6" t="n">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DPI67040 -&gt; DFT80016 -&gt; DPI63872 -&gt; DPI64181 -&gt; DPI66463 -&gt; DPI66507 -&gt; DPI64190 -&gt; DPI66332 -&gt; DPI64040 -&gt; DPI70014 -&gt; DPI67069 -&gt; DPI66008 -&gt; DPI64424 -&gt; DFT80025 -&gt; DPI66487 -&gt; DPI64235 -&gt; DPI63862 -&gt; DPI66035 -&gt; DPI70051 -&gt; DPI64594 -&gt; DPI70126 -&gt; DPI64717 -&gt; DPI66290 -&gt; DPI70129 -&gt; DPI63871 -&gt; DPI64610 -&gt; DPI67252 -&gt; DFT80069 -&gt; DPI67235 -&gt; DPI64205 -&gt; DPI63843 -&gt; DPI63834 -&gt; DPI70182 -&gt; DPI64204 -&gt; DPI63905 -&gt; DPI64084 -&gt; DPI66904 -&gt; DPI64030 -&gt; DPI64349 -&gt; DPI64286 -&gt; DPI70321</t>
+          <t>DPI70327 -&gt; DPI64561 -&gt; DPI64281 -&gt; DPI66974 -&gt; DPI65827 -&gt; DPI67214 -&gt; DPI70254 -&gt; DPI66511 -&gt; DPI66512 -&gt; DPI70228 -&gt; DPI64400</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6668.978273000002</v>
+        <v>963.35313633</v>
       </c>
       <c r="F6" t="n">
-        <v>2127.40156000641</v>
+        <v>980</v>
       </c>
       <c r="G6" t="n">
-        <v>796892.4518381034</v>
+        <v>98.30134044183674</v>
+      </c>
+      <c r="H6" t="n">
+        <v>373</v>
+      </c>
+      <c r="I6" t="n">
+        <v>221273.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
+        <v>0</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>DPI66594 -&gt; DPI66372 -&gt; DPI64247 -&gt; DPI64191 -&gt; DPI70090 -&gt; DPI64024 -&gt; DPI67047 -&gt; DPI64361 -&gt; DPI65875 -&gt; DPI64590</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>981.6529681499999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>980</v>
+      </c>
+      <c r="G7" t="n">
+        <v>100.1686702193877</v>
+      </c>
+      <c r="H7" t="n">
+        <v>537</v>
+      </c>
+      <c r="I7" t="n">
+        <v>275081.7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>DPI70221 -&gt; DPI65967 -&gt; DPI64513 -&gt; DPI65824 -&gt; DPI65981 -&gt; DPI65927 -&gt; DPI67043 -&gt; DPI70082</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>929.7615670600001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>980</v>
+      </c>
+      <c r="G8" t="n">
+        <v>94.87362929183674</v>
+      </c>
+      <c r="H8" t="n">
+        <v>273</v>
+      </c>
+      <c r="I8" t="n">
+        <v>188463.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1109</v>
+      </c>
+      <c r="C9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>DPI66938 -&gt; DPI67138 -&gt; DPI67002 -&gt; DPI64644 -&gt; DPI64108 -&gt; DPI64254</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>634.46768466</v>
+      </c>
+      <c r="F9" t="n">
+        <v>660</v>
+      </c>
+      <c r="G9" t="n">
+        <v>96.13146737272727</v>
+      </c>
+      <c r="H9" t="n">
+        <v>962</v>
+      </c>
+      <c r="I9" t="n">
+        <v>360077.6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>0</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C10" t="n">
+        <v>8</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>DPI64462 -&gt; DPI64606 -&gt; DPI64711 -&gt; DPI67245 -&gt; DPI64364 -&gt; DPI65825 -&gt; DPI66265 -&gt; DPI64694</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>769.88111731</v>
+      </c>
+      <c r="F10" t="n">
+        <v>980</v>
+      </c>
+      <c r="G10" t="n">
+        <v>78.55929768469389</v>
+      </c>
+      <c r="H10" t="n">
+        <v>282</v>
+      </c>
+      <c r="I10" t="n">
+        <v>191416.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>0</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>DPI66669 -&gt; DPI70149 -&gt; DPI63904 -&gt; DPI66091 -&gt; DPI64374 -&gt; DPI70166 -&gt; DPI64118 -&gt; DPI70095</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>871.4090048300001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>980</v>
+      </c>
+      <c r="G11" t="n">
+        <v>88.91928620714286</v>
+      </c>
+      <c r="H11" t="n">
+        <v>938</v>
+      </c>
+      <c r="I11" t="n">
+        <v>406649.8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" t="n">
+        <v>407</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>DPI66460 -&gt; DPI63993 -&gt; DPI64176</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>179.54226</v>
+      </c>
+      <c r="F12" t="n">
+        <v>350</v>
+      </c>
+      <c r="G12" t="n">
+        <v>51.29778857142857</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1209</v>
+      </c>
+      <c r="I12" t="n">
+        <v>380879.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" t="n">
+        <v>207</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>DPI64044</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>65.98963999999999</v>
+      </c>
+      <c r="F13" t="n">
+        <v>150</v>
+      </c>
+      <c r="G13" t="n">
+        <v>43.99309333333333</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1218</v>
+      </c>
+      <c r="I13" t="n">
+        <v>307041</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1109</v>
+      </c>
+      <c r="C14" t="n">
+        <v>8</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>DPI64236 -&gt; DPI66734 -&gt; DPI70073 -&gt; DPI70038 -&gt; DPI64149 -&gt; DPI64234 -&gt; DPI66572 -&gt; DPI64639</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>605.02922</v>
+      </c>
+      <c r="F14" t="n">
+        <v>660</v>
+      </c>
+      <c r="G14" t="n">
+        <v>91.67109393939394</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1136</v>
+      </c>
+      <c r="I14" t="n">
+        <v>409632.8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C15" t="n">
+        <v>7</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>DPI64696 -&gt; DPI66692 -&gt; DPI64323 -&gt; DPI66618 -&gt; DPI66408 -&gt; DPI64624 -&gt; DPI66102</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>932.1960413500001</v>
+      </c>
+      <c r="F15" t="n">
+        <v>980</v>
+      </c>
+      <c r="G15" t="n">
+        <v>95.12204503571429</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1120</v>
+      </c>
+      <c r="I15" t="n">
+        <v>466364.0000000001</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C16" t="n">
+        <v>8</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>DPI64273 -&gt; DPI66646 -&gt; DPI70041 -&gt; DPI67024 -&gt; DPI64288 -&gt; DPI64352 -&gt; DPI67031 -&gt; DPI66684</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>904.4733</v>
+      </c>
+      <c r="F16" t="n">
+        <v>980</v>
+      </c>
+      <c r="G16" t="n">
+        <v>92.29319387755102</v>
+      </c>
+      <c r="H16" t="n">
+        <v>997</v>
+      </c>
+      <c r="I16" t="n">
+        <v>426007.7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C17" t="n">
+        <v>8</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>DPI67198 -&gt; DPI64692 -&gt; DPI66528 -&gt; DPI63920 -&gt; DPI66659 -&gt; DPI64476 -&gt; DPI66175 -&gt; DPI70317</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>921.0366468000001</v>
+      </c>
+      <c r="F17" t="n">
+        <v>980</v>
+      </c>
+      <c r="G17" t="n">
+        <v>93.98333130612245</v>
+      </c>
+      <c r="H17" t="n">
+        <v>560</v>
+      </c>
+      <c r="I17" t="n">
+        <v>282628</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C18" t="n">
+        <v>7</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>DPI64758 -&gt; DPI63822 -&gt; DPI66421 -&gt; DPI64378 -&gt; DPI67128 -&gt; DPI64303 -&gt; DPI64255</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>972.99394455</v>
+      </c>
+      <c r="F18" t="n">
+        <v>980</v>
+      </c>
+      <c r="G18" t="n">
+        <v>99.28509638265307</v>
+      </c>
+      <c r="H18" t="n">
+        <v>474</v>
+      </c>
+      <c r="I18" t="n">
+        <v>254411.4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C19" t="n">
+        <v>8</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>DPI66900 -&gt; DPI64179 -&gt; DPI64746 -&gt; DPI64392 -&gt; DPI66384 -&gt; DPI64166 -&gt; DPI66262 -&gt; DPI63847</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>966.13878676</v>
+      </c>
+      <c r="F19" t="n">
+        <v>980</v>
+      </c>
+      <c r="G19" t="n">
+        <v>98.58559048571429</v>
+      </c>
+      <c r="H19" t="n">
+        <v>939</v>
+      </c>
+      <c r="I19" t="n">
+        <v>406977.9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" t="n">
+        <v>207</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>DPI66264</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>147.74808</v>
+      </c>
+      <c r="F20" t="n">
+        <v>150</v>
+      </c>
+      <c r="G20" t="n">
+        <v>98.49872000000001</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>64050</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C21" t="n">
+        <v>12</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>DPI70179 -&gt; DPI70273 -&gt; DPI66144 -&gt; DPI70302 -&gt; DFT80087 -&gt; DPI64559 -&gt; DPI66229 -&gt; DPI66327 -&gt; DPI64484 -&gt; DPI66092 -&gt; DFT80034 -&gt; DFT80081</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>876.6482800000001</v>
+      </c>
+      <c r="F21" t="n">
+        <v>980</v>
+      </c>
+      <c r="G21" t="n">
+        <v>89.45390612244898</v>
+      </c>
+      <c r="H21" t="n">
+        <v>550</v>
+      </c>
+      <c r="I21" t="n">
+        <v>279347</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C22" t="n">
+        <v>10</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>DPI64104 -&gt; DPI64665 -&gt; DPI66263 -&gt; DPI64502 -&gt; DPI70120 -&gt; DPI64647 -&gt; DPI64032 -&gt; DPI66402 -&gt; DPI64409 -&gt; DPI70100</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>984.5953396499999</v>
+      </c>
+      <c r="F22" t="n">
+        <v>980</v>
+      </c>
+      <c r="G22" t="n">
+        <v>100.4689122091837</v>
+      </c>
+      <c r="H22" t="n">
+        <v>615</v>
+      </c>
+      <c r="I22" t="n">
+        <v>300673.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>DPI70106 -&gt; DPI70002 -&gt; DPI66335 -&gt; DPI63817 -&gt; DPI63895 -&gt; DPI64511 -&gt; DPI66508 -&gt; DFT80066 -&gt; DPI64651 -&gt; DPI70197</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>957.7799500000001</v>
+      </c>
+      <c r="F23" t="n">
+        <v>980</v>
+      </c>
+      <c r="G23" t="n">
+        <v>97.73264795918368</v>
+      </c>
+      <c r="H23" t="n">
+        <v>656</v>
+      </c>
+      <c r="I23" t="n">
+        <v>314125.6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" t="n">
+        <v>207</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>DPI70142</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>63.66179793000001</v>
+      </c>
+      <c r="F24" t="n">
+        <v>150</v>
+      </c>
+      <c r="G24" t="n">
+        <v>42.44119862</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>64050</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" t="n">
+        <v>207</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>DPI64548</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>118.61613</v>
+      </c>
+      <c r="F25" t="n">
+        <v>150</v>
+      </c>
+      <c r="G25" t="n">
+        <v>79.07742</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1258</v>
+      </c>
+      <c r="I25" t="n">
+        <v>315021</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2</v>
+      </c>
+      <c r="B26" t="n">
+        <v>407</v>
+      </c>
+      <c r="C26" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>DPI70107 -&gt; DPI70214 -&gt; DPI66634 -&gt; DPI70109</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>280.35797206</v>
+      </c>
+      <c r="F26" t="n">
+        <v>350</v>
+      </c>
+      <c r="G26" t="n">
+        <v>80.10227773142857</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1214</v>
+      </c>
+      <c r="I26" t="n">
+        <v>382128.6</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C27" t="n">
+        <v>7</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>DPI66096 -&gt; DPI64018 -&gt; DPI70229 -&gt; DPI66736 -&gt; DPI66129 -&gt; DPI64495 -&gt; DFT80080</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>945.6717099999998</v>
+      </c>
+      <c r="F27" t="n">
+        <v>980</v>
+      </c>
+      <c r="G27" t="n">
+        <v>96.49711326530611</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1253</v>
+      </c>
+      <c r="I27" t="n">
+        <v>510001.3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C28" t="n">
+        <v>8</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>DPI70213 -&gt; DPI66067 -&gt; DPI63915 -&gt; DPI64724 -&gt; DPI64297 -&gt; DPI67178 -&gt; DPI66742 -&gt; DPI64436</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>930.0945775</v>
+      </c>
+      <c r="F28" t="n">
+        <v>980</v>
+      </c>
+      <c r="G28" t="n">
+        <v>94.9076099489796</v>
+      </c>
+      <c r="H28" t="n">
+        <v>838</v>
+      </c>
+      <c r="I28" t="n">
+        <v>373839.8</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C29" t="n">
+        <v>10</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>DPI66923 -&gt; DFT80077 -&gt; DPI66636 -&gt; DPI64634 -&gt; DPI67180 -&gt; DPI70296 -&gt; DPI63976 -&gt; DPI64742 -&gt; DPI67148 -&gt; DPI67187</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>971.5546000000001</v>
+      </c>
+      <c r="F29" t="n">
+        <v>980</v>
+      </c>
+      <c r="G29" t="n">
+        <v>99.13822448979592</v>
+      </c>
+      <c r="H29" t="n">
+        <v>978</v>
+      </c>
+      <c r="I29" t="n">
+        <v>419773.8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C30" t="n">
+        <v>11</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>DPI70316 -&gt; DPI64094 -&gt; DPI66128 -&gt; DPI70096 -&gt; DPI64037 -&gt; DPI66172 -&gt; DPI64057 -&gt; DPI63802 -&gt; DPI66051 -&gt; DPI64169 -&gt; DPI66715</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>973.05680818</v>
+      </c>
+      <c r="F30" t="n">
+        <v>980</v>
+      </c>
+      <c r="G30" t="n">
+        <v>99.29151103877551</v>
+      </c>
+      <c r="H30" t="n">
+        <v>919</v>
+      </c>
+      <c r="I30" t="n">
+        <v>400415.9</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C31" t="n">
+        <v>8</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>DPI66653 -&gt; DPI66449 -&gt; DPI66576 -&gt; DPI64592 -&gt; DPI63919 -&gt; DPI64431 -&gt; DPI70047 -&gt; DPI66679</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>918.7296381</v>
+      </c>
+      <c r="F31" t="n">
+        <v>980</v>
+      </c>
+      <c r="G31" t="n">
+        <v>93.74792225510204</v>
+      </c>
+      <c r="H31" t="n">
+        <v>714</v>
+      </c>
+      <c r="I31" t="n">
+        <v>333155.4</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C32" t="n">
+        <v>9</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>DPI64480 -&gt; DPI66078 -&gt; DPI64433 -&gt; DPI66658 -&gt; DPI70105 -&gt; DPI64456 -&gt; DPI66574 -&gt; DPI66946 -&gt; DPI64136</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>923.4575500000002</v>
+      </c>
+      <c r="F32" t="n">
+        <v>980</v>
+      </c>
+      <c r="G32" t="n">
+        <v>94.23036224489798</v>
+      </c>
+      <c r="H32" t="n">
+        <v>868</v>
+      </c>
+      <c r="I32" t="n">
+        <v>383682.8</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C33" t="n">
+        <v>10</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>DPI64666 -&gt; DPI66209 -&gt; DPI67224 -&gt; DPI70190 -&gt; DPI70253 -&gt; DPI64056 -&gt; DPI67074 -&gt; DPI64628 -&gt; DPI64119 -&gt; DFT80078</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>849.8923600000001</v>
+      </c>
+      <c r="F33" t="n">
+        <v>980</v>
+      </c>
+      <c r="G33" t="n">
+        <v>86.72371020408164</v>
+      </c>
+      <c r="H33" t="n">
+        <v>929</v>
+      </c>
+      <c r="I33" t="n">
+        <v>403696.9</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C34" t="n">
+        <v>10</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>DPI66221 -&gt; DPI64196 -&gt; DPI66373 -&gt; DPI66153 -&gt; DPI67072 -&gt; DPI70081 -&gt; DPI66154 -&gt; DPI66313 -&gt; DPI63827 -&gt; DPI70009</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>965.25531832</v>
+      </c>
+      <c r="F34" t="n">
+        <v>980</v>
+      </c>
+      <c r="G34" t="n">
+        <v>98.49544064489795</v>
+      </c>
+      <c r="H34" t="n">
+        <v>420</v>
+      </c>
+      <c r="I34" t="n">
+        <v>236694</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C35" t="n">
+        <v>10</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>DPI66387 -&gt; DPI66339 -&gt; DPI66590 -&gt; DPI70255 -&gt; DPI66645 -&gt; DPI64413 -&gt; DPI64244 -&gt; DFT80088 -&gt; DPI64216 -&gt; DFT80044</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>913.93105241</v>
+      </c>
+      <c r="F35" t="n">
+        <v>980</v>
+      </c>
+      <c r="G35" t="n">
+        <v>93.25827065408163</v>
+      </c>
+      <c r="H35" t="n">
+        <v>590</v>
+      </c>
+      <c r="I35" t="n">
+        <v>292471</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C36" t="n">
+        <v>7</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>DPI64052 -&gt; DPI66179 -&gt; DPI66597 -&gt; DPI63958 -&gt; DPI66039 -&gt; DPI66307 -&gt; DPI64638</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>864.4288809000002</v>
+      </c>
+      <c r="F36" t="n">
+        <v>980</v>
+      </c>
+      <c r="G36" t="n">
+        <v>88.20702866326533</v>
+      </c>
+      <c r="H36" t="n">
+        <v>201</v>
+      </c>
+      <c r="I36" t="n">
+        <v>164840.1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C37" t="n">
+        <v>9</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>DPI64218 -&gt; DPI66289 -&gt; DPI64039 -&gt; DPI64301 -&gt; DPI66069 -&gt; DPI64686 -&gt; DPI66203 -&gt; DPI64450 -&gt; DPI67121</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>920.95597714</v>
+      </c>
+      <c r="F37" t="n">
+        <v>980</v>
+      </c>
+      <c r="G37" t="n">
+        <v>93.97509970816326</v>
+      </c>
+      <c r="H37" t="n">
+        <v>202</v>
+      </c>
+      <c r="I37" t="n">
+        <v>165168.2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>3</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C38" t="n">
+        <v>9</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>DPI66094 -&gt; DPI66389 -&gt; DPI65993 -&gt; DPI70261 -&gt; DPI66622 -&gt; DPI70148 -&gt; DPI66621 -&gt; DPI70320 -&gt; DPI70057</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>959.39262601</v>
+      </c>
+      <c r="F38" t="n">
+        <v>980</v>
+      </c>
+      <c r="G38" t="n">
+        <v>97.89720673571428</v>
+      </c>
+      <c r="H38" t="n">
+        <v>273</v>
+      </c>
+      <c r="I38" t="n">
+        <v>188463.3</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>3</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C39" t="n">
+        <v>9</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>DPI67042 -&gt; DPI66378 -&gt; DPI66688 -&gt; DPI66042 -&gt; DPI70104 -&gt; DPI66359 -&gt; DPI66400 -&gt; DPI70091 -&gt; DPI66241</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>967.08362267</v>
+      </c>
+      <c r="F39" t="n">
+        <v>980</v>
+      </c>
+      <c r="G39" t="n">
+        <v>98.6820023132653</v>
+      </c>
+      <c r="H39" t="n">
+        <v>253</v>
+      </c>
+      <c r="I39" t="n">
+        <v>181901.3</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>3</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1109</v>
+      </c>
+      <c r="C40" t="n">
+        <v>3</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>DPI66626 -&gt; DPI66578 -&gt; DPI66437</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>373.22844717</v>
+      </c>
+      <c r="F40" t="n">
+        <v>660</v>
+      </c>
+      <c r="G40" t="n">
+        <v>56.54976472272727</v>
+      </c>
+      <c r="H40" t="n">
+        <v>206</v>
+      </c>
+      <c r="I40" t="n">
+        <v>144768.8</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>3</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C41" t="n">
+        <v>10</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>DPI70140 -&gt; DPI64650 -&gt; DPI66410 -&gt; DPI66280 -&gt; DPI65877 -&gt; DPI64240 -&gt; DPI66970 -&gt; DPI67126 -&gt; DPI64470 -&gt; DPI64520</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>981.73877239</v>
+      </c>
+      <c r="F41" t="n">
+        <v>980</v>
+      </c>
+      <c r="G41" t="n">
+        <v>100.1774257540816</v>
+      </c>
+      <c r="H41" t="n">
+        <v>271</v>
+      </c>
+      <c r="I41" t="n">
+        <v>187807.1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>3</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C42" t="n">
+        <v>9</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>DPI70216 -&gt; DPI64741 -&gt; DPI64428 -&gt; DPI63945 -&gt; DPI66940 -&gt; DPI66119 -&gt; DPI64720 -&gt; DPI67093 -&gt; DPI64600</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>752.7613463700001</v>
+      </c>
+      <c r="F42" t="n">
+        <v>980</v>
+      </c>
+      <c r="G42" t="n">
+        <v>76.81238228265308</v>
+      </c>
+      <c r="H42" t="n">
+        <v>998</v>
+      </c>
+      <c r="I42" t="n">
+        <v>426335.8</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>3</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C43" t="n">
+        <v>13</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>DFT80058 -&gt; DPI64291 -&gt; DPI66104 -&gt; DPI66730 -&gt; DPI66944 -&gt; DPI66591 -&gt; DPI66239 -&gt; DPI70039 -&gt; DPI70022 -&gt; DPI66532 -&gt; DPI67062 -&gt; DPI64252 -&gt; DPI64317</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>770.95050487</v>
+      </c>
+      <c r="F43" t="n">
+        <v>980</v>
+      </c>
+      <c r="G43" t="n">
+        <v>78.66841886428571</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1041</v>
+      </c>
+      <c r="I43" t="n">
+        <v>440444.1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>3</v>
+      </c>
+      <c r="B44" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C44" t="n">
+        <v>14</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>DPI70256 -&gt; DPI64203 -&gt; DPI67050 -&gt; DPI64418 -&gt; DPI66122 -&gt; DPI66729 -&gt; DPI64350 -&gt; DPI66326 -&gt; DPI64246 -&gt; DPI63936 -&gt; DPI64703 -&gt; DPI66652 -&gt; DPI70058 -&gt; DPI64279</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>975.1779477099999</v>
+      </c>
+      <c r="F44" t="n">
+        <v>980</v>
+      </c>
+      <c r="G44" t="n">
+        <v>99.50795384795917</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1042</v>
+      </c>
+      <c r="I44" t="n">
+        <v>440772.2000000001</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>3</v>
+      </c>
+      <c r="B45" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C45" t="n">
+        <v>19</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>DPI66945 -&gt; DPI63813 -&gt; DPI66640 -&gt; DPI66125 -&gt; DPI64336 -&gt; DPI64237 -&gt; DPI66029 -&gt; DPI64102 -&gt; DPI66497 -&gt; DPI64525 -&gt; DPI64145 -&gt; DPI64079 -&gt; DPI63999 -&gt; DPI64641 -&gt; DPI66999 -&gt; DPI70032 -&gt; DPI64310 -&gt; DPI66224 -&gt; DPI64043</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>913.7526912600001</v>
+      </c>
+      <c r="F45" t="n">
+        <v>980</v>
+      </c>
+      <c r="G45" t="n">
+        <v>93.24007053673471</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1034</v>
+      </c>
+      <c r="I45" t="n">
+        <v>438147.4</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B46" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C46" t="n">
+        <v>10</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>DPI66386 -&gt; DPI66194 -&gt; DPI64019 -&gt; DPI65779 -&gt; DPI67014 -&gt; DPI66733 -&gt; DPI63978 -&gt; DPI64706 -&gt; DPI64083 -&gt; DPI64073</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>968.4121970399999</v>
+      </c>
+      <c r="F46" t="n">
+        <v>980</v>
+      </c>
+      <c r="G46" t="n">
+        <v>98.81757112653059</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1030</v>
+      </c>
+      <c r="I46" t="n">
+        <v>436835</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B47" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C47" t="n">
+        <v>11</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>DPI64377 -&gt; DFT80095 -&gt; DPI70069 -&gt; DPI67021 -&gt; DPI64207 -&gt; DPI70306 -&gt; DPI64408 -&gt; DPI66333 -&gt; DPI66926 -&gt; DPI64250 -&gt; DPI64577</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>942.46232549</v>
+      </c>
+      <c r="F47" t="n">
+        <v>980</v>
+      </c>
+      <c r="G47" t="n">
+        <v>96.16962504999999</v>
+      </c>
+      <c r="H47" t="n">
+        <v>302</v>
+      </c>
+      <c r="I47" t="n">
+        <v>197978.2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>3</v>
+      </c>
+      <c r="B48" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C48" t="n">
+        <v>10</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>DPI66377 -&gt; DPI63951 -&gt; DPI66501 -&gt; DPI64140 -&gt; DPI65998 -&gt; DPI66538 -&gt; DPI65969 -&gt; DPI66126 -&gt; DPI65919 -&gt; DPI64331</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>948.49393233</v>
+      </c>
+      <c r="F48" t="n">
+        <v>980</v>
+      </c>
+      <c r="G48" t="n">
+        <v>96.78509513571429</v>
+      </c>
+      <c r="H48" t="n">
+        <v>270</v>
+      </c>
+      <c r="I48" t="n">
+        <v>187479</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>3</v>
+      </c>
+      <c r="B49" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C49" t="n">
+        <v>9</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>DPI66076 -&gt; DPI65789 -&gt; DPI66136 -&gt; DPI67183 -&gt; DPI64602 -&gt; DPI65915 -&gt; DPI66522 -&gt; DPI66053 -&gt; DPI66685</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>976.4924243199999</v>
+      </c>
+      <c r="F49" t="n">
+        <v>980</v>
+      </c>
+      <c r="G49" t="n">
+        <v>99.64208411428571</v>
+      </c>
+      <c r="H49" t="n">
+        <v>268</v>
+      </c>
+      <c r="I49" t="n">
+        <v>186822.8</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>3</v>
+      </c>
+      <c r="B50" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C50" t="n">
+        <v>9</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>DPI66031 -&gt; DPI67181 -&gt; DPI64752 -&gt; DPI64106 -&gt; DPI66548 -&gt; DPI64469 -&gt; DPI64227 -&gt; DPI67118 -&gt; DPI63950</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>966.40726765</v>
+      </c>
+      <c r="F50" t="n">
+        <v>980</v>
+      </c>
+      <c r="G50" t="n">
+        <v>98.61298649489795</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1040</v>
+      </c>
+      <c r="I50" t="n">
+        <v>440116</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>3</v>
+      </c>
+      <c r="B51" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C51" t="n">
+        <v>9</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>DPI63823 -&gt; DPI66191 -&gt; DPI67217 -&gt; DPI65840 -&gt; DPI66422 -&gt; DPI66014 -&gt; DPI64026 -&gt; DPI66755 -&gt; DPI70176</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>979.27092405</v>
+      </c>
+      <c r="F51" t="n">
+        <v>980</v>
+      </c>
+      <c r="G51" t="n">
+        <v>99.92560449489795</v>
+      </c>
+      <c r="H51" t="n">
+        <v>265</v>
+      </c>
+      <c r="I51" t="n">
+        <v>185838.5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>3</v>
+      </c>
+      <c r="B52" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C52" t="n">
+        <v>9</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>DPI66573 -&gt; DPI66998 -&gt; DPI67110 -&gt; DPI67179 -&gt; DPI66660 -&gt; DPI66521 -&gt; DPI64631 -&gt; DPI66619 -&gt; DPI67064</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>971.8510420099999</v>
+      </c>
+      <c r="F52" t="n">
+        <v>980</v>
+      </c>
+      <c r="G52" t="n">
+        <v>99.16847367448979</v>
+      </c>
+      <c r="H52" t="n">
+        <v>252</v>
+      </c>
+      <c r="I52" t="n">
+        <v>181573.2</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>3</v>
+      </c>
+      <c r="B53" t="n">
+        <v>207</v>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>DPI66929</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>129.31327658</v>
+      </c>
+      <c r="F53" t="n">
+        <v>150</v>
+      </c>
+      <c r="G53" t="n">
+        <v>86.20885105333333</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>64050</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
         <v>5</v>
       </c>
-      <c r="B7" t="n">
-        <v>1613</v>
-      </c>
-      <c r="C7" t="n">
-        <v>29</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>DPI70309 -&gt; DPI67135 -&gt; DPI70242 -&gt; DPI64549 -&gt; DPI66441 -&gt; DPI65995 -&gt; DPI66445 -&gt; DPI64122 -&gt; DPI64494 -&gt; DPI67086 -&gt; DPI64683 -&gt; DPI70144 -&gt; DPI70018 -&gt; DPI70323 -&gt; DPI64005 -&gt; DPI64434 -&gt; DPI66500 -&gt; DPI64448 -&gt; DPI64702 -&gt; DPI64390 -&gt; DPI64654 -&gt; DPI64629 -&gt; DPI70303 -&gt; DPI70186 -&gt; DPI64737 -&gt; DPI66620 -&gt; DPI64226 -&gt; DPI66927 -&gt; DPI64655</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>3225.16760608</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1579.115090168377</v>
-      </c>
-      <c r="G7" t="n">
-        <v>616999.6610842445</v>
+      <c r="B54" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C54" t="n">
+        <v>10</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>DPI64434 -&gt; DPI66500 -&gt; DPI64448 -&gt; DPI70186 -&gt; DPI70303 -&gt; DPI64629 -&gt; DPI64654 -&gt; DPI64390 -&gt; DPI64702 -&gt; DPI64005</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>982.8216884799999</v>
+      </c>
+      <c r="F54" t="n">
+        <v>980</v>
+      </c>
+      <c r="G54" t="n">
+        <v>100.2879273959184</v>
+      </c>
+      <c r="H54" t="n">
+        <v>404</v>
+      </c>
+      <c r="I54" t="n">
+        <v>231444.4</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>5</v>
+      </c>
+      <c r="B55" t="n">
+        <v>207</v>
+      </c>
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>DPI70309</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>54.18531179999999</v>
+      </c>
+      <c r="F55" t="n">
+        <v>150</v>
+      </c>
+      <c r="G55" t="n">
+        <v>36.1235412</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>64050</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>5</v>
+      </c>
+      <c r="B56" t="n">
+        <v>1109</v>
+      </c>
+      <c r="C56" t="n">
+        <v>4</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>DPI64737 -&gt; DPI66927 -&gt; DPI64655 -&gt; DPI66620</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>456.3569774</v>
+      </c>
+      <c r="F56" t="n">
+        <v>660</v>
+      </c>
+      <c r="G56" t="n">
+        <v>69.14499657575757</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1073</v>
+      </c>
+      <c r="I56" t="n">
+        <v>391690.4</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>5</v>
+      </c>
+      <c r="B57" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C57" t="n">
+        <v>8</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>DPI65995 -&gt; DPI66445 -&gt; DPI64122 -&gt; DPI64494 -&gt; DPI67086 -&gt; DPI64683 -&gt; DPI70144 -&gt; DPI64549</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>951.0663683000001</v>
+      </c>
+      <c r="F57" t="n">
+        <v>980</v>
+      </c>
+      <c r="G57" t="n">
+        <v>97.04758860204083</v>
+      </c>
+      <c r="H57" t="n">
+        <v>34</v>
+      </c>
+      <c r="I57" t="n">
+        <v>110047.4</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>5</v>
+      </c>
+      <c r="B58" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C58" t="n">
+        <v>6</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>DPI70323 -&gt; DPI64226 -&gt; DPI70018 -&gt; DPI66441 -&gt; DPI70242 -&gt; DPI67135</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>780.7372601000001</v>
+      </c>
+      <c r="F58" t="n">
+        <v>980</v>
+      </c>
+      <c r="G58" t="n">
+        <v>79.66706735714286</v>
+      </c>
+      <c r="H58" t="n">
+        <v>703</v>
+      </c>
+      <c r="I58" t="n">
+        <v>329546.3</v>
       </c>
     </row>
   </sheetData>

--- a/secondary_logistics_routes.xlsx
+++ b/secondary_logistics_routes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,23 +487,23 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DPI66995 -&gt; DPI70031 -&gt; DPI66461 -&gt; DPI66555 -&gt; DPI70234 -&gt; DPI66380 -&gt; DPI66395 -&gt; DPI63929</t>
+          <t>DPI63929 -&gt; DPI66395 -&gt; DPI66100 -&gt; DPI64175 -&gt; DPI67004 -&gt; DPI66555 -&gt; DPI66461 -&gt; DPI70031</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>901.76759583</v>
+        <v>900.3305937299998</v>
       </c>
       <c r="F2" t="n">
         <v>980</v>
       </c>
       <c r="G2" t="n">
-        <v>92.01710161530612</v>
+        <v>91.87046874795917</v>
       </c>
       <c r="H2" t="n">
-        <v>915</v>
+        <v>885</v>
       </c>
       <c r="I2" t="n">
-        <v>399103.5</v>
+        <v>389260.5</v>
       </c>
     </row>
     <row r="3">
@@ -511,30 +511,30 @@
         <v>0</v>
       </c>
       <c r="B3" t="n">
-        <v>1613</v>
+        <v>1109</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DPI70165 -&gt; DPI67004 -&gt; DPI64175 -&gt; DPI66100 -&gt; DPI66491 -&gt; DPI66953 -&gt; DPI66759 -&gt; DPI64085 -&gt; DPI66060 -&gt; DPI64619</t>
+          <t>DPI66091 -&gt; DPI64374 -&gt; DPI70166 -&gt; DPI64118 -&gt; DPI70095 -&gt; DPI63904</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>955.8999013800001</v>
+        <v>637.47902</v>
       </c>
       <c r="F3" t="n">
-        <v>980</v>
+        <v>660</v>
       </c>
       <c r="G3" t="n">
-        <v>97.54080626326531</v>
+        <v>96.58773030303031</v>
       </c>
       <c r="H3" t="n">
-        <v>626</v>
+        <v>925</v>
       </c>
       <c r="I3" t="n">
-        <v>304282.6</v>
+        <v>349540</v>
       </c>
     </row>
     <row r="4">
@@ -542,30 +542,30 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>1613</v>
+        <v>407</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DPI64091 -&gt; DPI64239 -&gt; DPI64045 -&gt; DPI66503 -&gt; DPI64000 -&gt; DPI64506 -&gt; DPI66915 -&gt; DPI67102 -&gt; DPI70035 -&gt; DPI64008 -&gt; DPI70040</t>
+          <t>DPI67002 -&gt; DPI64644 -&gt; DPI66938</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>945.71706717</v>
+        <v>310.82337</v>
       </c>
       <c r="F4" t="n">
-        <v>980</v>
+        <v>350</v>
       </c>
       <c r="G4" t="n">
-        <v>96.50174154795917</v>
+        <v>88.80667714285713</v>
       </c>
       <c r="H4" t="n">
-        <v>656</v>
+        <v>960</v>
       </c>
       <c r="I4" t="n">
-        <v>314125.6</v>
+        <v>318654</v>
       </c>
     </row>
     <row r="5">
@@ -576,27 +576,27 @@
         <v>1613</v>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DPI64253 -&gt; DPI66748 -&gt; DPI66127 -&gt; DPI64563 -&gt; DPI66329 -&gt; DPI65841 -&gt; DPI64137 -&gt; DPI63902 -&gt; DPI64001 -&gt; DPI64299 -&gt; DPI64543 -&gt; DPI63898</t>
+          <t>DPI64254 -&gt; DPI64462 -&gt; DPI64606 -&gt; DPI64711 -&gt; DPI67245 -&gt; DPI64364 -&gt; DPI65825 -&gt; DPI66265 -&gt; DPI64694</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>974.8624757700002</v>
+        <v>890.5883619700001</v>
       </c>
       <c r="F5" t="n">
         <v>980</v>
       </c>
       <c r="G5" t="n">
-        <v>99.47576283367349</v>
+        <v>90.87636346632654</v>
       </c>
       <c r="H5" t="n">
-        <v>833</v>
+        <v>282</v>
       </c>
       <c r="I5" t="n">
-        <v>372199.3</v>
+        <v>191416.2</v>
       </c>
     </row>
     <row r="6">
@@ -607,27 +607,27 @@
         <v>1613</v>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DPI70327 -&gt; DPI64561 -&gt; DPI64281 -&gt; DPI66974 -&gt; DPI65827 -&gt; DPI67214 -&gt; DPI70254 -&gt; DPI66511 -&gt; DPI66512 -&gt; DPI70228 -&gt; DPI64400</t>
+          <t>DPI64299 -&gt; DPI64001 -&gt; DPI63902 -&gt; DPI64563 -&gt; DPI66329 -&gt; DPI66127 -&gt; DPI65841 -&gt; DPI64137 -&gt; DPI66748 -&gt; DPI64253 -&gt; DPI64543 -&gt; DPI63898</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>963.35313633</v>
+        <v>974.8624757700002</v>
       </c>
       <c r="F6" t="n">
         <v>980</v>
       </c>
       <c r="G6" t="n">
-        <v>98.30134044183674</v>
+        <v>99.47576283367349</v>
       </c>
       <c r="H6" t="n">
-        <v>373</v>
+        <v>823</v>
       </c>
       <c r="I6" t="n">
-        <v>221273.3</v>
+        <v>368918.3</v>
       </c>
     </row>
     <row r="7">
@@ -638,27 +638,27 @@
         <v>1613</v>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>DPI66594 -&gt; DPI66372 -&gt; DPI64247 -&gt; DPI64191 -&gt; DPI70090 -&gt; DPI64024 -&gt; DPI67047 -&gt; DPI64361 -&gt; DPI65875 -&gt; DPI64590</t>
+          <t>DPI66372 -&gt; DPI64239 -&gt; DPI64045 -&gt; DPI66503 -&gt; DPI64000 -&gt; DPI64506 -&gt; DPI66915 -&gt; DPI67102 -&gt; DPI70035 -&gt; DPI64008 -&gt; DPI70040</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>981.6529681499999</v>
+        <v>975.09293206</v>
       </c>
       <c r="F7" t="n">
         <v>980</v>
       </c>
       <c r="G7" t="n">
-        <v>100.1686702193877</v>
+        <v>99.49927878163265</v>
       </c>
       <c r="H7" t="n">
-        <v>537</v>
+        <v>655</v>
       </c>
       <c r="I7" t="n">
-        <v>275081.7</v>
+        <v>313797.5</v>
       </c>
     </row>
     <row r="8">
@@ -697,30 +697,30 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>1109</v>
+        <v>1613</v>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>DPI66938 -&gt; DPI67138 -&gt; DPI67002 -&gt; DPI64644 -&gt; DPI64108 -&gt; DPI64254</t>
+          <t>DPI70165 -&gt; DPI64619 -&gt; DPI64085 -&gt; DPI66060 -&gt; DPI70234 -&gt; DPI66491 -&gt; DPI66380 -&gt; DPI66953 -&gt; DPI66759 -&gt; DPI66995</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>634.46768466</v>
+        <v>957.33690348</v>
       </c>
       <c r="F9" t="n">
-        <v>660</v>
+        <v>980</v>
       </c>
       <c r="G9" t="n">
-        <v>96.13146737272727</v>
+        <v>97.68743913061225</v>
       </c>
       <c r="H9" t="n">
-        <v>962</v>
+        <v>649</v>
       </c>
       <c r="I9" t="n">
-        <v>360077.6</v>
+        <v>311828.9</v>
       </c>
     </row>
     <row r="10">
@@ -728,30 +728,30 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>1613</v>
+        <v>1109</v>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DPI64462 -&gt; DPI64606 -&gt; DPI64711 -&gt; DPI67245 -&gt; DPI64364 -&gt; DPI65825 -&gt; DPI66265 -&gt; DPI64694</t>
+          <t>DPI66669 -&gt; DPI70149 -&gt; DPI67138 -&gt; DPI64108</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>769.88111731</v>
+        <v>436.86705483</v>
       </c>
       <c r="F10" t="n">
-        <v>980</v>
+        <v>660</v>
       </c>
       <c r="G10" t="n">
-        <v>78.55929768469389</v>
+        <v>66.19197800454546</v>
       </c>
       <c r="H10" t="n">
-        <v>282</v>
+        <v>960</v>
       </c>
       <c r="I10" t="n">
-        <v>191416.2</v>
+        <v>359508</v>
       </c>
     </row>
     <row r="11">
@@ -762,58 +762,58 @@
         <v>1613</v>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DPI66669 -&gt; DPI70149 -&gt; DPI63904 -&gt; DPI66091 -&gt; DPI64374 -&gt; DPI70166 -&gt; DPI64118 -&gt; DPI70095</t>
+          <t>DPI66594 -&gt; DPI64091 -&gt; DPI64247 -&gt; DPI64191 -&gt; DPI70090 -&gt; DPI64024 -&gt; DPI67047 -&gt; DPI64361 -&gt; DPI65875 -&gt; DPI64590</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>871.4090048300001</v>
+        <v>952.2771032599999</v>
       </c>
       <c r="F11" t="n">
         <v>980</v>
       </c>
       <c r="G11" t="n">
-        <v>88.91928620714286</v>
+        <v>97.17113298571427</v>
       </c>
       <c r="H11" t="n">
-        <v>938</v>
+        <v>538</v>
       </c>
       <c r="I11" t="n">
-        <v>406649.8</v>
+        <v>275409.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>407</v>
+        <v>1613</v>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>DPI66460 -&gt; DPI63993 -&gt; DPI64176</t>
+          <t>DPI70327 -&gt; DPI65827 -&gt; DPI64561 -&gt; DPI64281 -&gt; DPI66974 -&gt; DPI67214 -&gt; DPI70254 -&gt; DPI66511 -&gt; DPI66512 -&gt; DPI70228 -&gt; DPI64400</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>179.54226</v>
+        <v>963.35313633</v>
       </c>
       <c r="F12" t="n">
-        <v>350</v>
+        <v>980</v>
       </c>
       <c r="G12" t="n">
-        <v>51.29778857142857</v>
+        <v>98.30134044183674</v>
       </c>
       <c r="H12" t="n">
-        <v>1209</v>
+        <v>373</v>
       </c>
       <c r="I12" t="n">
-        <v>380879.1</v>
+        <v>221273.3</v>
       </c>
     </row>
     <row r="13">
@@ -821,30 +821,30 @@
         <v>1</v>
       </c>
       <c r="B13" t="n">
-        <v>207</v>
+        <v>1613</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>DPI64044</t>
+          <t>DPI64639 -&gt; DPI66572 -&gt; DPI64234 -&gt; DPI64149 -&gt; DPI70038 -&gt; DPI70073 -&gt; DPI64288 -&gt; DPI64352 -&gt; DPI66734 -&gt; DPI64236 -&gt; DPI66684</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>65.98963999999999</v>
+        <v>913.6278000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>150</v>
+        <v>980</v>
       </c>
       <c r="G13" t="n">
-        <v>43.99309333333333</v>
+        <v>93.22732653061226</v>
       </c>
       <c r="H13" t="n">
-        <v>1218</v>
+        <v>1148</v>
       </c>
       <c r="I13" t="n">
-        <v>307041</v>
+        <v>475550.8</v>
       </c>
     </row>
     <row r="14">
@@ -852,30 +852,30 @@
         <v>1</v>
       </c>
       <c r="B14" t="n">
-        <v>1109</v>
+        <v>1613</v>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DPI64236 -&gt; DPI66734 -&gt; DPI70073 -&gt; DPI70038 -&gt; DPI64149 -&gt; DPI64234 -&gt; DPI66572 -&gt; DPI64639</t>
+          <t>DPI64273 -&gt; DPI64665 -&gt; DPI70120 -&gt; DPI64502 -&gt; DPI66263 -&gt; DPI64104 -&gt; DPI66264</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>605.02922</v>
+        <v>771.89832</v>
       </c>
       <c r="F14" t="n">
-        <v>660</v>
+        <v>980</v>
       </c>
       <c r="G14" t="n">
-        <v>91.67109393939394</v>
+        <v>78.76513469387754</v>
       </c>
       <c r="H14" t="n">
-        <v>1136</v>
+        <v>274</v>
       </c>
       <c r="I14" t="n">
-        <v>409632.8</v>
+        <v>188791.4</v>
       </c>
     </row>
     <row r="15">
@@ -883,30 +883,30 @@
         <v>1</v>
       </c>
       <c r="B15" t="n">
-        <v>1613</v>
+        <v>207</v>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>DPI64696 -&gt; DPI66692 -&gt; DPI64323 -&gt; DPI66618 -&gt; DPI66408 -&gt; DPI64624 -&gt; DPI66102</t>
+          <t>DPI64044</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>932.1960413500001</v>
+        <v>65.98963999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>980</v>
+        <v>150</v>
       </c>
       <c r="G15" t="n">
-        <v>95.12204503571429</v>
+        <v>43.99309333333333</v>
       </c>
       <c r="H15" t="n">
-        <v>1120</v>
+        <v>1218</v>
       </c>
       <c r="I15" t="n">
-        <v>466364.0000000001</v>
+        <v>307041</v>
       </c>
     </row>
     <row r="16">
@@ -921,23 +921,23 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DPI64273 -&gt; DPI66646 -&gt; DPI70041 -&gt; DPI67024 -&gt; DPI64288 -&gt; DPI64352 -&gt; DPI67031 -&gt; DPI66684</t>
+          <t>DPI64758 -&gt; DPI66659 -&gt; DPI64476 -&gt; DPI66175 -&gt; DPI66646 -&gt; DPI70041 -&gt; DPI67031 -&gt; DPI67024</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>904.4733</v>
+        <v>974.24177015</v>
       </c>
       <c r="F16" t="n">
         <v>980</v>
       </c>
       <c r="G16" t="n">
-        <v>92.29319387755102</v>
+        <v>99.4124255255102</v>
       </c>
       <c r="H16" t="n">
-        <v>997</v>
+        <v>1057</v>
       </c>
       <c r="I16" t="n">
-        <v>426007.7</v>
+        <v>445693.7000000001</v>
       </c>
     </row>
     <row r="17">
@@ -948,27 +948,27 @@
         <v>1613</v>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DPI67198 -&gt; DPI64692 -&gt; DPI66528 -&gt; DPI63920 -&gt; DPI66659 -&gt; DPI64476 -&gt; DPI66175 -&gt; DPI70317</t>
+          <t>DPI70106 -&gt; DPI70002 -&gt; DPI66335 -&gt; DPI63895 -&gt; DPI64511 -&gt; DPI66508 -&gt; DPI64484 -&gt; DPI66327 -&gt; DFT80087 -&gt; DFT80066</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>921.0366468000001</v>
+        <v>857.7314100000001</v>
       </c>
       <c r="F17" t="n">
         <v>980</v>
       </c>
       <c r="G17" t="n">
-        <v>93.98333130612245</v>
+        <v>87.52361326530614</v>
       </c>
       <c r="H17" t="n">
-        <v>560</v>
+        <v>591</v>
       </c>
       <c r="I17" t="n">
-        <v>282628</v>
+        <v>292799.1</v>
       </c>
     </row>
     <row r="18">
@@ -983,23 +983,23 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DPI64758 -&gt; DPI63822 -&gt; DPI66421 -&gt; DPI64378 -&gt; DPI67128 -&gt; DPI64303 -&gt; DPI64255</t>
+          <t>DPI64696 -&gt; DPI66692 -&gt; DPI64323 -&gt; DPI66618 -&gt; DPI66408 -&gt; DPI64624 -&gt; DPI66102</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>972.99394455</v>
+        <v>932.1960413500001</v>
       </c>
       <c r="F18" t="n">
         <v>980</v>
       </c>
       <c r="G18" t="n">
-        <v>99.28509638265307</v>
+        <v>95.12204503571429</v>
       </c>
       <c r="H18" t="n">
-        <v>474</v>
+        <v>1120</v>
       </c>
       <c r="I18" t="n">
-        <v>254411.4</v>
+        <v>466364.0000000001</v>
       </c>
     </row>
     <row r="19">
@@ -1010,27 +1010,27 @@
         <v>1613</v>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DPI66900 -&gt; DPI64179 -&gt; DPI64746 -&gt; DPI64392 -&gt; DPI66384 -&gt; DPI64166 -&gt; DPI66262 -&gt; DPI63847</t>
+          <t>DFT80081 -&gt; DFT80034 -&gt; DPI66092 -&gt; DPI66229 -&gt; DPI63817 -&gt; DPI64559 -&gt; DPI70302 -&gt; DPI70179 -&gt; DPI66144 -&gt; DPI70273 -&gt; DPI64651 -&gt; DPI70197</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>966.13878676</v>
+        <v>976.6968200000001</v>
       </c>
       <c r="F19" t="n">
         <v>980</v>
       </c>
       <c r="G19" t="n">
-        <v>98.58559048571429</v>
+        <v>99.66294081632654</v>
       </c>
       <c r="H19" t="n">
-        <v>939</v>
+        <v>553</v>
       </c>
       <c r="I19" t="n">
-        <v>406977.9</v>
+        <v>280331.3</v>
       </c>
     </row>
     <row r="20">
@@ -1038,30 +1038,30 @@
         <v>1</v>
       </c>
       <c r="B20" t="n">
-        <v>207</v>
+        <v>1613</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>DPI66264</t>
+          <t>DPI63822 -&gt; DPI66421 -&gt; DPI66528 -&gt; DPI63920 -&gt; DPI64692 -&gt; DPI67198 -&gt; DPI70317</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>147.74808</v>
+        <v>944.87035665</v>
       </c>
       <c r="F20" t="n">
-        <v>150</v>
+        <v>980</v>
       </c>
       <c r="G20" t="n">
-        <v>98.49872000000001</v>
+        <v>96.41534251530612</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>489</v>
       </c>
       <c r="I20" t="n">
-        <v>64050</v>
+        <v>259332.9</v>
       </c>
     </row>
     <row r="21">
@@ -1072,27 +1072,27 @@
         <v>1613</v>
       </c>
       <c r="C21" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DPI70179 -&gt; DPI70273 -&gt; DPI66144 -&gt; DPI70302 -&gt; DFT80087 -&gt; DPI64559 -&gt; DPI66229 -&gt; DPI66327 -&gt; DPI64484 -&gt; DPI66092 -&gt; DFT80034 -&gt; DFT80081</t>
+          <t>DPI64647 -&gt; DPI64032 -&gt; DPI66402 -&gt; DPI64409 -&gt; DPI64378 -&gt; DPI67128 -&gt; DPI70100 -&gt; DPI64303 -&gt; DPI64255</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>876.6482800000001</v>
+        <v>931.2382842000001</v>
       </c>
       <c r="F21" t="n">
         <v>980</v>
       </c>
       <c r="G21" t="n">
-        <v>89.45390612244898</v>
+        <v>95.02431471428572</v>
       </c>
       <c r="H21" t="n">
-        <v>550</v>
+        <v>487</v>
       </c>
       <c r="I21" t="n">
-        <v>279347</v>
+        <v>258676.7</v>
       </c>
     </row>
     <row r="22">
@@ -1103,27 +1103,27 @@
         <v>1613</v>
       </c>
       <c r="C22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>DPI64104 -&gt; DPI64665 -&gt; DPI66263 -&gt; DPI64502 -&gt; DPI70120 -&gt; DPI64647 -&gt; DPI64032 -&gt; DPI66402 -&gt; DPI64409 -&gt; DPI70100</t>
+          <t>DPI66900 -&gt; DPI64179 -&gt; DPI64746 -&gt; DPI64392 -&gt; DPI66384 -&gt; DPI64166 -&gt; DPI66262 -&gt; DPI63847</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>984.5953396499999</v>
+        <v>966.13878676</v>
       </c>
       <c r="F22" t="n">
         <v>980</v>
       </c>
       <c r="G22" t="n">
-        <v>100.4689122091837</v>
+        <v>98.58559048571429</v>
       </c>
       <c r="H22" t="n">
-        <v>615</v>
+        <v>939</v>
       </c>
       <c r="I22" t="n">
-        <v>300673.5</v>
+        <v>406977.9</v>
       </c>
     </row>
     <row r="23">
@@ -1131,30 +1131,30 @@
         <v>1</v>
       </c>
       <c r="B23" t="n">
-        <v>1613</v>
+        <v>407</v>
       </c>
       <c r="C23" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DPI70106 -&gt; DPI70002 -&gt; DPI66335 -&gt; DPI63817 -&gt; DPI63895 -&gt; DPI64511 -&gt; DPI66508 -&gt; DFT80066 -&gt; DPI64651 -&gt; DPI70197</t>
+          <t>DPI66460 -&gt; DPI63993 -&gt; DPI64176</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>957.7799500000001</v>
+        <v>179.54226</v>
       </c>
       <c r="F23" t="n">
-        <v>980</v>
+        <v>350</v>
       </c>
       <c r="G23" t="n">
-        <v>97.73264795918368</v>
+        <v>51.29778857142857</v>
       </c>
       <c r="H23" t="n">
-        <v>656</v>
+        <v>1209</v>
       </c>
       <c r="I23" t="n">
-        <v>314125.6</v>
+        <v>380879.1</v>
       </c>
     </row>
     <row r="24">
@@ -1162,30 +1162,30 @@
         <v>2</v>
       </c>
       <c r="B24" t="n">
-        <v>207</v>
+        <v>1613</v>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DPI70142</t>
+          <t>DPI63827 -&gt; DPI66313 -&gt; DPI66576 -&gt; DPI64592 -&gt; DPI63919 -&gt; DPI66449 -&gt; DPI64196 -&gt; DPI66221</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>63.66179793000001</v>
+        <v>977.57884312</v>
       </c>
       <c r="F24" t="n">
-        <v>150</v>
+        <v>980</v>
       </c>
       <c r="G24" t="n">
-        <v>42.44119862</v>
+        <v>99.7529431755102</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>427</v>
       </c>
       <c r="I24" t="n">
-        <v>64050</v>
+        <v>238990.7</v>
       </c>
     </row>
     <row r="25">
@@ -1293,23 +1293,23 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>DPI70213 -&gt; DPI66067 -&gt; DPI63915 -&gt; DPI64724 -&gt; DPI64297 -&gt; DPI67178 -&gt; DPI66742 -&gt; DPI64436</t>
+          <t>DPI64136 -&gt; DPI67178 -&gt; DPI66742 -&gt; DPI64297 -&gt; DPI64724 -&gt; DPI63915 -&gt; DPI66067 -&gt; DPI70213</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>930.0945775</v>
+        <v>913.863355</v>
       </c>
       <c r="F28" t="n">
         <v>980</v>
       </c>
       <c r="G28" t="n">
-        <v>94.9076099489796</v>
+        <v>93.25136275510204</v>
       </c>
       <c r="H28" t="n">
-        <v>838</v>
+        <v>849</v>
       </c>
       <c r="I28" t="n">
-        <v>373839.8</v>
+        <v>377448.9</v>
       </c>
     </row>
     <row r="29">
@@ -1320,21 +1320,21 @@
         <v>1613</v>
       </c>
       <c r="C29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>DPI66923 -&gt; DFT80077 -&gt; DPI66636 -&gt; DPI64634 -&gt; DPI67180 -&gt; DPI70296 -&gt; DPI63976 -&gt; DPI64742 -&gt; DPI67148 -&gt; DPI67187</t>
+          <t>DPI67187 -&gt; DPI67148 -&gt; DPI64742 -&gt; DPI63976 -&gt; DPI70296 -&gt; DPI67180 -&gt; DPI64634 -&gt; DPI67224 -&gt; DPI64666</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>971.5546000000001</v>
+        <v>960.0006999999999</v>
       </c>
       <c r="F29" t="n">
         <v>980</v>
       </c>
       <c r="G29" t="n">
-        <v>99.13822448979592</v>
+        <v>97.95925510204081</v>
       </c>
       <c r="H29" t="n">
         <v>978</v>
@@ -1351,27 +1351,27 @@
         <v>1613</v>
       </c>
       <c r="C30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DPI70316 -&gt; DPI64094 -&gt; DPI66128 -&gt; DPI70096 -&gt; DPI64037 -&gt; DPI66172 -&gt; DPI64057 -&gt; DPI63802 -&gt; DPI66051 -&gt; DPI64169 -&gt; DPI66715</t>
+          <t>DPI66715 -&gt; DPI64169 -&gt; DPI66051 -&gt; DPI63802 -&gt; DPI64057 -&gt; DPI66172 -&gt; DPI64037 -&gt; DPI70096 -&gt; DPI66128 -&gt; DPI64094</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>973.05680818</v>
+        <v>924.6208881799998</v>
       </c>
       <c r="F30" t="n">
         <v>980</v>
       </c>
       <c r="G30" t="n">
-        <v>99.29151103877551</v>
+        <v>94.34907022244896</v>
       </c>
       <c r="H30" t="n">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="I30" t="n">
-        <v>400415.9</v>
+        <v>399103.5</v>
       </c>
     </row>
     <row r="31">
@@ -1382,27 +1382,27 @@
         <v>1613</v>
       </c>
       <c r="C31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>DPI66653 -&gt; DPI66449 -&gt; DPI66576 -&gt; DPI64592 -&gt; DPI63919 -&gt; DPI64431 -&gt; DPI70047 -&gt; DPI66679</t>
+          <t>DPI64480 -&gt; DPI66078 -&gt; DPI64433 -&gt; DPI66658 -&gt; DPI70105 -&gt; DPI64436 -&gt; DPI64456 -&gt; DPI66574 -&gt; DPI66946</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>918.7296381</v>
+        <v>939.6887725000003</v>
       </c>
       <c r="F31" t="n">
         <v>980</v>
       </c>
       <c r="G31" t="n">
-        <v>93.74792225510204</v>
+        <v>95.88660943877554</v>
       </c>
       <c r="H31" t="n">
-        <v>714</v>
+        <v>867</v>
       </c>
       <c r="I31" t="n">
-        <v>333155.4</v>
+        <v>383354.7</v>
       </c>
     </row>
     <row r="32">
@@ -1413,27 +1413,27 @@
         <v>1613</v>
       </c>
       <c r="C32" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>DPI64480 -&gt; DPI66078 -&gt; DPI64433 -&gt; DPI66658 -&gt; DPI70105 -&gt; DPI64456 -&gt; DPI66574 -&gt; DPI66946 -&gt; DPI64136</t>
+          <t>DPI66923 -&gt; DFT80077 -&gt; DPI66636 -&gt; DPI66209 -&gt; DPI70190 -&gt; DPI70253 -&gt; DPI64056 -&gt; DPI67074 -&gt; DPI64628 -&gt; DPI64119 -&gt; DFT80078</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>923.4575500000002</v>
+        <v>861.4462600000002</v>
       </c>
       <c r="F32" t="n">
         <v>980</v>
       </c>
       <c r="G32" t="n">
-        <v>94.23036224489798</v>
+        <v>87.90267959183676</v>
       </c>
       <c r="H32" t="n">
-        <v>868</v>
+        <v>933</v>
       </c>
       <c r="I32" t="n">
-        <v>383682.8</v>
+        <v>405009.3</v>
       </c>
     </row>
     <row r="33">
@@ -1448,23 +1448,23 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DPI64666 -&gt; DPI66209 -&gt; DPI67224 -&gt; DPI70190 -&gt; DPI70253 -&gt; DPI64056 -&gt; DPI67074 -&gt; DPI64628 -&gt; DPI64119 -&gt; DFT80078</t>
+          <t>DPI66679 -&gt; DPI70047 -&gt; DPI64431 -&gt; DPI66653 -&gt; DPI66153 -&gt; DPI67072 -&gt; DPI70081 -&gt; DPI66154 -&gt; DPI66373 -&gt; DPI70009</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>849.8923600000001</v>
+        <v>906.4061132999999</v>
       </c>
       <c r="F33" t="n">
         <v>980</v>
       </c>
       <c r="G33" t="n">
-        <v>86.72371020408164</v>
+        <v>92.49041972448978</v>
       </c>
       <c r="H33" t="n">
-        <v>929</v>
+        <v>705</v>
       </c>
       <c r="I33" t="n">
-        <v>403696.9</v>
+        <v>330202.5</v>
       </c>
     </row>
     <row r="34">
@@ -1475,27 +1475,27 @@
         <v>1613</v>
       </c>
       <c r="C34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>DPI66221 -&gt; DPI64196 -&gt; DPI66373 -&gt; DPI66153 -&gt; DPI67072 -&gt; DPI70081 -&gt; DPI66154 -&gt; DPI66313 -&gt; DPI63827 -&gt; DPI70009</t>
+          <t>DPI66387 -&gt; DPI66339 -&gt; DPI66590 -&gt; DFT80044 -&gt; DPI70255 -&gt; DPI66645 -&gt; DPI64413 -&gt; DPI64244 -&gt; DFT80088 -&gt; DPI64216 -&gt; DPI70316</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>965.25531832</v>
+        <v>962.36697241</v>
       </c>
       <c r="F34" t="n">
         <v>980</v>
       </c>
       <c r="G34" t="n">
-        <v>98.49544064489795</v>
+        <v>98.20071147040817</v>
       </c>
       <c r="H34" t="n">
-        <v>420</v>
+        <v>594</v>
       </c>
       <c r="I34" t="n">
-        <v>236694</v>
+        <v>293783.4</v>
       </c>
     </row>
     <row r="35">
@@ -1506,27 +1506,27 @@
         <v>1613</v>
       </c>
       <c r="C35" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>DPI66387 -&gt; DPI66339 -&gt; DPI66590 -&gt; DPI70255 -&gt; DPI66645 -&gt; DPI64413 -&gt; DPI64244 -&gt; DFT80088 -&gt; DPI64216 -&gt; DFT80044</t>
+          <t>DPI63958 -&gt; DPI64686 -&gt; DPI66203 -&gt; DPI66289 -&gt; DPI64039 -&gt; DPI66069 -&gt; DPI64301 -&gt; DPI64218</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>913.93105241</v>
+        <v>877.69884627</v>
       </c>
       <c r="F35" t="n">
         <v>980</v>
       </c>
       <c r="G35" t="n">
-        <v>93.25827065408163</v>
+        <v>89.5611067622449</v>
       </c>
       <c r="H35" t="n">
-        <v>590</v>
+        <v>198</v>
       </c>
       <c r="I35" t="n">
-        <v>292471</v>
+        <v>163855.8</v>
       </c>
     </row>
     <row r="36">
@@ -1537,58 +1537,58 @@
         <v>1613</v>
       </c>
       <c r="C36" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>DPI64052 -&gt; DPI66179 -&gt; DPI66597 -&gt; DPI63958 -&gt; DPI66039 -&gt; DPI66307 -&gt; DPI64638</t>
+          <t>DPI70142 -&gt; DPI64052 -&gt; DPI66179 -&gt; DPI66597 -&gt; DPI67121 -&gt; DPI64450 -&gt; DPI66039 -&gt; DPI66307 -&gt; DPI64638</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>864.4288809000002</v>
+        <v>971.3478097000002</v>
       </c>
       <c r="F36" t="n">
         <v>980</v>
       </c>
       <c r="G36" t="n">
-        <v>88.20702866326533</v>
+        <v>99.11712343877554</v>
       </c>
       <c r="H36" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="I36" t="n">
-        <v>164840.1</v>
+        <v>165824.4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B37" t="n">
         <v>1613</v>
       </c>
       <c r="C37" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>DPI64218 -&gt; DPI66289 -&gt; DPI64039 -&gt; DPI64301 -&gt; DPI66069 -&gt; DPI64686 -&gt; DPI66203 -&gt; DPI64450 -&gt; DPI67121</t>
+          <t>DPI64203 -&gt; DPI67050 -&gt; DPI66122 -&gt; DPI64350 -&gt; DPI66729 -&gt; DPI64246 -&gt; DPI63936 -&gt; DPI66326 -&gt; DPI64418 -&gt; DPI66119 -&gt; DPI70256</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>920.95597714</v>
+        <v>929.4353752200001</v>
       </c>
       <c r="F37" t="n">
         <v>980</v>
       </c>
       <c r="G37" t="n">
-        <v>93.97509970816326</v>
+        <v>94.8403444102041</v>
       </c>
       <c r="H37" t="n">
-        <v>202</v>
+        <v>997</v>
       </c>
       <c r="I37" t="n">
-        <v>165168.2</v>
+        <v>426007.7</v>
       </c>
     </row>
     <row r="38">
@@ -1599,27 +1599,27 @@
         <v>1613</v>
       </c>
       <c r="C38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>DPI66094 -&gt; DPI66389 -&gt; DPI65993 -&gt; DPI70261 -&gt; DPI66622 -&gt; DPI70148 -&gt; DPI66621 -&gt; DPI70320 -&gt; DPI70057</t>
+          <t>DPI70176 -&gt; DPI66755 -&gt; DPI64026 -&gt; DPI70261 -&gt; DPI64469 -&gt; DPI64106 -&gt; DPI66622 -&gt; DPI66389 -&gt; DPI70057 -&gt; DPI66626</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>959.39262601</v>
+        <v>980.2124593699998</v>
       </c>
       <c r="F38" t="n">
         <v>980</v>
       </c>
       <c r="G38" t="n">
-        <v>97.89720673571428</v>
+        <v>100.021679527551</v>
       </c>
       <c r="H38" t="n">
-        <v>273</v>
+        <v>1024</v>
       </c>
       <c r="I38" t="n">
-        <v>188463.3</v>
+        <v>434866.4</v>
       </c>
     </row>
     <row r="39">
@@ -1627,30 +1627,30 @@
         <v>3</v>
       </c>
       <c r="B39" t="n">
-        <v>1613</v>
+        <v>1109</v>
       </c>
       <c r="C39" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>DPI67042 -&gt; DPI66378 -&gt; DPI66688 -&gt; DPI66042 -&gt; DPI70104 -&gt; DPI66359 -&gt; DPI66400 -&gt; DPI70091 -&gt; DPI66241</t>
+          <t>DPI63813 -&gt; DPI66640 -&gt; DPI64252 -&gt; DPI67062 -&gt; DPI66532 -&gt; DPI70022 -&gt; DPI70039 -&gt; DPI66239 -&gt; DPI66591 -&gt; DPI66944 -&gt; DPI66945</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>967.08362267</v>
+        <v>637.97845751</v>
       </c>
       <c r="F39" t="n">
-        <v>980</v>
+        <v>660</v>
       </c>
       <c r="G39" t="n">
-        <v>98.6820023132653</v>
+        <v>96.6634026530303</v>
       </c>
       <c r="H39" t="n">
-        <v>253</v>
+        <v>930</v>
       </c>
       <c r="I39" t="n">
-        <v>181901.3</v>
+        <v>350964</v>
       </c>
     </row>
     <row r="40">
@@ -1658,30 +1658,30 @@
         <v>3</v>
       </c>
       <c r="B40" t="n">
-        <v>1109</v>
+        <v>1613</v>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>DPI66626 -&gt; DPI66578 -&gt; DPI66437</t>
+          <t>DPI66377 -&gt; DPI63951 -&gt; DPI65969 -&gt; DPI67014 -&gt; DPI64140 -&gt; DPI67181 -&gt; DPI66031 -&gt; DPI64408 -&gt; DPI64227 -&gt; DPI64520</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>373.22844717</v>
+        <v>980.6777222499999</v>
       </c>
       <c r="F40" t="n">
-        <v>660</v>
+        <v>980</v>
       </c>
       <c r="G40" t="n">
-        <v>56.54976472272727</v>
+        <v>100.0691553316326</v>
       </c>
       <c r="H40" t="n">
-        <v>206</v>
+        <v>284</v>
       </c>
       <c r="I40" t="n">
-        <v>144768.8</v>
+        <v>192072.4</v>
       </c>
     </row>
     <row r="41">
@@ -1692,27 +1692,27 @@
         <v>1613</v>
       </c>
       <c r="C41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>DPI70140 -&gt; DPI64650 -&gt; DPI66410 -&gt; DPI66280 -&gt; DPI65877 -&gt; DPI64240 -&gt; DPI66970 -&gt; DPI67126 -&gt; DPI64470 -&gt; DPI64520</t>
+          <t>DPI66224 -&gt; DPI64310 -&gt; DPI70032 -&gt; DPI66999 -&gt; DPI64079 -&gt; DPI64237 -&gt; DPI66029 -&gt; DPI64102 -&gt; DPI64336 -&gt; DPI66125 -&gt; DPI66497 -&gt; DPI64525 -&gt; DPI64145 -&gt; DPI64317 -&gt; DPI66929</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>981.73877239</v>
+        <v>822.36630804</v>
       </c>
       <c r="F41" t="n">
         <v>980</v>
       </c>
       <c r="G41" t="n">
-        <v>100.1774257540816</v>
+        <v>83.91492939183674</v>
       </c>
       <c r="H41" t="n">
-        <v>271</v>
+        <v>977</v>
       </c>
       <c r="I41" t="n">
-        <v>187807.1</v>
+        <v>419445.7</v>
       </c>
     </row>
     <row r="42">
@@ -1720,30 +1720,30 @@
         <v>3</v>
       </c>
       <c r="B42" t="n">
-        <v>1613</v>
+        <v>407</v>
       </c>
       <c r="C42" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>DPI70216 -&gt; DPI64741 -&gt; DPI64428 -&gt; DPI63945 -&gt; DPI66940 -&gt; DPI66119 -&gt; DPI64720 -&gt; DPI67093 -&gt; DPI64600</t>
+          <t>DPI64279 -&gt; DPI70058 -&gt; DPI64641 -&gt; DPI63999 -&gt; DPI66652 -&gt; DPI64703 -&gt; DPI64043</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>752.7613463700001</v>
+        <v>304.60346063</v>
       </c>
       <c r="F42" t="n">
-        <v>980</v>
+        <v>350</v>
       </c>
       <c r="G42" t="n">
-        <v>76.81238228265308</v>
+        <v>87.02956017999999</v>
       </c>
       <c r="H42" t="n">
-        <v>998</v>
+        <v>1002</v>
       </c>
       <c r="I42" t="n">
-        <v>426335.8</v>
+        <v>329149.8</v>
       </c>
     </row>
     <row r="43">
@@ -1754,27 +1754,27 @@
         <v>1613</v>
       </c>
       <c r="C43" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>DFT80058 -&gt; DPI64291 -&gt; DPI66104 -&gt; DPI66730 -&gt; DPI66944 -&gt; DPI66591 -&gt; DPI66239 -&gt; DPI70039 -&gt; DPI70022 -&gt; DPI66532 -&gt; DPI67062 -&gt; DPI64252 -&gt; DPI64317</t>
+          <t>DPI66400 -&gt; DPI66410 -&gt; DPI66280 -&gt; DPI66926 -&gt; DPI65998 -&gt; DPI66126 -&gt; DPI66076 -&gt; DPI67110 -&gt; DPI66386</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>770.95050487</v>
+        <v>971.9376120800001</v>
       </c>
       <c r="F43" t="n">
         <v>980</v>
       </c>
       <c r="G43" t="n">
-        <v>78.66841886428571</v>
+        <v>99.17730735510204</v>
       </c>
       <c r="H43" t="n">
-        <v>1041</v>
+        <v>274</v>
       </c>
       <c r="I43" t="n">
-        <v>440444.1</v>
+        <v>188791.4</v>
       </c>
     </row>
     <row r="44">
@@ -1785,27 +1785,27 @@
         <v>1613</v>
       </c>
       <c r="C44" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>DPI70256 -&gt; DPI64203 -&gt; DPI67050 -&gt; DPI64418 -&gt; DPI66122 -&gt; DPI66729 -&gt; DPI64350 -&gt; DPI66326 -&gt; DPI64246 -&gt; DPI63936 -&gt; DPI64703 -&gt; DPI66652 -&gt; DPI70058 -&gt; DPI64279</t>
+          <t>DPI64073 -&gt; DPI66548 -&gt; DPI64083 -&gt; DPI63978 -&gt; DPI64752 -&gt; DPI66733 -&gt; DPI64602 -&gt; DPI65779 -&gt; DPI64019 -&gt; DPI66194</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>975.1779477099999</v>
+        <v>970.88138968</v>
       </c>
       <c r="F44" t="n">
         <v>980</v>
       </c>
       <c r="G44" t="n">
-        <v>99.50795384795917</v>
+        <v>99.06952955918366</v>
       </c>
       <c r="H44" t="n">
-        <v>1042</v>
+        <v>805</v>
       </c>
       <c r="I44" t="n">
-        <v>440772.2000000001</v>
+        <v>363012.5</v>
       </c>
     </row>
     <row r="45">
@@ -1816,27 +1816,27 @@
         <v>1613</v>
       </c>
       <c r="C45" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>DPI66945 -&gt; DPI63813 -&gt; DPI66640 -&gt; DPI66125 -&gt; DPI64336 -&gt; DPI64237 -&gt; DPI66029 -&gt; DPI64102 -&gt; DPI66497 -&gt; DPI64525 -&gt; DPI64145 -&gt; DPI64079 -&gt; DPI63999 -&gt; DPI64641 -&gt; DPI66999 -&gt; DPI70032 -&gt; DPI64310 -&gt; DPI66224 -&gt; DPI64043</t>
+          <t>DPI66578 -&gt; DPI67042 -&gt; DPI66378 -&gt; DPI63950 -&gt; DPI66042 -&gt; DPI70104 -&gt; DPI66522 -&gt; DPI66053</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>913.7526912600001</v>
+        <v>983.9871409399999</v>
       </c>
       <c r="F45" t="n">
         <v>980</v>
       </c>
       <c r="G45" t="n">
-        <v>93.24007053673471</v>
+        <v>100.4068511163265</v>
       </c>
       <c r="H45" t="n">
-        <v>1034</v>
+        <v>254</v>
       </c>
       <c r="I45" t="n">
-        <v>438147.4</v>
+        <v>182229.4</v>
       </c>
     </row>
     <row r="46">
@@ -1851,23 +1851,23 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>DPI66386 -&gt; DPI66194 -&gt; DPI64019 -&gt; DPI65779 -&gt; DPI67014 -&gt; DPI66733 -&gt; DPI63978 -&gt; DPI64706 -&gt; DPI64083 -&gt; DPI64073</t>
+          <t>DPI64377 -&gt; DPI63823 -&gt; DPI70140 -&gt; DPI66241 -&gt; DPI70091 -&gt; DPI64331 -&gt; DPI65919 -&gt; DPI66619 -&gt; DPI67064 -&gt; DPI66998</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>968.4121970399999</v>
+        <v>985.1537263599998</v>
       </c>
       <c r="F46" t="n">
         <v>980</v>
       </c>
       <c r="G46" t="n">
-        <v>98.81757112653059</v>
+        <v>100.525890444898</v>
       </c>
       <c r="H46" t="n">
-        <v>1030</v>
+        <v>248</v>
       </c>
       <c r="I46" t="n">
-        <v>436835</v>
+        <v>180260.8</v>
       </c>
     </row>
     <row r="47">
@@ -1875,30 +1875,30 @@
         <v>3</v>
       </c>
       <c r="B47" t="n">
-        <v>1613</v>
+        <v>407</v>
       </c>
       <c r="C47" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>DPI64377 -&gt; DFT80095 -&gt; DPI70069 -&gt; DPI67021 -&gt; DPI64207 -&gt; DPI70306 -&gt; DPI64408 -&gt; DPI66333 -&gt; DPI66926 -&gt; DPI64250 -&gt; DPI64577</t>
+          <t>DFT80058 -&gt; DPI64291 -&gt; DPI66104 -&gt; DPI66730</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>942.46232549</v>
+        <v>237.97301692</v>
       </c>
       <c r="F47" t="n">
-        <v>980</v>
+        <v>350</v>
       </c>
       <c r="G47" t="n">
-        <v>96.16962504999999</v>
+        <v>67.99229054857143</v>
       </c>
       <c r="H47" t="n">
-        <v>302</v>
+        <v>889</v>
       </c>
       <c r="I47" t="n">
-        <v>197978.2</v>
+        <v>300911.1</v>
       </c>
     </row>
     <row r="48">
@@ -1906,30 +1906,30 @@
         <v>3</v>
       </c>
       <c r="B48" t="n">
-        <v>1613</v>
+        <v>407</v>
       </c>
       <c r="C48" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>DPI66377 -&gt; DPI63951 -&gt; DPI66501 -&gt; DPI64140 -&gt; DPI65998 -&gt; DPI66538 -&gt; DPI65969 -&gt; DPI66126 -&gt; DPI65919 -&gt; DPI64331</t>
+          <t>DPI66437 -&gt; DPI66573</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>948.49393233</v>
+        <v>291.50053035</v>
       </c>
       <c r="F48" t="n">
-        <v>980</v>
+        <v>350</v>
       </c>
       <c r="G48" t="n">
-        <v>96.78509513571429</v>
+        <v>83.28586581428571</v>
       </c>
       <c r="H48" t="n">
-        <v>270</v>
+        <v>212</v>
       </c>
       <c r="I48" t="n">
-        <v>187479</v>
+        <v>131728.8</v>
       </c>
     </row>
     <row r="49">
@@ -1940,27 +1940,27 @@
         <v>1613</v>
       </c>
       <c r="C49" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>DPI66076 -&gt; DPI65789 -&gt; DPI66136 -&gt; DPI67183 -&gt; DPI64602 -&gt; DPI65915 -&gt; DPI66522 -&gt; DPI66053 -&gt; DPI66685</t>
+          <t>DFT80095 -&gt; DPI70069 -&gt; DPI67021 -&gt; DPI64207 -&gt; DPI64706 -&gt; DPI70306 -&gt; DPI66333 -&gt; DPI64240 -&gt; DPI66014 -&gt; DPI66359 -&gt; DPI66094</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>976.4924243199999</v>
+        <v>977.3896428099999</v>
       </c>
       <c r="F49" t="n">
         <v>980</v>
       </c>
       <c r="G49" t="n">
-        <v>99.64208411428571</v>
+        <v>99.73363702142856</v>
       </c>
       <c r="H49" t="n">
-        <v>268</v>
+        <v>994</v>
       </c>
       <c r="I49" t="n">
-        <v>186822.8</v>
+        <v>425023.4</v>
       </c>
     </row>
     <row r="50">
@@ -1971,27 +1971,27 @@
         <v>1613</v>
       </c>
       <c r="C50" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>DPI66031 -&gt; DPI67181 -&gt; DPI64752 -&gt; DPI64106 -&gt; DPI66548 -&gt; DPI64469 -&gt; DPI64227 -&gt; DPI67118 -&gt; DPI63950</t>
+          <t>DPI66688 -&gt; DPI66422 -&gt; DPI65840 -&gt; DPI64650 -&gt; DPI67217 -&gt; DPI66191 -&gt; DPI64577 -&gt; DPI66685</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>966.40726765</v>
+        <v>932.9729845700001</v>
       </c>
       <c r="F50" t="n">
         <v>980</v>
       </c>
       <c r="G50" t="n">
-        <v>98.61298649489795</v>
+        <v>95.20132495612246</v>
       </c>
       <c r="H50" t="n">
-        <v>1040</v>
+        <v>263</v>
       </c>
       <c r="I50" t="n">
-        <v>440116</v>
+        <v>185182.3</v>
       </c>
     </row>
     <row r="51">
@@ -2002,27 +2002,27 @@
         <v>1613</v>
       </c>
       <c r="C51" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>DPI63823 -&gt; DPI66191 -&gt; DPI67217 -&gt; DPI65840 -&gt; DPI66422 -&gt; DPI66014 -&gt; DPI64026 -&gt; DPI66755 -&gt; DPI70176</t>
+          <t>DPI64250 -&gt; DPI67118 -&gt; DPI65877 -&gt; DPI66970 -&gt; DPI67126 -&gt; DPI64470 -&gt; DPI65993 -&gt; DPI70148 -&gt; DPI66621 -&gt; DPI70320</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>979.27092405</v>
+        <v>985.6485894299999</v>
       </c>
       <c r="F51" t="n">
         <v>980</v>
       </c>
       <c r="G51" t="n">
-        <v>99.92560449489795</v>
+        <v>100.5763866765306</v>
       </c>
       <c r="H51" t="n">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="I51" t="n">
-        <v>185838.5</v>
+        <v>191088.1</v>
       </c>
     </row>
     <row r="52">
@@ -2030,30 +2030,30 @@
         <v>3</v>
       </c>
       <c r="B52" t="n">
-        <v>1613</v>
+        <v>1109</v>
       </c>
       <c r="C52" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>DPI66573 -&gt; DPI66998 -&gt; DPI67110 -&gt; DPI67179 -&gt; DPI66660 -&gt; DPI66521 -&gt; DPI64631 -&gt; DPI66619 -&gt; DPI67064</t>
+          <t>DPI64600 -&gt; DPI67093 -&gt; DPI64720 -&gt; DPI66940 -&gt; DPI63945 -&gt; DPI64428 -&gt; DPI64741 -&gt; DPI70216</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>971.8510420099999</v>
+        <v>609.5991484699999</v>
       </c>
       <c r="F52" t="n">
-        <v>980</v>
+        <v>660</v>
       </c>
       <c r="G52" t="n">
-        <v>99.16847367448979</v>
+        <v>92.36350734393939</v>
       </c>
       <c r="H52" t="n">
-        <v>252</v>
+        <v>987</v>
       </c>
       <c r="I52" t="n">
-        <v>181573.2</v>
+        <v>367197.6</v>
       </c>
     </row>
     <row r="53">
@@ -2061,30 +2061,30 @@
         <v>3</v>
       </c>
       <c r="B53" t="n">
-        <v>207</v>
+        <v>1613</v>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>DPI66929</t>
+          <t>DPI67179 -&gt; DPI64631 -&gt; DPI66501 -&gt; DPI65915 -&gt; DPI66538 -&gt; DPI67183 -&gt; DPI66136 -&gt; DPI65789 -&gt; DPI66521 -&gt; DPI66660</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>129.31327658</v>
+        <v>974.4717832899998</v>
       </c>
       <c r="F53" t="n">
-        <v>150</v>
+        <v>980</v>
       </c>
       <c r="G53" t="n">
-        <v>86.20885105333333</v>
+        <v>99.43589625408161</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="I53" t="n">
-        <v>64050</v>
+        <v>185838.5</v>
       </c>
     </row>
     <row r="54">
@@ -2123,30 +2123,30 @@
         <v>5</v>
       </c>
       <c r="B55" t="n">
-        <v>207</v>
+        <v>1613</v>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>DPI70309</t>
+          <t>DPI70323 -&gt; DPI64226 -&gt; DPI70018 -&gt; DPI66441 -&gt; DPI64549 -&gt; DPI70242 -&gt; DPI70309</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>54.18531179999999</v>
+        <v>833.1656819000001</v>
       </c>
       <c r="F55" t="n">
-        <v>150</v>
+        <v>980</v>
       </c>
       <c r="G55" t="n">
-        <v>36.1235412</v>
+        <v>85.01690631632654</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>704</v>
       </c>
       <c r="I55" t="n">
-        <v>64050</v>
+        <v>329874.4</v>
       </c>
     </row>
     <row r="56">
@@ -2161,11 +2161,11 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>DPI64737 -&gt; DPI66927 -&gt; DPI64655 -&gt; DPI66620</t>
+          <t>DPI66620 -&gt; DPI64655 -&gt; DPI66927 -&gt; DPI64737</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>456.3569774</v>
+        <v>456.3569773999999</v>
       </c>
       <c r="F56" t="n">
         <v>660</v>
@@ -2192,54 +2192,23 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>DPI65995 -&gt; DPI66445 -&gt; DPI64122 -&gt; DPI64494 -&gt; DPI67086 -&gt; DPI64683 -&gt; DPI70144 -&gt; DPI64549</t>
+          <t>DPI67135 -&gt; DPI65995 -&gt; DPI66445 -&gt; DPI64122 -&gt; DPI64494 -&gt; DPI67086 -&gt; DPI64683 -&gt; DPI70144</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>951.0663683000001</v>
+        <v>952.8232583</v>
       </c>
       <c r="F57" t="n">
         <v>980</v>
       </c>
       <c r="G57" t="n">
-        <v>97.04758860204083</v>
+        <v>97.22686309183673</v>
       </c>
       <c r="H57" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I57" t="n">
-        <v>110047.4</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>5</v>
-      </c>
-      <c r="B58" t="n">
-        <v>1613</v>
-      </c>
-      <c r="C58" t="n">
-        <v>6</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>DPI70323 -&gt; DPI64226 -&gt; DPI70018 -&gt; DPI66441 -&gt; DPI70242 -&gt; DPI67135</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>780.7372601000001</v>
-      </c>
-      <c r="F58" t="n">
-        <v>980</v>
-      </c>
-      <c r="G58" t="n">
-        <v>79.66706735714286</v>
-      </c>
-      <c r="H58" t="n">
-        <v>703</v>
-      </c>
-      <c r="I58" t="n">
-        <v>329546.3</v>
+        <v>109719.3</v>
       </c>
     </row>
   </sheetData>

--- a/secondary_logistics_routes.xlsx
+++ b/secondary_logistics_routes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,30 +480,30 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1613</v>
+        <v>407</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DPI63929 -&gt; DPI66395 -&gt; DPI66100 -&gt; DPI64175 -&gt; DPI67004 -&gt; DPI66555 -&gt; DPI66461 -&gt; DPI70031</t>
+          <t>DPI66938 -&gt; DPI64644 -&gt; DPI67002</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>900.3305937299998</v>
+        <v>310.82337</v>
       </c>
       <c r="F2" t="n">
-        <v>980</v>
+        <v>350</v>
       </c>
       <c r="G2" t="n">
-        <v>91.87046874795917</v>
+        <v>88.80667714285713</v>
       </c>
       <c r="H2" t="n">
-        <v>885</v>
+        <v>960</v>
       </c>
       <c r="I2" t="n">
-        <v>389260.5</v>
+        <v>318654</v>
       </c>
     </row>
     <row r="3">
@@ -511,30 +511,30 @@
         <v>0</v>
       </c>
       <c r="B3" t="n">
-        <v>1109</v>
+        <v>1613</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DPI66091 -&gt; DPI64374 -&gt; DPI70166 -&gt; DPI64118 -&gt; DPI70095 -&gt; DPI63904</t>
+          <t>DPI64254 -&gt; DPI63929 -&gt; DPI66395 -&gt; DPI66100 -&gt; DPI64175 -&gt; DPI67004 -&gt; DPI66555 -&gt; DPI70165</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>637.47902</v>
+        <v>831.4212860399999</v>
       </c>
       <c r="F3" t="n">
-        <v>660</v>
+        <v>980</v>
       </c>
       <c r="G3" t="n">
-        <v>96.58773030303031</v>
+        <v>84.83890673877551</v>
       </c>
       <c r="H3" t="n">
-        <v>925</v>
+        <v>874</v>
       </c>
       <c r="I3" t="n">
-        <v>349540</v>
+        <v>385651.4</v>
       </c>
     </row>
     <row r="4">
@@ -542,30 +542,30 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>407</v>
+        <v>1613</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DPI67002 -&gt; DPI64644 -&gt; DPI66938</t>
+          <t>DPI66995 -&gt; DPI70031 -&gt; DPI64606 -&gt; DPI64462 -&gt; DPI67043 -&gt; DPI65927 -&gt; DPI65981 -&gt; DPI67245 -&gt; DPI64711 -&gt; DPI70082</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>310.82337</v>
+        <v>983.2815564499998</v>
       </c>
       <c r="F4" t="n">
-        <v>350</v>
+        <v>980</v>
       </c>
       <c r="G4" t="n">
-        <v>88.80667714285713</v>
+        <v>100.3348526989796</v>
       </c>
       <c r="H4" t="n">
-        <v>960</v>
+        <v>297</v>
       </c>
       <c r="I4" t="n">
-        <v>318654</v>
+        <v>196337.7</v>
       </c>
     </row>
     <row r="5">
@@ -576,27 +576,27 @@
         <v>1613</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DPI64254 -&gt; DPI64462 -&gt; DPI64606 -&gt; DPI64711 -&gt; DPI67245 -&gt; DPI64364 -&gt; DPI65825 -&gt; DPI66265 -&gt; DPI64694</t>
+          <t>DPI66091 -&gt; DPI64374 -&gt; DPI70166 -&gt; DPI64118 -&gt; DPI70095 -&gt; DPI63904 -&gt; DPI66669</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>890.5883619700001</v>
+        <v>774.04216483</v>
       </c>
       <c r="F5" t="n">
         <v>980</v>
       </c>
       <c r="G5" t="n">
-        <v>90.87636346632654</v>
+        <v>78.98389437040817</v>
       </c>
       <c r="H5" t="n">
-        <v>282</v>
+        <v>928</v>
       </c>
       <c r="I5" t="n">
-        <v>191416.2</v>
+        <v>403368.8</v>
       </c>
     </row>
     <row r="6">
@@ -604,30 +604,30 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>1613</v>
+        <v>407</v>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DPI64299 -&gt; DPI64001 -&gt; DPI63902 -&gt; DPI64563 -&gt; DPI66329 -&gt; DPI66127 -&gt; DPI65841 -&gt; DPI64137 -&gt; DPI66748 -&gt; DPI64253 -&gt; DPI64543 -&gt; DPI63898</t>
+          <t>DPI64108 -&gt; DPI67138 -&gt; DPI70149</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>974.8624757700002</v>
+        <v>300.30391</v>
       </c>
       <c r="F6" t="n">
-        <v>980</v>
+        <v>350</v>
       </c>
       <c r="G6" t="n">
-        <v>99.47576283367349</v>
+        <v>85.80111714285714</v>
       </c>
       <c r="H6" t="n">
-        <v>823</v>
+        <v>957</v>
       </c>
       <c r="I6" t="n">
-        <v>368918.3</v>
+        <v>317904.3</v>
       </c>
     </row>
     <row r="7">
@@ -638,27 +638,27 @@
         <v>1613</v>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>DPI66372 -&gt; DPI64239 -&gt; DPI64045 -&gt; DPI66503 -&gt; DPI64000 -&gt; DPI64506 -&gt; DPI66915 -&gt; DPI67102 -&gt; DPI70035 -&gt; DPI64008 -&gt; DPI70040</t>
+          <t>DPI64694 -&gt; DPI65825 -&gt; DPI66265 -&gt; DPI64513 -&gt; DPI65824 -&gt; DPI64364 -&gt; DPI65967 -&gt; DPI70221</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>975.09293206</v>
+        <v>945.40733025</v>
       </c>
       <c r="F7" t="n">
         <v>980</v>
       </c>
       <c r="G7" t="n">
-        <v>99.49927878163265</v>
+        <v>96.47013573979592</v>
       </c>
       <c r="H7" t="n">
-        <v>655</v>
+        <v>269</v>
       </c>
       <c r="I7" t="n">
-        <v>313797.5</v>
+        <v>187150.9</v>
       </c>
     </row>
     <row r="8">
@@ -669,27 +669,27 @@
         <v>1613</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DPI70221 -&gt; DPI65967 -&gt; DPI64513 -&gt; DPI65824 -&gt; DPI65981 -&gt; DPI65927 -&gt; DPI67043 -&gt; DPI70082</t>
+          <t>DPI70327 -&gt; DPI64561 -&gt; DPI64281 -&gt; DPI66974 -&gt; DPI65827 -&gt; DPI67214 -&gt; DPI70254 -&gt; DPI66511 -&gt; DPI66512 -&gt; DPI70228 -&gt; DPI64400</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>929.7615670600001</v>
+        <v>963.35313633</v>
       </c>
       <c r="F8" t="n">
         <v>980</v>
       </c>
       <c r="G8" t="n">
-        <v>94.87362929183674</v>
+        <v>98.30134044183674</v>
       </c>
       <c r="H8" t="n">
-        <v>273</v>
+        <v>373</v>
       </c>
       <c r="I8" t="n">
-        <v>188463.3</v>
+        <v>221273.3</v>
       </c>
     </row>
     <row r="9">
@@ -704,23 +704,23 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>DPI70165 -&gt; DPI64619 -&gt; DPI64085 -&gt; DPI66060 -&gt; DPI70234 -&gt; DPI66491 -&gt; DPI66380 -&gt; DPI66953 -&gt; DPI66759 -&gt; DPI66995</t>
+          <t>DPI64590 -&gt; DPI64543 -&gt; DPI63898 -&gt; DPI65875 -&gt; DPI64361 -&gt; DPI67047 -&gt; DPI64024 -&gt; DPI66503 -&gt; DPI64045 -&gt; DPI64239</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>957.33690348</v>
+        <v>977.89186588</v>
       </c>
       <c r="F9" t="n">
         <v>980</v>
       </c>
       <c r="G9" t="n">
-        <v>97.68743913061225</v>
+        <v>99.78488427346939</v>
       </c>
       <c r="H9" t="n">
-        <v>649</v>
+        <v>562</v>
       </c>
       <c r="I9" t="n">
-        <v>311828.9</v>
+        <v>283284.2</v>
       </c>
     </row>
     <row r="10">
@@ -728,30 +728,30 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>1109</v>
+        <v>1613</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DPI66669 -&gt; DPI70149 -&gt; DPI67138 -&gt; DPI64108</t>
+          <t>DPI66461 -&gt; DPI66759 -&gt; DPI66953 -&gt; DPI66380 -&gt; DPI66491 -&gt; DPI70234 -&gt; DPI64085 -&gt; DPI66060 -&gt; DPI64619</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>436.86705483</v>
+        <v>917.9072535</v>
       </c>
       <c r="F10" t="n">
-        <v>660</v>
+        <v>980</v>
       </c>
       <c r="G10" t="n">
-        <v>66.19197800454546</v>
+        <v>93.66400545918367</v>
       </c>
       <c r="H10" t="n">
-        <v>960</v>
+        <v>642</v>
       </c>
       <c r="I10" t="n">
-        <v>359508</v>
+        <v>309532.2</v>
       </c>
     </row>
     <row r="11">
@@ -762,27 +762,27 @@
         <v>1613</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DPI66594 -&gt; DPI64091 -&gt; DPI64247 -&gt; DPI64191 -&gt; DPI70090 -&gt; DPI64024 -&gt; DPI67047 -&gt; DPI64361 -&gt; DPI65875 -&gt; DPI64590</t>
+          <t>DPI64299 -&gt; DPI64253 -&gt; DPI66748 -&gt; DPI66127 -&gt; DPI66329 -&gt; DPI64563 -&gt; DPI65841 -&gt; DPI64137 -&gt; DPI63902 -&gt; DPI64001 -&gt; DPI70090 -&gt; DPI64191</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>952.2771032599999</v>
+        <v>968.5314295600001</v>
       </c>
       <c r="F11" t="n">
         <v>980</v>
       </c>
       <c r="G11" t="n">
-        <v>97.17113298571427</v>
+        <v>98.82973771020409</v>
       </c>
       <c r="H11" t="n">
-        <v>538</v>
+        <v>855</v>
       </c>
       <c r="I11" t="n">
-        <v>275409.8</v>
+        <v>379417.5</v>
       </c>
     </row>
     <row r="12">
@@ -797,23 +797,23 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>DPI70327 -&gt; DPI65827 -&gt; DPI64561 -&gt; DPI64281 -&gt; DPI66974 -&gt; DPI67214 -&gt; DPI70254 -&gt; DPI66511 -&gt; DPI66512 -&gt; DPI70228 -&gt; DPI64400</t>
+          <t>DPI70040 -&gt; DPI70035 -&gt; DPI66915 -&gt; DPI64506 -&gt; DPI64000 -&gt; DPI67102 -&gt; DPI64008 -&gt; DPI64091 -&gt; DPI64247 -&gt; DPI66372 -&gt; DPI66594</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>963.35313633</v>
+        <v>955.8092156499999</v>
       </c>
       <c r="F12" t="n">
         <v>980</v>
       </c>
       <c r="G12" t="n">
-        <v>98.30134044183674</v>
+        <v>97.53155261734693</v>
       </c>
       <c r="H12" t="n">
-        <v>373</v>
+        <v>606</v>
       </c>
       <c r="I12" t="n">
-        <v>221273.3</v>
+        <v>297720.6</v>
       </c>
     </row>
     <row r="13">
@@ -821,30 +821,30 @@
         <v>1</v>
       </c>
       <c r="B13" t="n">
-        <v>1613</v>
+        <v>407</v>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>DPI64639 -&gt; DPI66572 -&gt; DPI64234 -&gt; DPI64149 -&gt; DPI70038 -&gt; DPI70073 -&gt; DPI64288 -&gt; DPI64352 -&gt; DPI66734 -&gt; DPI64236 -&gt; DPI66684</t>
+          <t>DPI66460 -&gt; DPI63993 -&gt; DPI64176</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>913.6278000000001</v>
+        <v>179.54226</v>
       </c>
       <c r="F13" t="n">
-        <v>980</v>
+        <v>350</v>
       </c>
       <c r="G13" t="n">
-        <v>93.22732653061226</v>
+        <v>51.29778857142857</v>
       </c>
       <c r="H13" t="n">
-        <v>1148</v>
+        <v>1209</v>
       </c>
       <c r="I13" t="n">
-        <v>475550.8</v>
+        <v>380879.1</v>
       </c>
     </row>
     <row r="14">
@@ -855,27 +855,27 @@
         <v>1613</v>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DPI64273 -&gt; DPI64665 -&gt; DPI70120 -&gt; DPI64502 -&gt; DPI66263 -&gt; DPI64104 -&gt; DPI66264</t>
+          <t>DPI64166 -&gt; DPI66102 -&gt; DPI64624 -&gt; DPI66408 -&gt; DPI66384 -&gt; DPI64392 -&gt; DPI66618 -&gt; DPI64179</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>771.89832</v>
+        <v>954.9283171000002</v>
       </c>
       <c r="F14" t="n">
         <v>980</v>
       </c>
       <c r="G14" t="n">
-        <v>78.76513469387754</v>
+        <v>97.4416650102041</v>
       </c>
       <c r="H14" t="n">
-        <v>274</v>
+        <v>1002</v>
       </c>
       <c r="I14" t="n">
-        <v>188791.4</v>
+        <v>427648.2</v>
       </c>
     </row>
     <row r="15">
@@ -883,30 +883,30 @@
         <v>1</v>
       </c>
       <c r="B15" t="n">
-        <v>207</v>
+        <v>1613</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>DPI64044</t>
+          <t>DPI70302 -&gt; DPI70179 -&gt; DPI64651 -&gt; DPI70273 -&gt; DPI66144 -&gt; DPI66262 -&gt; DPI63847 -&gt; DPI70197 -&gt; DPI66900</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>65.98963999999999</v>
+        <v>937.8021699999998</v>
       </c>
       <c r="F15" t="n">
-        <v>150</v>
+        <v>980</v>
       </c>
       <c r="G15" t="n">
-        <v>43.99309333333333</v>
+        <v>95.69409897959181</v>
       </c>
       <c r="H15" t="n">
-        <v>1218</v>
+        <v>466</v>
       </c>
       <c r="I15" t="n">
-        <v>307041</v>
+        <v>251786.6</v>
       </c>
     </row>
     <row r="16">
@@ -917,27 +917,27 @@
         <v>1613</v>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DPI64758 -&gt; DPI66659 -&gt; DPI64476 -&gt; DPI66175 -&gt; DPI66646 -&gt; DPI70041 -&gt; DPI67031 -&gt; DPI67024</t>
+          <t>DPI64409 -&gt; DPI64378 -&gt; DPI67128 -&gt; DPI64303 -&gt; DPI70100 -&gt; DPI66659 -&gt; DPI64476 -&gt; DPI63920 -&gt; DPI64255</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>974.24177015</v>
+        <v>938.73321135</v>
       </c>
       <c r="F16" t="n">
         <v>980</v>
       </c>
       <c r="G16" t="n">
-        <v>99.4124255255102</v>
+        <v>95.7891031989796</v>
       </c>
       <c r="H16" t="n">
-        <v>1057</v>
+        <v>484</v>
       </c>
       <c r="I16" t="n">
-        <v>445693.7000000001</v>
+        <v>257692.4</v>
       </c>
     </row>
     <row r="17">
@@ -952,23 +952,23 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DPI70106 -&gt; DPI70002 -&gt; DPI66335 -&gt; DPI63895 -&gt; DPI64511 -&gt; DPI66508 -&gt; DPI64484 -&gt; DPI66327 -&gt; DFT80087 -&gt; DFT80066</t>
+          <t>DPI70106 -&gt; DPI70002 -&gt; DPI66335 -&gt; DPI63817 -&gt; DPI66229 -&gt; DPI63895 -&gt; DPI64511 -&gt; DPI66508 -&gt; DFT80034 -&gt; DFT80081</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>857.7314100000001</v>
+        <v>900.6895700000001</v>
       </c>
       <c r="F17" t="n">
         <v>980</v>
       </c>
       <c r="G17" t="n">
-        <v>87.52361326530614</v>
+        <v>91.90709897959185</v>
       </c>
       <c r="H17" t="n">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="I17" t="n">
-        <v>292799.1</v>
+        <v>293455.3</v>
       </c>
     </row>
     <row r="18">
@@ -979,27 +979,27 @@
         <v>1613</v>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DPI64696 -&gt; DPI66692 -&gt; DPI64323 -&gt; DPI66618 -&gt; DPI66408 -&gt; DPI64624 -&gt; DPI66102</t>
+          <t>DPI66528 -&gt; DPI64692 -&gt; DPI67198 -&gt; DPI70317 -&gt; DPI66175 -&gt; DPI66646 -&gt; DPI70041 -&gt; DPI66734 -&gt; DPI64236</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>932.1960413500001</v>
+        <v>985.03682</v>
       </c>
       <c r="F18" t="n">
         <v>980</v>
       </c>
       <c r="G18" t="n">
-        <v>95.12204503571429</v>
+        <v>100.5139612244898</v>
       </c>
       <c r="H18" t="n">
-        <v>1120</v>
+        <v>1075</v>
       </c>
       <c r="I18" t="n">
-        <v>466364.0000000001</v>
+        <v>451599.5</v>
       </c>
     </row>
     <row r="19">
@@ -1007,30 +1007,30 @@
         <v>1</v>
       </c>
       <c r="B19" t="n">
-        <v>1613</v>
+        <v>207</v>
       </c>
       <c r="C19" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DFT80081 -&gt; DFT80034 -&gt; DPI66092 -&gt; DPI66229 -&gt; DPI63817 -&gt; DPI64559 -&gt; DPI70302 -&gt; DPI70179 -&gt; DPI66144 -&gt; DPI70273 -&gt; DPI64651 -&gt; DPI70197</t>
+          <t>DPI64044</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>976.6968200000001</v>
+        <v>65.98963999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>980</v>
+        <v>150</v>
       </c>
       <c r="G19" t="n">
-        <v>99.66294081632654</v>
+        <v>43.99309333333333</v>
       </c>
       <c r="H19" t="n">
-        <v>553</v>
+        <v>1218</v>
       </c>
       <c r="I19" t="n">
-        <v>280331.3</v>
+        <v>307041</v>
       </c>
     </row>
     <row r="20">
@@ -1041,27 +1041,27 @@
         <v>1613</v>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>DPI63822 -&gt; DPI66421 -&gt; DPI66528 -&gt; DPI63920 -&gt; DPI64692 -&gt; DPI67198 -&gt; DPI70317</t>
+          <t>DPI64696 -&gt; DPI66692 -&gt; DPI64323 -&gt; DPI64746 -&gt; DFT80087 -&gt; DPI64559 -&gt; DPI66327 -&gt; DPI64484 -&gt; DPI66092 -&gt; DFT80066</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>944.87035665</v>
+        <v>939.3430010100001</v>
       </c>
       <c r="F20" t="n">
         <v>980</v>
       </c>
       <c r="G20" t="n">
-        <v>96.41534251530612</v>
+        <v>95.85132663367347</v>
       </c>
       <c r="H20" t="n">
-        <v>489</v>
+        <v>1058</v>
       </c>
       <c r="I20" t="n">
-        <v>259332.9</v>
+        <v>446021.8</v>
       </c>
     </row>
     <row r="21">
@@ -1072,27 +1072,27 @@
         <v>1613</v>
       </c>
       <c r="C21" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DPI64647 -&gt; DPI64032 -&gt; DPI66402 -&gt; DPI64409 -&gt; DPI64378 -&gt; DPI67128 -&gt; DPI70100 -&gt; DPI64303 -&gt; DPI64255</t>
+          <t>DPI66684 -&gt; DPI67031 -&gt; DPI67024 -&gt; DPI64352 -&gt; DPI64288 -&gt; DPI70073 -&gt; DPI70038 -&gt; DPI64149 -&gt; DPI64234 -&gt; DPI66572 -&gt; DPI64639</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>931.2382842000001</v>
+        <v>965.4608400000001</v>
       </c>
       <c r="F21" t="n">
         <v>980</v>
       </c>
       <c r="G21" t="n">
-        <v>95.02431471428572</v>
+        <v>98.51641224489796</v>
       </c>
       <c r="H21" t="n">
-        <v>487</v>
+        <v>1138</v>
       </c>
       <c r="I21" t="n">
-        <v>258676.7</v>
+        <v>472269.8</v>
       </c>
     </row>
     <row r="22">
@@ -1103,27 +1103,27 @@
         <v>1613</v>
       </c>
       <c r="C22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>DPI66900 -&gt; DPI64179 -&gt; DPI64746 -&gt; DPI64392 -&gt; DPI66384 -&gt; DPI64166 -&gt; DPI66262 -&gt; DPI63847</t>
+          <t>DPI63822 -&gt; DPI66421 -&gt; DPI66402 -&gt; DPI64032 -&gt; DPI64647 -&gt; DPI64758</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>966.13878676</v>
+        <v>874.7473396499998</v>
       </c>
       <c r="F22" t="n">
         <v>980</v>
       </c>
       <c r="G22" t="n">
-        <v>98.58559048571429</v>
+        <v>89.25993261734692</v>
       </c>
       <c r="H22" t="n">
-        <v>939</v>
+        <v>471</v>
       </c>
       <c r="I22" t="n">
-        <v>406977.9</v>
+        <v>253427.1</v>
       </c>
     </row>
     <row r="23">
@@ -1131,30 +1131,30 @@
         <v>1</v>
       </c>
       <c r="B23" t="n">
-        <v>407</v>
+        <v>1613</v>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DPI66460 -&gt; DPI63993 -&gt; DPI64176</t>
+          <t>DPI66264 -&gt; DPI64104 -&gt; DPI66263 -&gt; DPI70120 -&gt; DPI64502 -&gt; DPI64665 -&gt; DPI64273</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>179.54226</v>
+        <v>771.89832</v>
       </c>
       <c r="F23" t="n">
-        <v>350</v>
+        <v>980</v>
       </c>
       <c r="G23" t="n">
-        <v>51.29778857142857</v>
+        <v>78.76513469387754</v>
       </c>
       <c r="H23" t="n">
-        <v>1209</v>
+        <v>274</v>
       </c>
       <c r="I23" t="n">
-        <v>380879.1</v>
+        <v>188791.4</v>
       </c>
     </row>
     <row r="24">
@@ -1162,30 +1162,30 @@
         <v>2</v>
       </c>
       <c r="B24" t="n">
-        <v>1613</v>
+        <v>207</v>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DPI63827 -&gt; DPI66313 -&gt; DPI66576 -&gt; DPI64592 -&gt; DPI63919 -&gt; DPI66449 -&gt; DPI64196 -&gt; DPI66221</t>
+          <t>DPI64548</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>977.57884312</v>
+        <v>118.61613</v>
       </c>
       <c r="F24" t="n">
-        <v>980</v>
+        <v>150</v>
       </c>
       <c r="G24" t="n">
-        <v>99.7529431755102</v>
+        <v>79.07742</v>
       </c>
       <c r="H24" t="n">
-        <v>427</v>
+        <v>1258</v>
       </c>
       <c r="I24" t="n">
-        <v>238990.7</v>
+        <v>315021</v>
       </c>
     </row>
     <row r="25">
@@ -1193,30 +1193,30 @@
         <v>2</v>
       </c>
       <c r="B25" t="n">
-        <v>207</v>
+        <v>407</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>DPI64548</t>
+          <t>DPI70109 -&gt; DPI66634 -&gt; DPI70214 -&gt; DPI70107 -&gt; DPI70142</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>118.61613</v>
+        <v>344.0197699900001</v>
       </c>
       <c r="F25" t="n">
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="G25" t="n">
-        <v>79.07742</v>
+        <v>98.29136285428575</v>
       </c>
       <c r="H25" t="n">
-        <v>1258</v>
+        <v>1214</v>
       </c>
       <c r="I25" t="n">
-        <v>315021</v>
+        <v>382128.6</v>
       </c>
     </row>
     <row r="26">
@@ -1224,30 +1224,30 @@
         <v>2</v>
       </c>
       <c r="B26" t="n">
-        <v>407</v>
+        <v>1613</v>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>DPI70107 -&gt; DPI70214 -&gt; DPI66634 -&gt; DPI70109</t>
+          <t>DPI66221 -&gt; DPI64196 -&gt; DPI66449 -&gt; DPI66153 -&gt; DPI67072 -&gt; DPI70081 -&gt; DPI66154 -&gt; DPI66373 -&gt; DPI70009</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>280.35797206</v>
+        <v>901.4684851999999</v>
       </c>
       <c r="F26" t="n">
-        <v>350</v>
+        <v>980</v>
       </c>
       <c r="G26" t="n">
-        <v>80.10227773142857</v>
+        <v>91.98658012244897</v>
       </c>
       <c r="H26" t="n">
-        <v>1214</v>
+        <v>418</v>
       </c>
       <c r="I26" t="n">
-        <v>382128.6</v>
+        <v>236037.8</v>
       </c>
     </row>
     <row r="27">
@@ -1262,17 +1262,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>DPI66096 -&gt; DPI64018 -&gt; DPI70229 -&gt; DPI66736 -&gt; DPI66129 -&gt; DPI64495 -&gt; DFT80080</t>
+          <t>DFT80080 -&gt; DPI64495 -&gt; DPI66129 -&gt; DPI66736 -&gt; DPI70229 -&gt; DPI64018 -&gt; DPI66096</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>945.6717099999998</v>
+        <v>945.67171</v>
       </c>
       <c r="F27" t="n">
         <v>980</v>
       </c>
       <c r="G27" t="n">
-        <v>96.49711326530611</v>
+        <v>96.49711326530613</v>
       </c>
       <c r="H27" t="n">
         <v>1253</v>
@@ -1289,27 +1289,27 @@
         <v>1613</v>
       </c>
       <c r="C28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>DPI64136 -&gt; DPI67178 -&gt; DPI66742 -&gt; DPI64297 -&gt; DPI64724 -&gt; DPI63915 -&gt; DPI66067 -&gt; DPI70213</t>
+          <t>DPI66653 -&gt; DPI64431 -&gt; DPI70047 -&gt; DPI66679 -&gt; DPI63919 -&gt; DPI64592 -&gt; DPI66576 -&gt; DPI66313 -&gt; DPI63827</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>913.863355</v>
+        <v>982.5164712200001</v>
       </c>
       <c r="F28" t="n">
         <v>980</v>
       </c>
       <c r="G28" t="n">
-        <v>93.25136275510204</v>
+        <v>100.256782777551</v>
       </c>
       <c r="H28" t="n">
-        <v>849</v>
+        <v>714</v>
       </c>
       <c r="I28" t="n">
-        <v>377448.9</v>
+        <v>333155.4</v>
       </c>
     </row>
     <row r="29">
@@ -1320,21 +1320,21 @@
         <v>1613</v>
       </c>
       <c r="C29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>DPI67187 -&gt; DPI67148 -&gt; DPI64742 -&gt; DPI63976 -&gt; DPI70296 -&gt; DPI67180 -&gt; DPI64634 -&gt; DPI67224 -&gt; DPI64666</t>
+          <t>DPI66923 -&gt; DFT80077 -&gt; DPI66636 -&gt; DPI64634 -&gt; DPI67180 -&gt; DPI70296 -&gt; DPI63976 -&gt; DPI64742 -&gt; DPI67148 -&gt; DPI67187</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>960.0006999999999</v>
+        <v>971.5546000000001</v>
       </c>
       <c r="F29" t="n">
         <v>980</v>
       </c>
       <c r="G29" t="n">
-        <v>97.95925510204081</v>
+        <v>99.13822448979592</v>
       </c>
       <c r="H29" t="n">
         <v>978</v>
@@ -1351,27 +1351,27 @@
         <v>1613</v>
       </c>
       <c r="C30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DPI66715 -&gt; DPI64169 -&gt; DPI66051 -&gt; DPI63802 -&gt; DPI64057 -&gt; DPI66172 -&gt; DPI64037 -&gt; DPI70096 -&gt; DPI66128 -&gt; DPI64094</t>
+          <t>DPI64480 -&gt; DPI66078 -&gt; DPI64433 -&gt; DPI66658 -&gt; DPI70105 -&gt; DPI64456 -&gt; DPI66574 -&gt; DPI66946 -&gt; DPI64136</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>924.6208881799998</v>
+        <v>923.4575500000002</v>
       </c>
       <c r="F30" t="n">
         <v>980</v>
       </c>
       <c r="G30" t="n">
-        <v>94.34907022244896</v>
+        <v>94.23036224489798</v>
       </c>
       <c r="H30" t="n">
-        <v>915</v>
+        <v>868</v>
       </c>
       <c r="I30" t="n">
-        <v>399103.5</v>
+        <v>383682.8</v>
       </c>
     </row>
     <row r="31">
@@ -1382,27 +1382,27 @@
         <v>1613</v>
       </c>
       <c r="C31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>DPI64480 -&gt; DPI66078 -&gt; DPI64433 -&gt; DPI66658 -&gt; DPI70105 -&gt; DPI64436 -&gt; DPI64456 -&gt; DPI66574 -&gt; DPI66946</t>
+          <t>DPI64301 -&gt; DPI66069 -&gt; DPI64039 -&gt; DPI66289 -&gt; DPI66039 -&gt; DPI66307 -&gt; DPI64638 -&gt; DPI63958</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>939.6887725000003</v>
+        <v>869.7783600100001</v>
       </c>
       <c r="F31" t="n">
         <v>980</v>
       </c>
       <c r="G31" t="n">
-        <v>95.88660943877554</v>
+        <v>88.75289387857144</v>
       </c>
       <c r="H31" t="n">
-        <v>867</v>
+        <v>192</v>
       </c>
       <c r="I31" t="n">
-        <v>383354.7</v>
+        <v>161887.2</v>
       </c>
     </row>
     <row r="32">
@@ -1413,27 +1413,27 @@
         <v>1613</v>
       </c>
       <c r="C32" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>DPI66923 -&gt; DFT80077 -&gt; DPI66636 -&gt; DPI66209 -&gt; DPI70190 -&gt; DPI70253 -&gt; DPI64056 -&gt; DPI67074 -&gt; DPI64628 -&gt; DPI64119 -&gt; DFT80078</t>
+          <t>DPI64218 -&gt; DPI66203 -&gt; DPI64686 -&gt; DPI64450 -&gt; DPI67121 -&gt; DPI66597 -&gt; DPI66179 -&gt; DPI64052</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>861.4462600000002</v>
+        <v>915.6064980300001</v>
       </c>
       <c r="F32" t="n">
         <v>980</v>
       </c>
       <c r="G32" t="n">
-        <v>87.90267959183676</v>
+        <v>93.42923449285716</v>
       </c>
       <c r="H32" t="n">
-        <v>933</v>
+        <v>211</v>
       </c>
       <c r="I32" t="n">
-        <v>405009.3</v>
+        <v>168121.1</v>
       </c>
     </row>
     <row r="33">
@@ -1444,27 +1444,27 @@
         <v>1613</v>
       </c>
       <c r="C33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DPI66679 -&gt; DPI70047 -&gt; DPI64431 -&gt; DPI66653 -&gt; DPI66153 -&gt; DPI67072 -&gt; DPI70081 -&gt; DPI66154 -&gt; DPI66373 -&gt; DPI70009</t>
+          <t>DPI70316 -&gt; DPI64094 -&gt; DPI66128 -&gt; DPI64244 -&gt; DPI70255 -&gt; DPI66590 -&gt; DPI66339 -&gt; DPI66387</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>906.4061132999999</v>
+        <v>917.84542277</v>
       </c>
       <c r="F33" t="n">
         <v>980</v>
       </c>
       <c r="G33" t="n">
-        <v>92.49041972448978</v>
+        <v>93.65769620102041</v>
       </c>
       <c r="H33" t="n">
-        <v>705</v>
+        <v>580</v>
       </c>
       <c r="I33" t="n">
-        <v>330202.5</v>
+        <v>289190</v>
       </c>
     </row>
     <row r="34">
@@ -1475,27 +1475,27 @@
         <v>1613</v>
       </c>
       <c r="C34" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>DPI66387 -&gt; DPI66339 -&gt; DPI66590 -&gt; DFT80044 -&gt; DPI70255 -&gt; DPI66645 -&gt; DPI64413 -&gt; DPI64244 -&gt; DFT80088 -&gt; DPI64216 -&gt; DPI70316</t>
+          <t>DPI64436 -&gt; DPI70213 -&gt; DPI66067 -&gt; DPI63915 -&gt; DPI64724 -&gt; DPI64297 -&gt; DPI66742 -&gt; DPI67178</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>962.36697241</v>
+        <v>930.0945775</v>
       </c>
       <c r="F34" t="n">
         <v>980</v>
       </c>
       <c r="G34" t="n">
-        <v>98.20071147040817</v>
+        <v>94.9076099489796</v>
       </c>
       <c r="H34" t="n">
-        <v>594</v>
+        <v>839</v>
       </c>
       <c r="I34" t="n">
-        <v>293783.4</v>
+        <v>374167.9</v>
       </c>
     </row>
     <row r="35">
@@ -1506,27 +1506,27 @@
         <v>1613</v>
       </c>
       <c r="C35" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>DPI63958 -&gt; DPI64686 -&gt; DPI66203 -&gt; DPI66289 -&gt; DPI64039 -&gt; DPI66069 -&gt; DPI64301 -&gt; DPI64218</t>
+          <t>DPI66715 -&gt; DPI64169 -&gt; DPI66051 -&gt; DPI63802 -&gt; DPI64057 -&gt; DPI66172 -&gt; DPI64037 -&gt; DPI70096 -&gt; DPI64413 -&gt; DPI66645 -&gt; DFT80088 -&gt; DPI64216 -&gt; DFT80044</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>877.69884627</v>
+        <v>969.1424378199999</v>
       </c>
       <c r="F35" t="n">
         <v>980</v>
       </c>
       <c r="G35" t="n">
-        <v>89.5611067622449</v>
+        <v>98.89208549183672</v>
       </c>
       <c r="H35" t="n">
-        <v>198</v>
+        <v>911</v>
       </c>
       <c r="I35" t="n">
-        <v>163855.8</v>
+        <v>397791.1</v>
       </c>
     </row>
     <row r="36">
@@ -1537,27 +1537,27 @@
         <v>1613</v>
       </c>
       <c r="C36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>DPI70142 -&gt; DPI64052 -&gt; DPI66179 -&gt; DPI66597 -&gt; DPI67121 -&gt; DPI64450 -&gt; DPI66039 -&gt; DPI66307 -&gt; DPI64638</t>
+          <t>DPI64666 -&gt; DPI66209 -&gt; DPI67224 -&gt; DPI70190 -&gt; DPI70253 -&gt; DPI64056 -&gt; DPI67074 -&gt; DPI64628 -&gt; DPI64119 -&gt; DFT80078</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>971.3478097000002</v>
+        <v>849.8923600000001</v>
       </c>
       <c r="F36" t="n">
         <v>980</v>
       </c>
       <c r="G36" t="n">
-        <v>99.11712343877554</v>
+        <v>86.72371020408164</v>
       </c>
       <c r="H36" t="n">
-        <v>204</v>
+        <v>929</v>
       </c>
       <c r="I36" t="n">
-        <v>165824.4</v>
+        <v>403696.9</v>
       </c>
     </row>
     <row r="37">
@@ -1565,30 +1565,30 @@
         <v>3</v>
       </c>
       <c r="B37" t="n">
-        <v>1613</v>
+        <v>1109</v>
       </c>
       <c r="C37" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>DPI64203 -&gt; DPI67050 -&gt; DPI66122 -&gt; DPI64350 -&gt; DPI66729 -&gt; DPI64246 -&gt; DPI63936 -&gt; DPI66326 -&gt; DPI64418 -&gt; DPI66119 -&gt; DPI70256</t>
+          <t>DPI66940 -&gt; DPI63945 -&gt; DPI64428 -&gt; DPI64741 -&gt; DPI70216 -&gt; DPI64600</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>929.4353752200001</v>
+        <v>456.56431679</v>
       </c>
       <c r="F37" t="n">
-        <v>980</v>
+        <v>660</v>
       </c>
       <c r="G37" t="n">
-        <v>94.8403444102041</v>
+        <v>69.17641163484848</v>
       </c>
       <c r="H37" t="n">
-        <v>997</v>
+        <v>987</v>
       </c>
       <c r="I37" t="n">
-        <v>426007.7</v>
+        <v>367197.6</v>
       </c>
     </row>
     <row r="38">
@@ -1599,27 +1599,27 @@
         <v>1613</v>
       </c>
       <c r="C38" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>DPI70176 -&gt; DPI66755 -&gt; DPI64026 -&gt; DPI70261 -&gt; DPI64469 -&gt; DPI64106 -&gt; DPI66622 -&gt; DPI66389 -&gt; DPI70057 -&gt; DPI66626</t>
+          <t>DPI66400 -&gt; DPI64650 -&gt; DPI66422 -&gt; DPI64250 -&gt; DPI66410 -&gt; DPI65840 -&gt; DPI66377 -&gt; DPI65919</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>980.2124593699998</v>
+        <v>949.1436238800001</v>
       </c>
       <c r="F38" t="n">
         <v>980</v>
       </c>
       <c r="G38" t="n">
-        <v>100.021679527551</v>
+        <v>96.85139019183674</v>
       </c>
       <c r="H38" t="n">
-        <v>1024</v>
+        <v>264</v>
       </c>
       <c r="I38" t="n">
-        <v>434866.4</v>
+        <v>185510.4</v>
       </c>
     </row>
     <row r="39">
@@ -1630,27 +1630,27 @@
         <v>1109</v>
       </c>
       <c r="C39" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>DPI63813 -&gt; DPI66640 -&gt; DPI64252 -&gt; DPI67062 -&gt; DPI66532 -&gt; DPI70022 -&gt; DPI70039 -&gt; DPI66239 -&gt; DPI66591 -&gt; DPI66944 -&gt; DPI66945</t>
+          <t>DPI66578 -&gt; DPI66685 -&gt; DPI66053 -&gt; DPI66437</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>637.97845751</v>
+        <v>538.82434858</v>
       </c>
       <c r="F39" t="n">
         <v>660</v>
       </c>
       <c r="G39" t="n">
-        <v>96.6634026530303</v>
+        <v>81.64005281515151</v>
       </c>
       <c r="H39" t="n">
-        <v>930</v>
+        <v>233</v>
       </c>
       <c r="I39" t="n">
-        <v>350964</v>
+        <v>152458.4</v>
       </c>
     </row>
     <row r="40">
@@ -1665,23 +1665,23 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>DPI66377 -&gt; DPI63951 -&gt; DPI65969 -&gt; DPI67014 -&gt; DPI64140 -&gt; DPI67181 -&gt; DPI66031 -&gt; DPI64408 -&gt; DPI64227 -&gt; DPI64520</t>
+          <t>DPI64377 -&gt; DPI66621 -&gt; DPI70261 -&gt; DPI66622 -&gt; DPI64469 -&gt; DPI64706 -&gt; DPI70306 -&gt; DPI63978 -&gt; DPI64752 -&gt; DPI67014</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>980.6777222499999</v>
+        <v>975.71642203</v>
       </c>
       <c r="F40" t="n">
         <v>980</v>
       </c>
       <c r="G40" t="n">
-        <v>100.0691553316326</v>
+        <v>99.56290020714286</v>
       </c>
       <c r="H40" t="n">
-        <v>284</v>
+        <v>993</v>
       </c>
       <c r="I40" t="n">
-        <v>192072.4</v>
+        <v>424695.3</v>
       </c>
     </row>
     <row r="41">
@@ -1692,27 +1692,27 @@
         <v>1613</v>
       </c>
       <c r="C41" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>DPI66224 -&gt; DPI64310 -&gt; DPI70032 -&gt; DPI66999 -&gt; DPI64079 -&gt; DPI64237 -&gt; DPI66029 -&gt; DPI64102 -&gt; DPI64336 -&gt; DPI66125 -&gt; DPI66497 -&gt; DPI64525 -&gt; DPI64145 -&gt; DPI64317 -&gt; DPI66929</t>
+          <t>DPI64043 -&gt; DPI66119 -&gt; DPI64418 -&gt; DPI66326 -&gt; DPI63936 -&gt; DPI64246 -&gt; DPI64350 -&gt; DPI66729 -&gt; DPI66122 -&gt; DPI64720 -&gt; DPI67093</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>822.36630804</v>
+        <v>808.75885138</v>
       </c>
       <c r="F41" t="n">
         <v>980</v>
       </c>
       <c r="G41" t="n">
-        <v>83.91492939183674</v>
+        <v>82.52641340612244</v>
       </c>
       <c r="H41" t="n">
-        <v>977</v>
+        <v>1001</v>
       </c>
       <c r="I41" t="n">
-        <v>419445.7</v>
+        <v>427320.1</v>
       </c>
     </row>
     <row r="42">
@@ -1720,30 +1720,30 @@
         <v>3</v>
       </c>
       <c r="B42" t="n">
-        <v>407</v>
+        <v>1613</v>
       </c>
       <c r="C42" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>DPI64279 -&gt; DPI70058 -&gt; DPI64641 -&gt; DPI63999 -&gt; DPI66652 -&gt; DPI64703 -&gt; DPI64043</t>
+          <t>DPI66626 -&gt; DPI70057 -&gt; DPI70320 -&gt; DPI64207 -&gt; DPI64106 -&gt; DPI64026 -&gt; DPI66688 -&gt; DPI66378 -&gt; DPI67042</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>304.60346063</v>
+        <v>932.6874006900001</v>
       </c>
       <c r="F42" t="n">
-        <v>350</v>
+        <v>980</v>
       </c>
       <c r="G42" t="n">
-        <v>87.02956017999999</v>
+        <v>95.17218374387755</v>
       </c>
       <c r="H42" t="n">
-        <v>1002</v>
+        <v>1024</v>
       </c>
       <c r="I42" t="n">
-        <v>329149.8</v>
+        <v>434866.4</v>
       </c>
     </row>
     <row r="43">
@@ -1751,30 +1751,30 @@
         <v>3</v>
       </c>
       <c r="B43" t="n">
-        <v>1613</v>
+        <v>1109</v>
       </c>
       <c r="C43" t="n">
         <v>9</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>DPI66400 -&gt; DPI66410 -&gt; DPI66280 -&gt; DPI66926 -&gt; DPI65998 -&gt; DPI66126 -&gt; DPI66076 -&gt; DPI67110 -&gt; DPI66386</t>
+          <t>DPI64279 -&gt; DPI70058 -&gt; DPI64641 -&gt; DPI63999 -&gt; DPI66652 -&gt; DPI64703 -&gt; DPI67050 -&gt; DPI64203 -&gt; DPI70256</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>971.9376120800001</v>
+        <v>578.31481615</v>
       </c>
       <c r="F43" t="n">
-        <v>980</v>
+        <v>660</v>
       </c>
       <c r="G43" t="n">
-        <v>99.17730735510204</v>
+        <v>87.62345699242424</v>
       </c>
       <c r="H43" t="n">
-        <v>274</v>
+        <v>1004</v>
       </c>
       <c r="I43" t="n">
-        <v>188791.4</v>
+        <v>372039.2</v>
       </c>
     </row>
     <row r="44">
@@ -1782,30 +1782,30 @@
         <v>3</v>
       </c>
       <c r="B44" t="n">
-        <v>1613</v>
+        <v>1109</v>
       </c>
       <c r="C44" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>DPI64073 -&gt; DPI66548 -&gt; DPI64083 -&gt; DPI63978 -&gt; DPI64752 -&gt; DPI66733 -&gt; DPI64602 -&gt; DPI65779 -&gt; DPI64019 -&gt; DPI66194</t>
+          <t>DPI64317 -&gt; DPI64145 -&gt; DPI64525 -&gt; DPI66497 -&gt; DPI64102 -&gt; DPI64336 -&gt; DPI66029 -&gt; DPI64237 -&gt; DPI64079 -&gt; DPI66999 -&gt; DPI70032 -&gt; DPI64310 -&gt; DPI66224</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>970.88138968</v>
+        <v>557.25702013</v>
       </c>
       <c r="F44" t="n">
-        <v>980</v>
+        <v>660</v>
       </c>
       <c r="G44" t="n">
-        <v>99.06952955918366</v>
+        <v>84.4328818378788</v>
       </c>
       <c r="H44" t="n">
-        <v>805</v>
+        <v>973</v>
       </c>
       <c r="I44" t="n">
-        <v>363012.5</v>
+        <v>363210.4</v>
       </c>
     </row>
     <row r="45">
@@ -1816,27 +1816,27 @@
         <v>1613</v>
       </c>
       <c r="C45" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>DPI66578 -&gt; DPI67042 -&gt; DPI66378 -&gt; DPI63950 -&gt; DPI66042 -&gt; DPI70104 -&gt; DPI66522 -&gt; DPI66053</t>
+          <t>DPI66929 -&gt; DPI66945 -&gt; DPI66944 -&gt; DPI66591 -&gt; DPI66239 -&gt; DPI70039 -&gt; DPI70022 -&gt; DPI67062 -&gt; DPI66532 -&gt; DPI66125 -&gt; DPI64252 -&gt; DPI66640 -&gt; DPI63813</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>983.9871409399999</v>
+        <v>903.0877454200001</v>
       </c>
       <c r="F45" t="n">
         <v>980</v>
       </c>
       <c r="G45" t="n">
-        <v>100.4068511163265</v>
+        <v>92.15181075714287</v>
       </c>
       <c r="H45" t="n">
-        <v>254</v>
+        <v>933</v>
       </c>
       <c r="I45" t="n">
-        <v>182229.4</v>
+        <v>405009.3</v>
       </c>
     </row>
     <row r="46">
@@ -1851,23 +1851,23 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>DPI64377 -&gt; DPI63823 -&gt; DPI70140 -&gt; DPI66241 -&gt; DPI70091 -&gt; DPI64331 -&gt; DPI65919 -&gt; DPI66619 -&gt; DPI67064 -&gt; DPI66998</t>
+          <t>DPI70069 -&gt; DPI64073 -&gt; DPI64083 -&gt; DPI66548 -&gt; DPI64227 -&gt; DPI66333 -&gt; DPI66926 -&gt; DPI65877 -&gt; DPI66280 -&gt; DPI64577</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>985.1537263599998</v>
+        <v>966.22996573</v>
       </c>
       <c r="F46" t="n">
         <v>980</v>
       </c>
       <c r="G46" t="n">
-        <v>100.525890444898</v>
+        <v>98.59489446224489</v>
       </c>
       <c r="H46" t="n">
-        <v>248</v>
+        <v>806</v>
       </c>
       <c r="I46" t="n">
-        <v>180260.8</v>
+        <v>363340.6</v>
       </c>
     </row>
     <row r="47">
@@ -1875,30 +1875,30 @@
         <v>3</v>
       </c>
       <c r="B47" t="n">
-        <v>407</v>
+        <v>1613</v>
       </c>
       <c r="C47" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>DFT80058 -&gt; DPI64291 -&gt; DPI66104 -&gt; DPI66730</t>
+          <t>DFT80095 -&gt; DPI67021 -&gt; DPI70148 -&gt; DPI66389 -&gt; DPI66042 -&gt; DPI70104 -&gt; DPI66359 -&gt; DPI64520 -&gt; DPI66522 -&gt; DPI66094</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>237.97301692</v>
+        <v>941.5678704300001</v>
       </c>
       <c r="F47" t="n">
-        <v>350</v>
+        <v>980</v>
       </c>
       <c r="G47" t="n">
-        <v>67.99229054857143</v>
+        <v>96.07835412551022</v>
       </c>
       <c r="H47" t="n">
-        <v>889</v>
+        <v>273</v>
       </c>
       <c r="I47" t="n">
-        <v>300911.1</v>
+        <v>188463.3</v>
       </c>
     </row>
     <row r="48">
@@ -1906,30 +1906,30 @@
         <v>3</v>
       </c>
       <c r="B48" t="n">
-        <v>407</v>
+        <v>1613</v>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>DPI66437 -&gt; DPI66573</t>
+          <t>DPI66126 -&gt; DPI65998 -&gt; DPI64140 -&gt; DPI66031 -&gt; DPI64408 -&gt; DPI67181 -&gt; DPI66733 -&gt; DPI66538 -&gt; DPI65969</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>291.50053035</v>
+        <v>943.8202863500001</v>
       </c>
       <c r="F48" t="n">
-        <v>350</v>
+        <v>980</v>
       </c>
       <c r="G48" t="n">
-        <v>83.28586581428571</v>
+        <v>96.30819248469389</v>
       </c>
       <c r="H48" t="n">
-        <v>212</v>
+        <v>285</v>
       </c>
       <c r="I48" t="n">
-        <v>131728.8</v>
+        <v>192400.5</v>
       </c>
     </row>
     <row r="49">
@@ -1940,27 +1940,27 @@
         <v>1613</v>
       </c>
       <c r="C49" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>DFT80095 -&gt; DPI70069 -&gt; DPI67021 -&gt; DPI64207 -&gt; DPI64706 -&gt; DPI70306 -&gt; DPI66333 -&gt; DPI64240 -&gt; DPI66014 -&gt; DPI66359 -&gt; DPI66094</t>
+          <t>DPI63950 -&gt; DPI66014 -&gt; DPI64470 -&gt; DPI67118 -&gt; DPI64240 -&gt; DPI66970 -&gt; DPI67126 -&gt; DPI65993 -&gt; DPI66755 -&gt; DPI70176</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>977.3896428099999</v>
+        <v>977.8676689399999</v>
       </c>
       <c r="F49" t="n">
         <v>980</v>
       </c>
       <c r="G49" t="n">
-        <v>99.73363702142856</v>
+        <v>99.78241519795917</v>
       </c>
       <c r="H49" t="n">
-        <v>994</v>
+        <v>273</v>
       </c>
       <c r="I49" t="n">
-        <v>425023.4</v>
+        <v>188463.3</v>
       </c>
     </row>
     <row r="50">
@@ -1971,27 +1971,27 @@
         <v>1613</v>
       </c>
       <c r="C50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>DPI66688 -&gt; DPI66422 -&gt; DPI65840 -&gt; DPI64650 -&gt; DPI67217 -&gt; DPI66191 -&gt; DPI64577 -&gt; DPI66685</t>
+          <t>DPI66573 -&gt; DPI67110 -&gt; DPI66194 -&gt; DPI66660 -&gt; DPI66521 -&gt; DPI65789 -&gt; DPI64631 -&gt; DPI66076 -&gt; DPI67179</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>932.9729845700001</v>
+        <v>972.6723503599999</v>
       </c>
       <c r="F50" t="n">
         <v>980</v>
       </c>
       <c r="G50" t="n">
-        <v>95.20132495612246</v>
+        <v>99.25228064897958</v>
       </c>
       <c r="H50" t="n">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="I50" t="n">
-        <v>185182.3</v>
+        <v>181573.2</v>
       </c>
     </row>
     <row r="51">
@@ -2006,23 +2006,23 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>DPI64250 -&gt; DPI67118 -&gt; DPI65877 -&gt; DPI66970 -&gt; DPI67126 -&gt; DPI64470 -&gt; DPI65993 -&gt; DPI70148 -&gt; DPI66621 -&gt; DPI70320</t>
+          <t>DPI64019 -&gt; DPI66136 -&gt; DPI65779 -&gt; DPI64602 -&gt; DPI67183 -&gt; DPI65915 -&gt; DPI66501 -&gt; DPI63951 -&gt; DPI67217 -&gt; DPI63823</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>985.6485894299999</v>
+        <v>949.74686466</v>
       </c>
       <c r="F51" t="n">
         <v>980</v>
       </c>
       <c r="G51" t="n">
-        <v>100.5763866765306</v>
+        <v>96.9129453734694</v>
       </c>
       <c r="H51" t="n">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="I51" t="n">
-        <v>191088.1</v>
+        <v>186166.6</v>
       </c>
     </row>
     <row r="52">
@@ -2030,30 +2030,30 @@
         <v>3</v>
       </c>
       <c r="B52" t="n">
-        <v>1109</v>
+        <v>1613</v>
       </c>
       <c r="C52" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>DPI64600 -&gt; DPI67093 -&gt; DPI64720 -&gt; DPI66940 -&gt; DPI63945 -&gt; DPI64428 -&gt; DPI64741 -&gt; DPI70216</t>
+          <t>DPI66998 -&gt; DPI66386 -&gt; DPI67064 -&gt; DPI66619 -&gt; DPI64331 -&gt; DPI66191 -&gt; DPI70091 -&gt; DPI66241 -&gt; DPI70140</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>609.5991484699999</v>
+        <v>886.5567794799999</v>
       </c>
       <c r="F52" t="n">
-        <v>660</v>
+        <v>980</v>
       </c>
       <c r="G52" t="n">
-        <v>92.36350734393939</v>
+        <v>90.46497749795918</v>
       </c>
       <c r="H52" t="n">
-        <v>987</v>
+        <v>244</v>
       </c>
       <c r="I52" t="n">
-        <v>367197.6</v>
+        <v>178948.4</v>
       </c>
     </row>
     <row r="53">
@@ -2061,153 +2061,1455 @@
         <v>3</v>
       </c>
       <c r="B53" t="n">
-        <v>1613</v>
+        <v>407</v>
       </c>
       <c r="C53" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>DPI67179 -&gt; DPI64631 -&gt; DPI66501 -&gt; DPI65915 -&gt; DPI66538 -&gt; DPI67183 -&gt; DPI66136 -&gt; DPI65789 -&gt; DPI66521 -&gt; DPI66660</t>
+          <t>DPI66730 -&gt; DPI66104 -&gt; DPI64291 -&gt; DFT80058</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>974.4717832899998</v>
+        <v>237.9730169200001</v>
       </c>
       <c r="F53" t="n">
-        <v>980</v>
+        <v>350</v>
       </c>
       <c r="G53" t="n">
-        <v>99.43589625408161</v>
+        <v>67.99229054857146</v>
       </c>
       <c r="H53" t="n">
-        <v>265</v>
+        <v>889</v>
       </c>
       <c r="I53" t="n">
-        <v>185838.5</v>
+        <v>300911.1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B54" t="n">
-        <v>1613</v>
+        <v>207</v>
       </c>
       <c r="C54" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>DPI64434 -&gt; DPI66500 -&gt; DPI64448 -&gt; DPI70186 -&gt; DPI70303 -&gt; DPI64629 -&gt; DPI64654 -&gt; DPI64390 -&gt; DPI64702 -&gt; DPI64005</t>
+          <t>DFT80016</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>982.8216884799999</v>
+        <v>22.082508</v>
       </c>
       <c r="F54" t="n">
-        <v>980</v>
+        <v>150</v>
       </c>
       <c r="G54" t="n">
-        <v>100.2879273959184</v>
+        <v>14.721672</v>
       </c>
       <c r="H54" t="n">
-        <v>404</v>
+        <v>65</v>
       </c>
       <c r="I54" t="n">
-        <v>231444.4</v>
+        <v>77017.5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B55" t="n">
-        <v>1613</v>
+        <v>207</v>
       </c>
       <c r="C55" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>DPI70323 -&gt; DPI64226 -&gt; DPI70018 -&gt; DPI66441 -&gt; DPI64549 -&gt; DPI70242 -&gt; DPI70309</t>
+          <t>DFT80025</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>833.1656819000001</v>
+        <v>26.1654</v>
       </c>
       <c r="F55" t="n">
-        <v>980</v>
+        <v>150</v>
       </c>
       <c r="G55" t="n">
-        <v>85.01690631632654</v>
+        <v>17.4436</v>
       </c>
       <c r="H55" t="n">
-        <v>704</v>
+        <v>188</v>
       </c>
       <c r="I55" t="n">
-        <v>329874.4</v>
+        <v>101556</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B56" t="n">
-        <v>1109</v>
+        <v>207</v>
       </c>
       <c r="C56" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>DPI66620 -&gt; DPI64655 -&gt; DPI66927 -&gt; DPI64737</t>
+          <t>DFT80069</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>456.3569773999999</v>
+        <v>41.9052</v>
       </c>
       <c r="F56" t="n">
-        <v>660</v>
+        <v>150</v>
       </c>
       <c r="G56" t="n">
-        <v>69.14499657575757</v>
+        <v>27.9368</v>
       </c>
       <c r="H56" t="n">
-        <v>1073</v>
+        <v>769</v>
       </c>
       <c r="I56" t="n">
-        <v>391690.4</v>
+        <v>217465.5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
+        <v>4</v>
+      </c>
+      <c r="B57" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>DPI63834</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>898.0380000000002</v>
+      </c>
+      <c r="F57" t="n">
+        <v>980</v>
+      </c>
+      <c r="G57" t="n">
+        <v>91.63653061224493</v>
+      </c>
+      <c r="H57" t="n">
+        <v>964</v>
+      </c>
+      <c r="I57" t="n">
+        <v>415180.4</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>4</v>
+      </c>
+      <c r="B58" t="n">
+        <v>207</v>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>DPI63843</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>13.4594</v>
+      </c>
+      <c r="F58" t="n">
+        <v>150</v>
+      </c>
+      <c r="G58" t="n">
+        <v>8.972933333333334</v>
+      </c>
+      <c r="H58" t="n">
+        <v>964</v>
+      </c>
+      <c r="I58" t="n">
+        <v>256368</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>4</v>
+      </c>
+      <c r="B59" t="n">
+        <v>207</v>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>DPI63862</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>109.8696</v>
+      </c>
+      <c r="F59" t="n">
+        <v>150</v>
+      </c>
+      <c r="G59" t="n">
+        <v>73.24639999999999</v>
+      </c>
+      <c r="H59" t="n">
+        <v>185</v>
+      </c>
+      <c r="I59" t="n">
+        <v>100957.5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>4</v>
+      </c>
+      <c r="B60" t="n">
+        <v>207</v>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>DPI63872</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>128.60566</v>
+      </c>
+      <c r="F60" t="n">
+        <v>150</v>
+      </c>
+      <c r="G60" t="n">
+        <v>85.73710666666666</v>
+      </c>
+      <c r="H60" t="n">
+        <v>150</v>
+      </c>
+      <c r="I60" t="n">
+        <v>93975</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>4</v>
+      </c>
+      <c r="B61" t="n">
+        <v>1109</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>DPI63905</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>571.5419999999999</v>
+      </c>
+      <c r="F61" t="n">
+        <v>660</v>
+      </c>
+      <c r="G61" t="n">
+        <v>86.59727272727271</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1017</v>
+      </c>
+      <c r="I61" t="n">
+        <v>375741.6</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>4</v>
+      </c>
+      <c r="B62" t="n">
+        <v>207</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>DPI64030</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>122.977441</v>
+      </c>
+      <c r="F62" t="n">
+        <v>150</v>
+      </c>
+      <c r="G62" t="n">
+        <v>81.98496066666667</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1104</v>
+      </c>
+      <c r="I62" t="n">
+        <v>284298</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>4</v>
+      </c>
+      <c r="B63" t="n">
+        <v>207</v>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>DPI64040</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>131.0654675</v>
+      </c>
+      <c r="F63" t="n">
+        <v>150</v>
+      </c>
+      <c r="G63" t="n">
+        <v>87.37697833333333</v>
+      </c>
+      <c r="H63" t="n">
+        <v>204</v>
+      </c>
+      <c r="I63" t="n">
+        <v>104748</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>4</v>
+      </c>
+      <c r="B64" t="n">
+        <v>207</v>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>DPI64084</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>95.62609999999999</v>
+      </c>
+      <c r="F64" t="n">
+        <v>150</v>
+      </c>
+      <c r="G64" t="n">
+        <v>63.75073333333333</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1044</v>
+      </c>
+      <c r="I64" t="n">
+        <v>272328</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>4</v>
+      </c>
+      <c r="B65" t="n">
+        <v>207</v>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>DPI64181</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>106.7479</v>
+      </c>
+      <c r="F65" t="n">
+        <v>150</v>
+      </c>
+      <c r="G65" t="n">
+        <v>71.16526666666668</v>
+      </c>
+      <c r="H65" t="n">
+        <v>191</v>
+      </c>
+      <c r="I65" t="n">
+        <v>102154.5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>4</v>
+      </c>
+      <c r="B66" t="n">
+        <v>207</v>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>DPI64190</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>123.2049255</v>
+      </c>
+      <c r="F66" t="n">
+        <v>150</v>
+      </c>
+      <c r="G66" t="n">
+        <v>82.13661699999997</v>
+      </c>
+      <c r="H66" t="n">
+        <v>193</v>
+      </c>
+      <c r="I66" t="n">
+        <v>102553.5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>4</v>
+      </c>
+      <c r="B67" t="n">
+        <v>407</v>
+      </c>
+      <c r="C67" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>DPI64204</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>284.046</v>
+      </c>
+      <c r="F67" t="n">
+        <v>350</v>
+      </c>
+      <c r="G67" t="n">
+        <v>81.15599999999999</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1021</v>
+      </c>
+      <c r="I67" t="n">
+        <v>333897.9</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>4</v>
+      </c>
+      <c r="B68" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C68" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>DPI64205</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>995.3472000000002</v>
+      </c>
+      <c r="F68" t="n">
+        <v>980</v>
+      </c>
+      <c r="G68" t="n">
+        <v>101.5660408163265</v>
+      </c>
+      <c r="H68" t="n">
+        <v>780</v>
+      </c>
+      <c r="I68" t="n">
+        <v>354810</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>4</v>
+      </c>
+      <c r="B69" t="n">
+        <v>207</v>
+      </c>
+      <c r="C69" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>DPI64235</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>56.9948</v>
+      </c>
+      <c r="F69" t="n">
+        <v>150</v>
+      </c>
+      <c r="G69" t="n">
+        <v>37.99653333333333</v>
+      </c>
+      <c r="H69" t="n">
+        <v>184</v>
+      </c>
+      <c r="I69" t="n">
+        <v>100758</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>4</v>
+      </c>
+      <c r="B70" t="n">
+        <v>407</v>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>DPI64286</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>162.227688</v>
+      </c>
+      <c r="F70" t="n">
+        <v>350</v>
+      </c>
+      <c r="G70" t="n">
+        <v>46.350768</v>
+      </c>
+      <c r="H70" t="n">
+        <v>1191</v>
+      </c>
+      <c r="I70" t="n">
+        <v>376380.9</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>4</v>
+      </c>
+      <c r="B71" t="n">
+        <v>207</v>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>DPI64349</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>93.85904950000001</v>
+      </c>
+      <c r="F71" t="n">
+        <v>150</v>
+      </c>
+      <c r="G71" t="n">
+        <v>62.57269966666668</v>
+      </c>
+      <c r="H71" t="n">
+        <v>1179</v>
+      </c>
+      <c r="I71" t="n">
+        <v>299260.5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>4</v>
+      </c>
+      <c r="B72" t="n">
+        <v>207</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>DPI64424</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>72.16600000000001</v>
+      </c>
+      <c r="F72" t="n">
+        <v>150</v>
+      </c>
+      <c r="G72" t="n">
+        <v>48.11066666666667</v>
+      </c>
+      <c r="H72" t="n">
+        <v>187</v>
+      </c>
+      <c r="I72" t="n">
+        <v>101356.5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>4</v>
+      </c>
+      <c r="B73" t="n">
+        <v>207</v>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>DPI64594</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>77.25859999999999</v>
+      </c>
+      <c r="F73" t="n">
+        <v>150</v>
+      </c>
+      <c r="G73" t="n">
+        <v>51.50573333333332</v>
+      </c>
+      <c r="H73" t="n">
+        <v>188</v>
+      </c>
+      <c r="I73" t="n">
+        <v>101556</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>4</v>
+      </c>
+      <c r="B74" t="n">
+        <v>207</v>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>DPI64717</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>72.49699999999999</v>
+      </c>
+      <c r="F74" t="n">
+        <v>150</v>
+      </c>
+      <c r="G74" t="n">
+        <v>48.33133333333333</v>
+      </c>
+      <c r="H74" t="n">
+        <v>224</v>
+      </c>
+      <c r="I74" t="n">
+        <v>108738</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>4</v>
+      </c>
+      <c r="B75" t="n">
+        <v>407</v>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>DPI66008</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>186.4224215</v>
+      </c>
+      <c r="F75" t="n">
+        <v>350</v>
+      </c>
+      <c r="G75" t="n">
+        <v>53.26354900000001</v>
+      </c>
+      <c r="H75" t="n">
+        <v>188</v>
+      </c>
+      <c r="I75" t="n">
+        <v>125731.2</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>4</v>
+      </c>
+      <c r="B76" t="n">
+        <v>407</v>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>DPI66035</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>150.1102</v>
+      </c>
+      <c r="F76" t="n">
+        <v>350</v>
+      </c>
+      <c r="G76" t="n">
+        <v>42.88862857142858</v>
+      </c>
+      <c r="H76" t="n">
+        <v>185</v>
+      </c>
+      <c r="I76" t="n">
+        <v>124981.5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>4</v>
+      </c>
+      <c r="B77" t="n">
+        <v>207</v>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>DPI66290</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>71.23049999999999</v>
+      </c>
+      <c r="F77" t="n">
+        <v>150</v>
+      </c>
+      <c r="G77" t="n">
+        <v>47.48699999999999</v>
+      </c>
+      <c r="H77" t="n">
+        <v>225</v>
+      </c>
+      <c r="I77" t="n">
+        <v>108937.5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>4</v>
+      </c>
+      <c r="B78" t="n">
+        <v>407</v>
+      </c>
+      <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>DPI66332</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>222.122161</v>
+      </c>
+      <c r="F78" t="n">
+        <v>350</v>
+      </c>
+      <c r="G78" t="n">
+        <v>63.46347457142857</v>
+      </c>
+      <c r="H78" t="n">
+        <v>198</v>
+      </c>
+      <c r="I78" t="n">
+        <v>128230.2</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>4</v>
+      </c>
+      <c r="B79" t="n">
+        <v>407</v>
+      </c>
+      <c r="C79" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>DPI66463</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>243.76794</v>
+      </c>
+      <c r="F79" t="n">
+        <v>350</v>
+      </c>
+      <c r="G79" t="n">
+        <v>69.64798285714285</v>
+      </c>
+      <c r="H79" t="n">
+        <v>194</v>
+      </c>
+      <c r="I79" t="n">
+        <v>127230.6</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>4</v>
+      </c>
+      <c r="B80" t="n">
+        <v>207</v>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>DPI66487</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>59.30860000000001</v>
+      </c>
+      <c r="F80" t="n">
+        <v>150</v>
+      </c>
+      <c r="G80" t="n">
+        <v>39.53906666666667</v>
+      </c>
+      <c r="H80" t="n">
+        <v>183</v>
+      </c>
+      <c r="I80" t="n">
+        <v>100558.5</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>4</v>
+      </c>
+      <c r="B81" t="n">
+        <v>407</v>
+      </c>
+      <c r="C81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>DPI66507</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>200.4813</v>
+      </c>
+      <c r="F81" t="n">
+        <v>350</v>
+      </c>
+      <c r="G81" t="n">
+        <v>57.28037142857143</v>
+      </c>
+      <c r="H81" t="n">
+        <v>191</v>
+      </c>
+      <c r="I81" t="n">
+        <v>126480.9</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>4</v>
+      </c>
+      <c r="B82" t="n">
+        <v>407</v>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>DPI66904</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>152.1270185</v>
+      </c>
+      <c r="F82" t="n">
+        <v>350</v>
+      </c>
+      <c r="G82" t="n">
+        <v>43.46486242857143</v>
+      </c>
+      <c r="H82" t="n">
+        <v>1101</v>
+      </c>
+      <c r="I82" t="n">
+        <v>353889.9</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>4</v>
+      </c>
+      <c r="B83" t="n">
+        <v>207</v>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>DPI67040</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>100.023278</v>
+      </c>
+      <c r="F83" t="n">
+        <v>150</v>
+      </c>
+      <c r="G83" t="n">
+        <v>66.68218533333334</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
+        <v>64050</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>4</v>
+      </c>
+      <c r="B84" t="n">
+        <v>207</v>
+      </c>
+      <c r="C84" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>DPI67069</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>65.61912249999999</v>
+      </c>
+      <c r="F84" t="n">
+        <v>150</v>
+      </c>
+      <c r="G84" t="n">
+        <v>43.74608166666666</v>
+      </c>
+      <c r="H84" t="n">
+        <v>188</v>
+      </c>
+      <c r="I84" t="n">
+        <v>101556</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>4</v>
+      </c>
+      <c r="B85" t="n">
+        <v>207</v>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>DPI67235</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>59.61479999999999</v>
+      </c>
+      <c r="F85" t="n">
+        <v>150</v>
+      </c>
+      <c r="G85" t="n">
+        <v>39.74319999999999</v>
+      </c>
+      <c r="H85" t="n">
+        <v>773</v>
+      </c>
+      <c r="I85" t="n">
+        <v>218263.5</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>4</v>
+      </c>
+      <c r="B86" t="n">
+        <v>207</v>
+      </c>
+      <c r="C86" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>DPI67252</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>92.10120000000001</v>
+      </c>
+      <c r="F86" t="n">
+        <v>150</v>
+      </c>
+      <c r="G86" t="n">
+        <v>61.4008</v>
+      </c>
+      <c r="H86" t="n">
+        <v>768</v>
+      </c>
+      <c r="I86" t="n">
+        <v>217266</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>4</v>
+      </c>
+      <c r="B87" t="n">
+        <v>207</v>
+      </c>
+      <c r="C87" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>DPI70014</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>87.2212</v>
+      </c>
+      <c r="F87" t="n">
+        <v>150</v>
+      </c>
+      <c r="G87" t="n">
+        <v>58.14746666666667</v>
+      </c>
+      <c r="H87" t="n">
+        <v>199</v>
+      </c>
+      <c r="I87" t="n">
+        <v>103750.5</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>4</v>
+      </c>
+      <c r="B88" t="n">
+        <v>207</v>
+      </c>
+      <c r="C88" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>DPI70051</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>44.383</v>
+      </c>
+      <c r="F88" t="n">
+        <v>150</v>
+      </c>
+      <c r="G88" t="n">
+        <v>29.58866666666666</v>
+      </c>
+      <c r="H88" t="n">
+        <v>185</v>
+      </c>
+      <c r="I88" t="n">
+        <v>100957.5</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>4</v>
+      </c>
+      <c r="B89" t="n">
+        <v>207</v>
+      </c>
+      <c r="C89" t="n">
+        <v>1</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>DPI70126</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>72.4555</v>
+      </c>
+      <c r="F89" t="n">
+        <v>150</v>
+      </c>
+      <c r="G89" t="n">
+        <v>48.30366666666666</v>
+      </c>
+      <c r="H89" t="n">
+        <v>213</v>
+      </c>
+      <c r="I89" t="n">
+        <v>106543.5</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>4</v>
+      </c>
+      <c r="B90" t="n">
+        <v>407</v>
+      </c>
+      <c r="C90" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>DPI70182</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>228.606</v>
+      </c>
+      <c r="F90" t="n">
+        <v>350</v>
+      </c>
+      <c r="G90" t="n">
+        <v>65.316</v>
+      </c>
+      <c r="H90" t="n">
+        <v>1030</v>
+      </c>
+      <c r="I90" t="n">
+        <v>336147</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>4</v>
+      </c>
+      <c r="B91" t="n">
+        <v>207</v>
+      </c>
+      <c r="C91" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>DPI70321</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>106.680992</v>
+      </c>
+      <c r="F91" t="n">
+        <v>150</v>
+      </c>
+      <c r="G91" t="n">
+        <v>71.12066133333335</v>
+      </c>
+      <c r="H91" t="n">
+        <v>938</v>
+      </c>
+      <c r="I91" t="n">
+        <v>251181</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>4</v>
+      </c>
+      <c r="B92" t="n">
+        <v>207</v>
+      </c>
+      <c r="C92" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>DPI63871</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>137.11044</v>
+      </c>
+      <c r="F92" t="n">
+        <v>150</v>
+      </c>
+      <c r="G92" t="n">
+        <v>91.40696</v>
+      </c>
+      <c r="H92" t="n">
+        <v>479</v>
+      </c>
+      <c r="I92" t="n">
+        <v>159610.5</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>4</v>
+      </c>
+      <c r="B93" t="n">
+        <v>207</v>
+      </c>
+      <c r="C93" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>DPI64610</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>81.90635999999998</v>
+      </c>
+      <c r="F93" t="n">
+        <v>150</v>
+      </c>
+      <c r="G93" t="n">
+        <v>54.60423999999998</v>
+      </c>
+      <c r="H93" t="n">
+        <v>481</v>
+      </c>
+      <c r="I93" t="n">
+        <v>160009.5</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>4</v>
+      </c>
+      <c r="B94" t="n">
+        <v>207</v>
+      </c>
+      <c r="C94" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>DPI70129</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>102.0003</v>
+      </c>
+      <c r="F94" t="n">
+        <v>150</v>
+      </c>
+      <c r="G94" t="n">
+        <v>68.00019999999999</v>
+      </c>
+      <c r="H94" t="n">
+        <v>369</v>
+      </c>
+      <c r="I94" t="n">
+        <v>137665.5</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
         <v>5</v>
       </c>
-      <c r="B57" t="n">
-        <v>1613</v>
-      </c>
-      <c r="C57" t="n">
+      <c r="B95" t="n">
+        <v>207</v>
+      </c>
+      <c r="C95" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>DPI70309</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>54.18531179999999</v>
+      </c>
+      <c r="F95" t="n">
+        <v>150</v>
+      </c>
+      <c r="G95" t="n">
+        <v>36.1235412</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
+        <v>64050</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>5</v>
+      </c>
+      <c r="B96" t="n">
+        <v>1109</v>
+      </c>
+      <c r="C96" t="n">
+        <v>4</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>DPI64737 -&gt; DPI66927 -&gt; DPI64655 -&gt; DPI66620</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>456.3569774</v>
+      </c>
+      <c r="F96" t="n">
+        <v>660</v>
+      </c>
+      <c r="G96" t="n">
+        <v>69.14499657575757</v>
+      </c>
+      <c r="H96" t="n">
+        <v>1073</v>
+      </c>
+      <c r="I96" t="n">
+        <v>391690.4</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>5</v>
+      </c>
+      <c r="B97" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C97" t="n">
+        <v>6</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>DPI70242 -&gt; DPI64549 -&gt; DPI66441 -&gt; DPI70018 -&gt; DPI64226 -&gt; DPI70323</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>778.9803701000001</v>
+      </c>
+      <c r="F97" t="n">
+        <v>980</v>
+      </c>
+      <c r="G97" t="n">
+        <v>79.48779286734695</v>
+      </c>
+      <c r="H97" t="n">
+        <v>704</v>
+      </c>
+      <c r="I97" t="n">
+        <v>329874.4</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>5</v>
+      </c>
+      <c r="B98" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C98" t="n">
+        <v>10</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>DPI64005 -&gt; DPI64702 -&gt; DPI64390 -&gt; DPI64654 -&gt; DPI70303 -&gt; DPI64629 -&gt; DPI70186 -&gt; DPI64448 -&gt; DPI66500 -&gt; DPI64434</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>982.82168848</v>
+      </c>
+      <c r="F98" t="n">
+        <v>980</v>
+      </c>
+      <c r="G98" t="n">
+        <v>100.2879273959184</v>
+      </c>
+      <c r="H98" t="n">
+        <v>404</v>
+      </c>
+      <c r="I98" t="n">
+        <v>231444.4</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>5</v>
+      </c>
+      <c r="B99" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C99" t="n">
         <v>8</v>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>DPI67135 -&gt; DPI65995 -&gt; DPI66445 -&gt; DPI64122 -&gt; DPI64494 -&gt; DPI67086 -&gt; DPI64683 -&gt; DPI70144</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>DPI70144 -&gt; DPI64683 -&gt; DPI67086 -&gt; DPI64494 -&gt; DPI64122 -&gt; DPI66445 -&gt; DPI65995 -&gt; DPI67135</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
         <v>952.8232583</v>
       </c>
-      <c r="F57" t="n">
-        <v>980</v>
-      </c>
-      <c r="G57" t="n">
+      <c r="F99" t="n">
+        <v>980</v>
+      </c>
+      <c r="G99" t="n">
         <v>97.22686309183673</v>
       </c>
-      <c r="H57" t="n">
+      <c r="H99" t="n">
         <v>33</v>
       </c>
-      <c r="I57" t="n">
+      <c r="I99" t="n">
         <v>109719.3</v>
       </c>
     </row>
